--- a/can上层通信协议.xlsx
+++ b/can上层通信协议.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\FanArray\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\FanArray\CODE\FA_Ctrl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{84E54814-4EE8-448D-AC23-3256B4C53EE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F231857-7BD2-44F3-88D7-49F5D6341D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView minimized="1" xWindow="-375" yWindow="2775" windowWidth="27660" windowHeight="17580" xr2:uid="{33FD23F6-9F23-4515-98A3-37DCFD7DD961}"/>
+    <workbookView xWindow="-28920" yWindow="2220" windowWidth="29040" windowHeight="16440" xr2:uid="{33FD23F6-9F23-4515-98A3-37DCFD7DD961}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -35,8 +36,26 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
+    <author>tc={884D21C7-659A-4E91-B8F0-6D588451F1B6}</author>
+  </authors>
+  <commentList>
+    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{884D21C7-659A-4E91-B8F0-6D588451F1B6}">
+      <text>
+        <t>[线程批注]
+你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
+注释:
+    暂时只用一帧，4个数据一起</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="74">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="96">
   <si>
     <t>遥控帧</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -260,10 +279,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>风机模块id（4个风机）</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>风机模块id</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -321,11 +336,6 @@
   </si>
   <si>
     <t>2，uint16</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>同上 + 
-8=上传本机状态；9=上传转速</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -390,6 +400,102 @@
     </r>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>0x02</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x01、0x02</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x03、0x04</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x09</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0A、0x0B</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点id（4个风机）</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>|</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>p</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>i</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>d</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>open/close</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>rpm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>m</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>s</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>data(HEX)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>txid</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>rxid</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>dlc</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>系统模式</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上 + 8=上传本机状态；9=停止上传、A=上传转速</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>rpm1</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>rpm2</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>rpm3</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>rpm4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -398,7 +504,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="10" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -467,6 +573,29 @@
       <sz val="11"/>
       <name val="微软雅黑"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="6"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
+      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -568,7 +697,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="50">
+  <borders count="51">
     <border>
       <left/>
       <right/>
@@ -1161,6 +1290,17 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1170,7 +1310,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="136">
+  <cellXfs count="156">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1243,9 +1383,6 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="3" borderId="41" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1378,7 +1515,67 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1492,18 +1689,6 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1528,6 +1713,18 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1559,9 +1756,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1578,6 +1772,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1821,6 +2021,12 @@
     <xdr:clientData/>
   </xdr:oneCellAnchor>
 </xdr:wsDr>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <person displayName="h ." id="{C53B3D0C-41A5-4772-BD6A-75C33DE0B9F3}" userId="ee0ab4f62dbe73ae" providerId="Windows Live"/>
+</personList>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2138,8 +2344,16 @@
 </a:theme>
 </file>
 
+<file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="J12" dT="2026-10-11T16:21:09.51" personId="{C53B3D0C-41A5-4772-BD6A-75C33DE0B9F3}" id="{884D21C7-659A-4E91-B8F0-6D588451F1B6}">
+    <text>暂时只用一帧，4个数据一起</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D80C86E-B8D5-4F55-A52E-43C4564E8A86}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D80C86E-B8D5-4F55-A52E-43C4564E8A86}">
   <dimension ref="D1:P44"/>
   <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
@@ -2165,173 +2379,175 @@
     </row>
     <row r="2" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="3" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="F3" s="56" t="s">
+      <c r="F3" s="55" t="s">
         <v>55</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="96" t="s">
+      <c r="H3" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="97"/>
-      <c r="J3" s="98"/>
+      <c r="I3" s="116"/>
+      <c r="J3" s="117"/>
       <c r="K3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="L3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="128" t="s">
+      <c r="M3" s="147" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="129"/>
-      <c r="O3" s="33" t="s">
+      <c r="N3" s="148"/>
+      <c r="O3" s="32" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D4" s="70" t="s">
+      <c r="D4" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="100" t="s">
+      <c r="E4" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="133">
+      <c r="F4" s="151">
         <v>2</v>
       </c>
-      <c r="G4" s="119" t="s">
-        <v>65</v>
-      </c>
-      <c r="H4" s="105" t="s">
+      <c r="G4" s="138" t="s">
+        <v>64</v>
+      </c>
+      <c r="H4" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="106"/>
-      <c r="J4" s="107" t="s">
+      <c r="I4" s="125"/>
+      <c r="J4" s="68" t="s">
+        <v>57</v>
+      </c>
+      <c r="K4" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="K4" s="57" t="s">
-        <v>59</v>
-      </c>
-      <c r="L4" s="75" t="s">
+      <c r="L4" s="94" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="122" t="s">
+      <c r="M4" s="141" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="116"/>
-      <c r="O4" s="110" t="s">
+      <c r="N4" s="131"/>
+      <c r="O4" s="136" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D5" s="99"/>
-      <c r="E5" s="101"/>
-      <c r="F5" s="134"/>
-      <c r="G5" s="120"/>
-      <c r="H5" s="86"/>
-      <c r="I5" s="87"/>
-      <c r="J5" s="108"/>
-      <c r="K5" s="48" t="s">
+      <c r="D5" s="118"/>
+      <c r="E5" s="120"/>
+      <c r="F5" s="152"/>
+      <c r="G5" s="139"/>
+      <c r="H5" s="105"/>
+      <c r="I5" s="106"/>
+      <c r="J5" s="134" t="s">
+        <v>72</v>
+      </c>
+      <c r="K5" s="47" t="s">
+        <v>61</v>
+      </c>
+      <c r="L5" s="95"/>
+      <c r="M5" s="142"/>
+      <c r="N5" s="132"/>
+      <c r="O5" s="126"/>
+    </row>
+    <row r="6" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D6" s="118"/>
+      <c r="E6" s="120"/>
+      <c r="F6" s="152"/>
+      <c r="G6" s="139"/>
+      <c r="H6" s="105"/>
+      <c r="I6" s="106"/>
+      <c r="J6" s="134"/>
+      <c r="K6" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="L5" s="76"/>
-      <c r="M5" s="123"/>
-      <c r="N5" s="117"/>
-      <c r="O5" s="111"/>
-    </row>
-    <row r="6" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D6" s="99"/>
-      <c r="E6" s="101"/>
-      <c r="F6" s="134"/>
-      <c r="G6" s="120"/>
-      <c r="H6" s="86"/>
-      <c r="I6" s="87"/>
-      <c r="J6" s="108"/>
-      <c r="K6" s="48" t="s">
+      <c r="L6" s="95"/>
+      <c r="M6" s="142"/>
+      <c r="N6" s="132"/>
+      <c r="O6" s="126"/>
+    </row>
+    <row r="7" spans="4:16" x14ac:dyDescent="0.3">
+      <c r="D7" s="118"/>
+      <c r="E7" s="120"/>
+      <c r="F7" s="153"/>
+      <c r="G7" s="140"/>
+      <c r="H7" s="105"/>
+      <c r="I7" s="106"/>
+      <c r="J7" s="135"/>
+      <c r="K7" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="L6" s="76"/>
-      <c r="M6" s="123"/>
-      <c r="N6" s="117"/>
-      <c r="O6" s="111"/>
-    </row>
-    <row r="7" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D7" s="99"/>
-      <c r="E7" s="101"/>
-      <c r="F7" s="135"/>
-      <c r="G7" s="121"/>
-      <c r="H7" s="86"/>
-      <c r="I7" s="87"/>
-      <c r="J7" s="109"/>
-      <c r="K7" s="49" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" s="77"/>
-      <c r="M7" s="123"/>
-      <c r="N7" s="118"/>
-      <c r="O7" s="111"/>
+      <c r="L7" s="96"/>
+      <c r="M7" s="142"/>
+      <c r="N7" s="133"/>
+      <c r="O7" s="126"/>
     </row>
     <row r="8" spans="4:16" ht="47.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="99"/>
-      <c r="E8" s="101"/>
-      <c r="F8" s="78">
+      <c r="D8" s="118"/>
+      <c r="E8" s="120"/>
+      <c r="F8" s="97">
         <v>8</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="86"/>
-      <c r="I8" s="87"/>
-      <c r="J8" s="58" t="s">
-        <v>34</v>
-      </c>
-      <c r="K8" s="36" t="s">
+      <c r="H8" s="105"/>
+      <c r="I8" s="106"/>
+      <c r="J8" s="57" t="s">
+        <v>75</v>
+      </c>
+      <c r="K8" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="L8" s="29">
+      <c r="L8" s="28">
         <v>2</v>
       </c>
-      <c r="M8" s="123"/>
-      <c r="N8" s="34"/>
-      <c r="O8" s="111"/>
+      <c r="M8" s="142"/>
+      <c r="N8" s="33"/>
+      <c r="O8" s="126" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="9" spans="4:16" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D9" s="99"/>
-      <c r="E9" s="101"/>
-      <c r="F9" s="79"/>
+      <c r="D9" s="118"/>
+      <c r="E9" s="120"/>
+      <c r="F9" s="98"/>
       <c r="G9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="86"/>
-      <c r="I9" s="87"/>
-      <c r="J9" s="42" t="s">
-        <v>67</v>
+      <c r="H9" s="105"/>
+      <c r="I9" s="106"/>
+      <c r="J9" s="41" t="s">
+        <v>66</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="L9" s="30" t="s">
+        <v>71</v>
+      </c>
+      <c r="L9" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="124"/>
-      <c r="N9" s="35"/>
-      <c r="O9" s="24" t="s">
-        <v>26</v>
-      </c>
+      <c r="M9" s="143"/>
+      <c r="N9" s="34"/>
+      <c r="O9" s="137"/>
       <c r="P9" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="4:16" ht="3" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D10" s="99"/>
-      <c r="E10" s="101"/>
-      <c r="F10" s="80"/>
+      <c r="D10" s="118"/>
+      <c r="E10" s="120"/>
+      <c r="F10" s="99"/>
       <c r="G10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="86"/>
-      <c r="I10" s="87"/>
+      <c r="H10" s="105"/>
+      <c r="I10" s="106"/>
       <c r="J10" s="8" t="s">
         <v>15</v>
       </c>
@@ -2344,78 +2560,78 @@
       <c r="O10" s="15"/>
     </row>
     <row r="11" spans="4:16" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="99"/>
-      <c r="E11" s="81" t="s">
+      <c r="D11" s="118"/>
+      <c r="E11" s="100" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="21">
         <v>2</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="H11" s="84" t="s">
-        <v>56</v>
-      </c>
-      <c r="I11" s="85"/>
-      <c r="J11" s="43" t="s">
-        <v>58</v>
-      </c>
-      <c r="K11" s="68" t="s">
-        <v>72</v>
-      </c>
-      <c r="L11" s="31"/>
-      <c r="M11" s="113" t="s">
+        <v>65</v>
+      </c>
+      <c r="H11" s="103" t="s">
+        <v>77</v>
+      </c>
+      <c r="I11" s="104"/>
+      <c r="J11" s="42" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="67" t="s">
+        <v>91</v>
+      </c>
+      <c r="L11" s="30"/>
+      <c r="M11" s="128" t="s">
         <v>22</v>
       </c>
       <c r="N11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="O11" s="111" t="s">
+      <c r="O11" s="126" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D12" s="99"/>
-      <c r="E12" s="82"/>
-      <c r="F12" s="90">
+      <c r="D12" s="118"/>
+      <c r="E12" s="101"/>
+      <c r="F12" s="109">
         <v>8</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="86"/>
-      <c r="I12" s="87"/>
-      <c r="J12" s="59" t="s">
-        <v>46</v>
-      </c>
-      <c r="K12" s="92" t="s">
+      <c r="H12" s="105"/>
+      <c r="I12" s="106"/>
+      <c r="J12" s="58" t="s">
+        <v>74</v>
+      </c>
+      <c r="K12" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="131" t="s">
-        <v>71</v>
-      </c>
-      <c r="M12" s="114"/>
-      <c r="N12" s="69"/>
-      <c r="O12" s="111"/>
+      <c r="L12" s="149" t="s">
+        <v>70</v>
+      </c>
+      <c r="M12" s="129"/>
+      <c r="N12" s="86"/>
+      <c r="O12" s="126"/>
     </row>
     <row r="13" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D13" s="71"/>
-      <c r="E13" s="83"/>
-      <c r="F13" s="91"/>
+      <c r="D13" s="90"/>
+      <c r="E13" s="102"/>
+      <c r="F13" s="110"/>
       <c r="G13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="88"/>
-      <c r="I13" s="89"/>
-      <c r="J13" s="45" t="s">
-        <v>47</v>
-      </c>
-      <c r="K13" s="93"/>
-      <c r="L13" s="132"/>
-      <c r="M13" s="115"/>
-      <c r="N13" s="130"/>
-      <c r="O13" s="112"/>
+      <c r="H13" s="107"/>
+      <c r="I13" s="108"/>
+      <c r="J13" s="44" t="s">
+        <v>76</v>
+      </c>
+      <c r="K13" s="112"/>
+      <c r="L13" s="150"/>
+      <c r="M13" s="130"/>
+      <c r="N13" s="88"/>
+      <c r="O13" s="127"/>
     </row>
     <row r="14" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D14"/>
@@ -2440,27 +2656,27 @@
       <c r="L15"/>
     </row>
     <row r="16" spans="4:16" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D16" s="70" t="s">
+      <c r="D16" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="125"/>
-      <c r="F16" s="60">
+      <c r="E16" s="144"/>
+      <c r="F16" s="59">
         <v>8</v>
       </c>
-      <c r="G16" s="62" t="s">
-        <v>69</v>
-      </c>
-      <c r="H16" s="63" t="s">
-        <v>57</v>
-      </c>
-      <c r="I16" s="38"/>
-      <c r="J16" s="46" t="s">
+      <c r="G16" s="61" t="s">
+        <v>68</v>
+      </c>
+      <c r="H16" s="62" t="s">
+        <v>56</v>
+      </c>
+      <c r="I16" s="37"/>
+      <c r="J16" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="K16" s="28" t="s">
+      <c r="K16" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="L16" s="32">
+      <c r="L16" s="31">
         <v>2</v>
       </c>
       <c r="M16" s="13" t="s">
@@ -2469,45 +2685,45 @@
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="4:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D17" s="99"/>
-      <c r="E17" s="126"/>
-      <c r="F17" s="61">
+      <c r="D17" s="118"/>
+      <c r="E17" s="145"/>
+      <c r="F17" s="60">
         <v>8</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>61</v>
-      </c>
-      <c r="H17" s="64" t="s">
+        <v>60</v>
+      </c>
+      <c r="H17" s="63" t="s">
         <v>43</v>
       </c>
       <c r="I17" s="9"/>
-      <c r="J17" s="66" t="s">
-        <v>68</v>
-      </c>
-      <c r="K17" s="67" t="s">
-        <v>70</v>
-      </c>
-      <c r="L17" s="65"/>
+      <c r="J17" s="65" t="s">
+        <v>67</v>
+      </c>
+      <c r="K17" s="66" t="s">
+        <v>69</v>
+      </c>
+      <c r="L17" s="64"/>
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="4:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D18" s="71"/>
-      <c r="E18" s="127"/>
-      <c r="F18" s="61">
+      <c r="D18" s="90"/>
+      <c r="E18" s="146"/>
+      <c r="F18" s="60">
         <v>0</v>
       </c>
-      <c r="G18" s="62" t="s">
+      <c r="G18" s="61" t="s">
         <v>44</v>
       </c>
-      <c r="H18" s="51" t="s">
+      <c r="H18" s="50" t="s">
         <v>43</v>
       </c>
-      <c r="I18" s="37"/>
-      <c r="J18" s="27" t="s">
-        <v>60</v>
-      </c>
-      <c r="K18" s="28"/>
-      <c r="L18" s="65"/>
+      <c r="I18" s="36"/>
+      <c r="J18" s="26" t="s">
+        <v>59</v>
+      </c>
+      <c r="K18" s="27"/>
+      <c r="L18" s="64"/>
       <c r="M18" s="13"/>
       <c r="N18" s="14"/>
     </row>
@@ -2537,17 +2753,17 @@
     </row>
     <row r="29" spans="4:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="30" spans="4:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D30" s="72"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="74"/>
+      <c r="D30" s="91"/>
+      <c r="E30" s="92"/>
+      <c r="F30" s="93"/>
       <c r="G30" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="96" t="s">
+      <c r="H30" s="115" t="s">
         <v>3</v>
       </c>
-      <c r="I30" s="97"/>
-      <c r="J30" s="98"/>
+      <c r="I30" s="116"/>
+      <c r="J30" s="117"/>
       <c r="K30" s="11" t="s">
         <v>2</v>
       </c>
@@ -2556,139 +2772,139 @@
       </c>
     </row>
     <row r="31" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D31" s="70" t="s">
+      <c r="D31" s="89" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="100" t="s">
+      <c r="E31" s="119" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="102" t="s">
+      <c r="F31" s="121" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="105" t="s">
+      <c r="H31" s="124" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="106"/>
-      <c r="J31" s="39" t="s">
+      <c r="I31" s="125"/>
+      <c r="J31" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="K31" s="75" t="s">
+      <c r="K31" s="94" t="s">
         <v>52</v>
       </c>
-      <c r="L31" s="75">
+      <c r="L31" s="94">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D32" s="99"/>
-      <c r="E32" s="101"/>
-      <c r="F32" s="103"/>
+      <c r="D32" s="118"/>
+      <c r="E32" s="120"/>
+      <c r="F32" s="122"/>
       <c r="G32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="86"/>
-      <c r="I32" s="87"/>
-      <c r="J32" s="40" t="s">
+      <c r="H32" s="105"/>
+      <c r="I32" s="106"/>
+      <c r="J32" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K32" s="76"/>
-      <c r="L32" s="76"/>
+      <c r="K32" s="95"/>
+      <c r="L32" s="95"/>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D33" s="99"/>
-      <c r="E33" s="101"/>
-      <c r="F33" s="103"/>
+      <c r="D33" s="118"/>
+      <c r="E33" s="120"/>
+      <c r="F33" s="122"/>
       <c r="G33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H33" s="86"/>
-      <c r="I33" s="87"/>
-      <c r="J33" s="40" t="s">
+      <c r="H33" s="105"/>
+      <c r="I33" s="106"/>
+      <c r="J33" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="76"/>
-      <c r="L33" s="76"/>
+      <c r="K33" s="95"/>
+      <c r="L33" s="95"/>
     </row>
     <row r="34" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D34" s="99"/>
-      <c r="E34" s="101"/>
-      <c r="F34" s="104"/>
+      <c r="D34" s="118"/>
+      <c r="E34" s="120"/>
+      <c r="F34" s="123"/>
       <c r="G34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="86"/>
-      <c r="I34" s="87"/>
-      <c r="J34" s="40" t="s">
+      <c r="H34" s="105"/>
+      <c r="I34" s="106"/>
+      <c r="J34" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="77"/>
-      <c r="L34" s="77"/>
+      <c r="K34" s="96"/>
+      <c r="L34" s="96"/>
     </row>
     <row r="35" spans="4:12" ht="33" x14ac:dyDescent="0.3">
-      <c r="D35" s="99"/>
-      <c r="E35" s="101"/>
-      <c r="F35" s="78" t="s">
+      <c r="D35" s="118"/>
+      <c r="E35" s="120"/>
+      <c r="F35" s="97" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H35" s="86"/>
-      <c r="I35" s="87"/>
-      <c r="J35" s="41" t="s">
+      <c r="H35" s="105"/>
+      <c r="I35" s="106"/>
+      <c r="J35" s="40" t="s">
         <v>34</v>
       </c>
-      <c r="K35" s="36" t="s">
+      <c r="K35" s="35" t="s">
         <v>36</v>
       </c>
-      <c r="L35" s="53">
+      <c r="L35" s="52">
         <v>2</v>
       </c>
     </row>
     <row r="36" spans="4:12" ht="31.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D36" s="99"/>
-      <c r="E36" s="101"/>
-      <c r="F36" s="79"/>
+      <c r="D36" s="118"/>
+      <c r="E36" s="120"/>
+      <c r="F36" s="98"/>
       <c r="G36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H36" s="86"/>
-      <c r="I36" s="87"/>
-      <c r="J36" s="42" t="s">
+      <c r="H36" s="105"/>
+      <c r="I36" s="106"/>
+      <c r="J36" s="41" t="s">
         <v>35</v>
       </c>
       <c r="K36" s="16" t="s">
         <v>39</v>
       </c>
-      <c r="L36" s="54" t="s">
+      <c r="L36" s="53" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="37" spans="4:12" ht="0.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D37" s="99"/>
-      <c r="E37" s="101"/>
-      <c r="F37" s="80"/>
+      <c r="D37" s="118"/>
+      <c r="E37" s="120"/>
+      <c r="F37" s="99"/>
       <c r="G37" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="86"/>
-      <c r="I37" s="87"/>
+      <c r="H37" s="105"/>
+      <c r="I37" s="106"/>
       <c r="J37" s="8" t="s">
         <v>15</v>
       </c>
       <c r="K37" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="L37" s="55" t="s">
+      <c r="L37" s="54" t="s">
         <v>18</v>
       </c>
     </row>
     <row r="38" spans="4:12" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="99"/>
-      <c r="E38" s="81" t="s">
+      <c r="D38" s="118"/>
+      <c r="E38" s="100" t="s">
         <v>5</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -2697,11 +2913,11 @@
       <c r="G38" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="84" t="s">
+      <c r="H38" s="103" t="s">
         <v>53</v>
       </c>
-      <c r="I38" s="85"/>
-      <c r="J38" s="43" t="s">
+      <c r="I38" s="104"/>
+      <c r="J38" s="42" t="s">
         <v>50</v>
       </c>
       <c r="K38" s="18" t="s">
@@ -2712,113 +2928,113 @@
       </c>
     </row>
     <row r="39" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D39" s="99"/>
-      <c r="E39" s="82"/>
-      <c r="F39" s="90" t="s">
+      <c r="D39" s="118"/>
+      <c r="E39" s="101"/>
+      <c r="F39" s="109" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H39" s="86"/>
-      <c r="I39" s="87"/>
-      <c r="J39" s="44" t="s">
+      <c r="H39" s="105"/>
+      <c r="I39" s="106"/>
+      <c r="J39" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="92" t="s">
+      <c r="K39" s="111" t="s">
         <v>38</v>
       </c>
-      <c r="L39" s="94">
+      <c r="L39" s="113">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D40" s="71"/>
-      <c r="E40" s="83"/>
-      <c r="F40" s="91"/>
+      <c r="D40" s="90"/>
+      <c r="E40" s="102"/>
+      <c r="F40" s="110"/>
       <c r="G40" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H40" s="88"/>
-      <c r="I40" s="89"/>
-      <c r="J40" s="45" t="s">
+      <c r="H40" s="107"/>
+      <c r="I40" s="108"/>
+      <c r="J40" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="K40" s="93"/>
-      <c r="L40" s="95"/>
+      <c r="K40" s="112"/>
+      <c r="L40" s="114"/>
     </row>
     <row r="41" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D41" s="69"/>
-      <c r="E41" s="69"/>
-      <c r="F41" s="69"/>
-      <c r="G41" s="69"/>
-      <c r="H41" s="69"/>
-      <c r="I41" s="69"/>
-      <c r="J41" s="69"/>
-      <c r="K41" s="69"/>
-      <c r="L41" s="69"/>
+      <c r="D41" s="86"/>
+      <c r="E41" s="86"/>
+      <c r="F41" s="86"/>
+      <c r="G41" s="86"/>
+      <c r="H41" s="86"/>
+      <c r="I41" s="86"/>
+      <c r="J41" s="86"/>
+      <c r="K41" s="86"/>
+      <c r="L41" s="86"/>
     </row>
     <row r="42" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D42" s="69"/>
-      <c r="E42" s="69"/>
-      <c r="F42" s="69"/>
-      <c r="G42" s="69"/>
-      <c r="H42" s="69"/>
-      <c r="I42" s="69"/>
-      <c r="J42" s="69"/>
-      <c r="K42" s="69"/>
-      <c r="L42" s="69"/>
+      <c r="D42" s="86"/>
+      <c r="E42" s="86"/>
+      <c r="F42" s="86"/>
+      <c r="G42" s="86"/>
+      <c r="H42" s="86"/>
+      <c r="I42" s="86"/>
+      <c r="J42" s="86"/>
+      <c r="K42" s="86"/>
+      <c r="L42" s="86"/>
     </row>
     <row r="43" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D43" s="70" t="s">
+      <c r="D43" s="89" t="s">
         <v>9</v>
       </c>
-      <c r="E43" s="26"/>
-      <c r="F43" s="25" t="s">
+      <c r="E43" s="25"/>
+      <c r="F43" s="24" t="s">
         <v>1</v>
       </c>
       <c r="G43" s="7" t="s">
         <v>7</v>
       </c>
-      <c r="H43" s="50" t="s">
+      <c r="H43" s="49" t="s">
         <v>53</v>
       </c>
-      <c r="I43" s="51"/>
-      <c r="J43" s="46" t="s">
+      <c r="I43" s="50"/>
+      <c r="J43" s="45" t="s">
         <v>31</v>
       </c>
-      <c r="K43" s="28" t="s">
+      <c r="K43" s="27" t="s">
         <v>11</v>
       </c>
-      <c r="L43" s="32">
+      <c r="L43" s="31">
         <v>2</v>
       </c>
     </row>
     <row r="44" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D44" s="71"/>
-      <c r="E44" s="26"/>
-      <c r="F44" s="47" t="s">
+      <c r="D44" s="90"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="46" t="s">
         <v>0</v>
       </c>
       <c r="G44" s="7" t="s">
         <v>44</v>
       </c>
-      <c r="H44" s="50" t="s">
+      <c r="H44" s="49" t="s">
         <v>54</v>
       </c>
-      <c r="I44" s="52"/>
-      <c r="J44" s="27" t="s">
+      <c r="I44" s="51"/>
+      <c r="J44" s="26" t="s">
         <v>41</v>
       </c>
-      <c r="K44" s="28" t="s">
+      <c r="K44" s="27" t="s">
         <v>52</v>
       </c>
-      <c r="L44" s="32">
+      <c r="L44" s="31">
         <v>1</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="39">
+  <mergeCells count="40">
     <mergeCell ref="D16:D18"/>
     <mergeCell ref="G4:G7"/>
     <mergeCell ref="M4:M9"/>
@@ -2835,13 +3051,14 @@
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="H4:I10"/>
     <mergeCell ref="F4:F7"/>
-    <mergeCell ref="J4:J7"/>
-    <mergeCell ref="O4:O8"/>
     <mergeCell ref="O11:O13"/>
     <mergeCell ref="H11:I13"/>
     <mergeCell ref="M11:M13"/>
     <mergeCell ref="L4:L7"/>
     <mergeCell ref="N4:N7"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="O4:O7"/>
+    <mergeCell ref="O8:O9"/>
     <mergeCell ref="D41:L42"/>
     <mergeCell ref="D43:D44"/>
     <mergeCell ref="D30:F30"/>
@@ -2862,5 +3079,563 @@
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8521510C-1B37-40AB-AFA2-021412ADBA84}">
+  <dimension ref="B4:R24"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="3" max="18" width="2.77734375" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>2</v>
+      </c>
+      <c r="E4">
+        <v>3</v>
+      </c>
+      <c r="F4">
+        <v>4</v>
+      </c>
+      <c r="G4">
+        <v>5</v>
+      </c>
+      <c r="H4">
+        <v>6</v>
+      </c>
+      <c r="I4">
+        <v>7</v>
+      </c>
+      <c r="J4">
+        <v>8</v>
+      </c>
+      <c r="K4">
+        <v>9</v>
+      </c>
+      <c r="L4">
+        <v>10</v>
+      </c>
+      <c r="M4">
+        <v>11</v>
+      </c>
+      <c r="N4">
+        <v>12</v>
+      </c>
+      <c r="O4">
+        <v>13</v>
+      </c>
+      <c r="P4">
+        <v>14</v>
+      </c>
+      <c r="Q4">
+        <v>15</v>
+      </c>
+      <c r="R4">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>1</v>
+      </c>
+      <c r="C5" s="71"/>
+      <c r="D5" s="72"/>
+      <c r="E5" s="72"/>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
+      <c r="J5" s="72"/>
+      <c r="K5" s="72"/>
+      <c r="L5" s="72"/>
+      <c r="M5" s="72"/>
+      <c r="N5" s="72"/>
+      <c r="O5" s="72"/>
+      <c r="P5" s="72"/>
+      <c r="Q5" s="72"/>
+      <c r="R5" s="73"/>
+    </row>
+    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B6">
+        <v>2</v>
+      </c>
+      <c r="C6" s="74"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="1"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
+      <c r="N6" s="1"/>
+      <c r="O6" s="1"/>
+      <c r="P6" s="1"/>
+      <c r="Q6" s="1"/>
+      <c r="R6" s="75"/>
+    </row>
+    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B7">
+        <v>3</v>
+      </c>
+      <c r="C7" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="D7" s="86"/>
+      <c r="E7" s="86"/>
+      <c r="F7" s="86"/>
+      <c r="G7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H7" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="I7" s="86"/>
+      <c r="J7" s="86"/>
+      <c r="K7" s="86"/>
+      <c r="L7" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M7" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="N7" s="86"/>
+      <c r="O7" s="86"/>
+      <c r="P7" s="86"/>
+      <c r="Q7" s="1"/>
+      <c r="R7" s="75"/>
+    </row>
+    <row r="8" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B8">
+        <v>4</v>
+      </c>
+      <c r="C8" s="87" t="s">
+        <v>82</v>
+      </c>
+      <c r="D8" s="88"/>
+      <c r="E8" s="88"/>
+      <c r="F8" s="88"/>
+      <c r="G8" s="88"/>
+      <c r="H8" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="I8" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="J8" s="79"/>
+      <c r="K8" s="79"/>
+      <c r="L8" s="79"/>
+      <c r="M8" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="N8" s="69"/>
+      <c r="O8" s="69"/>
+      <c r="P8" s="69"/>
+      <c r="Q8" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="11" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C11">
+        <v>1</v>
+      </c>
+      <c r="D11">
+        <v>2</v>
+      </c>
+      <c r="E11">
+        <v>3</v>
+      </c>
+      <c r="F11">
+        <v>4</v>
+      </c>
+      <c r="G11">
+        <v>5</v>
+      </c>
+      <c r="H11">
+        <v>6</v>
+      </c>
+      <c r="I11">
+        <v>7</v>
+      </c>
+      <c r="J11">
+        <v>8</v>
+      </c>
+      <c r="K11">
+        <v>9</v>
+      </c>
+      <c r="L11">
+        <v>10</v>
+      </c>
+      <c r="M11">
+        <v>11</v>
+      </c>
+      <c r="N11">
+        <v>12</v>
+      </c>
+      <c r="O11">
+        <v>13</v>
+      </c>
+      <c r="P11">
+        <v>14</v>
+      </c>
+      <c r="Q11">
+        <v>15</v>
+      </c>
+      <c r="R11">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B12">
+        <v>1</v>
+      </c>
+      <c r="C12" s="83" t="s">
+        <v>87</v>
+      </c>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="F12" s="72" t="s">
+        <v>78</v>
+      </c>
+      <c r="G12" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="J12" s="72" t="s">
+        <v>78</v>
+      </c>
+      <c r="K12" s="77" t="s">
+        <v>65</v>
+      </c>
+      <c r="L12" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="M12" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="N12" s="72"/>
+      <c r="O12" s="72"/>
+      <c r="P12" s="72"/>
+      <c r="Q12" s="72"/>
+      <c r="R12" s="73"/>
+    </row>
+    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B13">
+        <v>2</v>
+      </c>
+      <c r="C13" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="D13" s="81"/>
+      <c r="E13" s="81"/>
+      <c r="F13" s="81"/>
+      <c r="G13" s="81"/>
+      <c r="H13" s="81"/>
+      <c r="I13" s="81"/>
+      <c r="J13" s="81"/>
+      <c r="K13" s="81"/>
+      <c r="L13" s="81"/>
+      <c r="M13" s="81"/>
+      <c r="N13" s="81"/>
+      <c r="O13" s="81"/>
+      <c r="P13" s="81"/>
+      <c r="Q13" s="81"/>
+      <c r="R13" s="82"/>
+    </row>
+    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B14">
+        <v>3</v>
+      </c>
+      <c r="C14" s="85" t="s">
+        <v>79</v>
+      </c>
+      <c r="D14" s="86"/>
+      <c r="E14" s="86"/>
+      <c r="F14" s="86"/>
+      <c r="G14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="H14" s="86" t="s">
+        <v>80</v>
+      </c>
+      <c r="I14" s="86"/>
+      <c r="J14" s="86"/>
+      <c r="K14" s="86"/>
+      <c r="L14" s="1" t="s">
+        <v>78</v>
+      </c>
+      <c r="M14" s="86" t="s">
+        <v>81</v>
+      </c>
+      <c r="N14" s="86"/>
+      <c r="O14" s="86"/>
+      <c r="P14" s="86"/>
+      <c r="Q14" s="1"/>
+      <c r="R14" s="75"/>
+    </row>
+    <row r="15" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B15">
+        <v>4</v>
+      </c>
+      <c r="C15" s="78" t="s">
+        <v>90</v>
+      </c>
+      <c r="D15" s="79"/>
+      <c r="E15" s="79"/>
+      <c r="F15" s="79"/>
+      <c r="G15" s="79"/>
+      <c r="H15" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="I15" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="J15" s="79"/>
+      <c r="K15" s="79"/>
+      <c r="L15" s="79"/>
+      <c r="M15" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="N15" s="69"/>
+      <c r="O15" s="69"/>
+      <c r="P15" s="69"/>
+      <c r="Q15" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="R15" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="18" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="D18">
+        <v>2</v>
+      </c>
+      <c r="E18">
+        <v>3</v>
+      </c>
+      <c r="F18">
+        <v>4</v>
+      </c>
+      <c r="G18">
+        <v>5</v>
+      </c>
+      <c r="H18">
+        <v>6</v>
+      </c>
+      <c r="I18">
+        <v>7</v>
+      </c>
+      <c r="J18">
+        <v>8</v>
+      </c>
+      <c r="K18">
+        <v>9</v>
+      </c>
+      <c r="L18">
+        <v>10</v>
+      </c>
+      <c r="M18">
+        <v>11</v>
+      </c>
+      <c r="N18">
+        <v>12</v>
+      </c>
+      <c r="O18">
+        <v>13</v>
+      </c>
+      <c r="P18">
+        <v>14</v>
+      </c>
+      <c r="Q18">
+        <v>15</v>
+      </c>
+      <c r="R18">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="83" t="s">
+        <v>87</v>
+      </c>
+      <c r="D19" s="84"/>
+      <c r="E19" s="84"/>
+      <c r="F19" s="72" t="s">
+        <v>78</v>
+      </c>
+      <c r="G19" s="84" t="s">
+        <v>88</v>
+      </c>
+      <c r="H19" s="84"/>
+      <c r="I19" s="84"/>
+      <c r="J19" s="72" t="s">
+        <v>78</v>
+      </c>
+      <c r="K19" s="77" t="s">
+        <v>65</v>
+      </c>
+      <c r="L19" s="70" t="s">
+        <v>78</v>
+      </c>
+      <c r="M19" s="76" t="s">
+        <v>89</v>
+      </c>
+      <c r="N19" s="72"/>
+      <c r="O19" s="72"/>
+      <c r="P19" s="72"/>
+      <c r="Q19" s="72"/>
+      <c r="R19" s="73"/>
+    </row>
+    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" s="80" t="s">
+        <v>86</v>
+      </c>
+      <c r="D20" s="81"/>
+      <c r="E20" s="81"/>
+      <c r="F20" s="81"/>
+      <c r="G20" s="81"/>
+      <c r="H20" s="81"/>
+      <c r="I20" s="81"/>
+      <c r="J20" s="81"/>
+      <c r="K20" s="81"/>
+      <c r="L20" s="81"/>
+      <c r="M20" s="81"/>
+      <c r="N20" s="81"/>
+      <c r="O20" s="81"/>
+      <c r="P20" s="81"/>
+      <c r="Q20" s="81"/>
+      <c r="R20" s="82"/>
+    </row>
+    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" s="85" t="s">
+        <v>92</v>
+      </c>
+      <c r="D21" s="154"/>
+      <c r="E21" s="154"/>
+      <c r="F21" s="154"/>
+      <c r="G21" s="86" t="s">
+        <v>93</v>
+      </c>
+      <c r="H21" s="86"/>
+      <c r="I21" s="86"/>
+      <c r="J21" s="86"/>
+      <c r="K21" s="86" t="s">
+        <v>94</v>
+      </c>
+      <c r="L21" s="86"/>
+      <c r="M21" s="86"/>
+      <c r="N21" s="86"/>
+      <c r="O21" s="86" t="s">
+        <v>95</v>
+      </c>
+      <c r="P21" s="86"/>
+      <c r="Q21" s="86"/>
+      <c r="R21" s="155"/>
+    </row>
+    <row r="22" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22" s="78" t="s">
+        <v>90</v>
+      </c>
+      <c r="D22" s="79"/>
+      <c r="E22" s="79"/>
+      <c r="F22" s="79"/>
+      <c r="G22" s="79"/>
+      <c r="H22" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="I22" s="79" t="s">
+        <v>83</v>
+      </c>
+      <c r="J22" s="79"/>
+      <c r="K22" s="79"/>
+      <c r="L22" s="79"/>
+      <c r="M22" s="69" t="s">
+        <v>78</v>
+      </c>
+      <c r="N22" s="69"/>
+      <c r="O22" s="69"/>
+      <c r="P22" s="69"/>
+      <c r="Q22" s="69" t="s">
+        <v>84</v>
+      </c>
+      <c r="R22" s="15" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>1</v>
+      </c>
+      <c r="H23">
+        <v>6</v>
+      </c>
+      <c r="I23">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="G24">
+        <f>H23-G23</f>
+        <v>5</v>
+      </c>
+      <c r="H24">
+        <f>I23-H23</f>
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="22">
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="G19:I19"/>
+    <mergeCell ref="C20:R20"/>
+    <mergeCell ref="C7:F7"/>
+    <mergeCell ref="H7:K7"/>
+    <mergeCell ref="M7:P7"/>
+    <mergeCell ref="C8:G8"/>
+    <mergeCell ref="I8:L8"/>
+    <mergeCell ref="C15:G15"/>
+    <mergeCell ref="I15:L15"/>
+    <mergeCell ref="C13:R13"/>
+    <mergeCell ref="C12:E12"/>
+    <mergeCell ref="G12:I12"/>
+    <mergeCell ref="C14:F14"/>
+    <mergeCell ref="H14:K14"/>
+    <mergeCell ref="M14:P14"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/can上层通信协议.xlsx
+++ b/can上层通信协议.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F231857-7BD2-44F3-88D7-49F5D6341D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="2220" windowWidth="29040" windowHeight="16440" xr2:uid="{33FD23F6-9F23-4515-98A3-37DCFD7DD961}"/>
+    <workbookView xWindow="-24285" yWindow="2865" windowWidth="19740" windowHeight="13950" activeTab="1" xr2:uid="{33FD23F6-9F23-4515-98A3-37DCFD7DD961}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -504,7 +504,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -589,13 +589,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1310,7 +1303,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="156">
+  <cellXfs count="155">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1545,70 +1538,79 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1620,81 +1622,60 @@
     <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1704,6 +1685,15 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1725,58 +1715,58 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -2385,120 +2375,120 @@
       <c r="G3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="115" t="s">
+      <c r="H3" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="116"/>
-      <c r="J3" s="117"/>
+      <c r="I3" s="97"/>
+      <c r="J3" s="98"/>
       <c r="K3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="L3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="147" t="s">
+      <c r="M3" s="90" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="148"/>
+      <c r="N3" s="91"/>
       <c r="O3" s="32" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D4" s="89" t="s">
+      <c r="D4" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="119" t="s">
+      <c r="E4" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="151">
+      <c r="F4" s="115">
         <v>2</v>
       </c>
-      <c r="G4" s="138" t="s">
+      <c r="G4" s="81" t="s">
         <v>64</v>
       </c>
-      <c r="H4" s="124" t="s">
+      <c r="H4" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="125"/>
+      <c r="I4" s="112"/>
       <c r="J4" s="68" t="s">
         <v>57</v>
       </c>
       <c r="K4" s="56" t="s">
         <v>58</v>
       </c>
-      <c r="L4" s="94" t="s">
+      <c r="L4" s="127" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="141" t="s">
+      <c r="M4" s="84" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="131"/>
-      <c r="O4" s="136" t="s">
+      <c r="N4" s="130"/>
+      <c r="O4" s="135" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D5" s="118"/>
-      <c r="E5" s="120"/>
-      <c r="F5" s="152"/>
-      <c r="G5" s="139"/>
-      <c r="H5" s="105"/>
-      <c r="I5" s="106"/>
-      <c r="J5" s="134" t="s">
+      <c r="D5" s="79"/>
+      <c r="E5" s="107"/>
+      <c r="F5" s="116"/>
+      <c r="G5" s="82"/>
+      <c r="H5" s="113"/>
+      <c r="I5" s="114"/>
+      <c r="J5" s="133" t="s">
         <v>72</v>
       </c>
       <c r="K5" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="L5" s="95"/>
-      <c r="M5" s="142"/>
-      <c r="N5" s="132"/>
-      <c r="O5" s="126"/>
+      <c r="L5" s="128"/>
+      <c r="M5" s="85"/>
+      <c r="N5" s="131"/>
+      <c r="O5" s="118"/>
     </row>
     <row r="6" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D6" s="118"/>
-      <c r="E6" s="120"/>
-      <c r="F6" s="152"/>
-      <c r="G6" s="139"/>
-      <c r="H6" s="105"/>
-      <c r="I6" s="106"/>
-      <c r="J6" s="134"/>
+      <c r="D6" s="79"/>
+      <c r="E6" s="107"/>
+      <c r="F6" s="116"/>
+      <c r="G6" s="82"/>
+      <c r="H6" s="113"/>
+      <c r="I6" s="114"/>
+      <c r="J6" s="133"/>
       <c r="K6" s="47" t="s">
         <v>62</v>
       </c>
-      <c r="L6" s="95"/>
-      <c r="M6" s="142"/>
-      <c r="N6" s="132"/>
-      <c r="O6" s="126"/>
+      <c r="L6" s="128"/>
+      <c r="M6" s="85"/>
+      <c r="N6" s="131"/>
+      <c r="O6" s="118"/>
     </row>
     <row r="7" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D7" s="118"/>
-      <c r="E7" s="120"/>
-      <c r="F7" s="153"/>
-      <c r="G7" s="140"/>
-      <c r="H7" s="105"/>
-      <c r="I7" s="106"/>
-      <c r="J7" s="135"/>
+      <c r="D7" s="79"/>
+      <c r="E7" s="107"/>
+      <c r="F7" s="117"/>
+      <c r="G7" s="83"/>
+      <c r="H7" s="113"/>
+      <c r="I7" s="114"/>
+      <c r="J7" s="134"/>
       <c r="K7" s="48" t="s">
         <v>63</v>
       </c>
-      <c r="L7" s="96"/>
-      <c r="M7" s="142"/>
-      <c r="N7" s="133"/>
-      <c r="O7" s="126"/>
+      <c r="L7" s="129"/>
+      <c r="M7" s="85"/>
+      <c r="N7" s="132"/>
+      <c r="O7" s="118"/>
     </row>
     <row r="8" spans="4:16" ht="47.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="118"/>
-      <c r="E8" s="120"/>
-      <c r="F8" s="97">
+      <c r="D8" s="79"/>
+      <c r="E8" s="107"/>
+      <c r="F8" s="108">
         <v>8</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="105"/>
-      <c r="I8" s="106"/>
+      <c r="H8" s="113"/>
+      <c r="I8" s="114"/>
       <c r="J8" s="57" t="s">
         <v>75</v>
       </c>
@@ -2508,21 +2498,21 @@
       <c r="L8" s="28">
         <v>2</v>
       </c>
-      <c r="M8" s="142"/>
+      <c r="M8" s="85"/>
       <c r="N8" s="33"/>
-      <c r="O8" s="126" t="s">
+      <c r="O8" s="118" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="4:16" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D9" s="118"/>
-      <c r="E9" s="120"/>
-      <c r="F9" s="98"/>
+      <c r="D9" s="79"/>
+      <c r="E9" s="107"/>
+      <c r="F9" s="109"/>
       <c r="G9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="105"/>
-      <c r="I9" s="106"/>
+      <c r="H9" s="113"/>
+      <c r="I9" s="114"/>
       <c r="J9" s="41" t="s">
         <v>66</v>
       </c>
@@ -2532,22 +2522,22 @@
       <c r="L9" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="143"/>
+      <c r="M9" s="86"/>
       <c r="N9" s="34"/>
-      <c r="O9" s="137"/>
+      <c r="O9" s="136"/>
       <c r="P9" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="4:16" ht="3" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D10" s="118"/>
-      <c r="E10" s="120"/>
-      <c r="F10" s="99"/>
+      <c r="D10" s="79"/>
+      <c r="E10" s="107"/>
+      <c r="F10" s="110"/>
       <c r="G10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="105"/>
-      <c r="I10" s="106"/>
+      <c r="H10" s="113"/>
+      <c r="I10" s="114"/>
       <c r="J10" s="8" t="s">
         <v>15</v>
       </c>
@@ -2560,8 +2550,8 @@
       <c r="O10" s="15"/>
     </row>
     <row r="11" spans="4:16" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="118"/>
-      <c r="E11" s="100" t="s">
+      <c r="D11" s="79"/>
+      <c r="E11" s="103" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="21">
@@ -2570,10 +2560,10 @@
       <c r="G11" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="H11" s="103" t="s">
+      <c r="H11" s="120" t="s">
         <v>77</v>
       </c>
-      <c r="I11" s="104"/>
+      <c r="I11" s="121"/>
       <c r="J11" s="42" t="s">
         <v>73</v>
       </c>
@@ -2581,57 +2571,57 @@
         <v>91</v>
       </c>
       <c r="L11" s="30"/>
-      <c r="M11" s="128" t="s">
+      <c r="M11" s="124" t="s">
         <v>22</v>
       </c>
       <c r="N11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="O11" s="126" t="s">
+      <c r="O11" s="118" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D12" s="118"/>
-      <c r="E12" s="101"/>
-      <c r="F12" s="109">
+      <c r="D12" s="79"/>
+      <c r="E12" s="104"/>
+      <c r="F12" s="99">
         <v>8</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="105"/>
-      <c r="I12" s="106"/>
+      <c r="H12" s="113"/>
+      <c r="I12" s="114"/>
       <c r="J12" s="58" t="s">
         <v>74</v>
       </c>
-      <c r="K12" s="111" t="s">
+      <c r="K12" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="149" t="s">
+      <c r="L12" s="94" t="s">
         <v>70</v>
       </c>
-      <c r="M12" s="129"/>
-      <c r="N12" s="86"/>
-      <c r="O12" s="126"/>
+      <c r="M12" s="125"/>
+      <c r="N12" s="92"/>
+      <c r="O12" s="118"/>
     </row>
     <row r="13" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D13" s="90"/>
-      <c r="E13" s="102"/>
-      <c r="F13" s="110"/>
+      <c r="D13" s="80"/>
+      <c r="E13" s="105"/>
+      <c r="F13" s="100"/>
       <c r="G13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="107"/>
-      <c r="I13" s="108"/>
+      <c r="H13" s="122"/>
+      <c r="I13" s="123"/>
       <c r="J13" s="44" t="s">
         <v>76</v>
       </c>
-      <c r="K13" s="112"/>
-      <c r="L13" s="150"/>
-      <c r="M13" s="130"/>
-      <c r="N13" s="88"/>
-      <c r="O13" s="127"/>
+      <c r="K13" s="102"/>
+      <c r="L13" s="95"/>
+      <c r="M13" s="126"/>
+      <c r="N13" s="93"/>
+      <c r="O13" s="119"/>
     </row>
     <row r="14" spans="4:16" x14ac:dyDescent="0.3">
       <c r="D14"/>
@@ -2656,10 +2646,10 @@
       <c r="L15"/>
     </row>
     <row r="16" spans="4:16" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D16" s="89" t="s">
+      <c r="D16" s="78" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="144"/>
+      <c r="E16" s="87"/>
       <c r="F16" s="59">
         <v>8</v>
       </c>
@@ -2685,8 +2675,8 @@
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="4:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D17" s="118"/>
-      <c r="E17" s="145"/>
+      <c r="D17" s="79"/>
+      <c r="E17" s="88"/>
       <c r="F17" s="60">
         <v>8</v>
       </c>
@@ -2707,8 +2697,8 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="4:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D18" s="90"/>
-      <c r="E18" s="146"/>
+      <c r="D18" s="80"/>
+      <c r="E18" s="89"/>
       <c r="F18" s="60">
         <v>0</v>
       </c>
@@ -2753,17 +2743,17 @@
     </row>
     <row r="29" spans="4:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
     <row r="30" spans="4:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D30" s="91"/>
-      <c r="E30" s="92"/>
-      <c r="F30" s="93"/>
+      <c r="D30" s="137"/>
+      <c r="E30" s="138"/>
+      <c r="F30" s="139"/>
       <c r="G30" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="115" t="s">
+      <c r="H30" s="96" t="s">
         <v>3</v>
       </c>
-      <c r="I30" s="116"/>
-      <c r="J30" s="117"/>
+      <c r="I30" s="97"/>
+      <c r="J30" s="98"/>
       <c r="K30" s="11" t="s">
         <v>2</v>
       </c>
@@ -2772,88 +2762,88 @@
       </c>
     </row>
     <row r="31" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D31" s="89" t="s">
+      <c r="D31" s="78" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="119" t="s">
+      <c r="E31" s="106" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="121" t="s">
+      <c r="F31" s="142" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="124" t="s">
+      <c r="H31" s="111" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="125"/>
+      <c r="I31" s="112"/>
       <c r="J31" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="K31" s="94" t="s">
+      <c r="K31" s="127" t="s">
         <v>52</v>
       </c>
-      <c r="L31" s="94">
+      <c r="L31" s="127">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D32" s="118"/>
-      <c r="E32" s="120"/>
-      <c r="F32" s="122"/>
+      <c r="D32" s="79"/>
+      <c r="E32" s="107"/>
+      <c r="F32" s="143"/>
       <c r="G32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="105"/>
-      <c r="I32" s="106"/>
+      <c r="H32" s="113"/>
+      <c r="I32" s="114"/>
       <c r="J32" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K32" s="95"/>
-      <c r="L32" s="95"/>
+      <c r="K32" s="128"/>
+      <c r="L32" s="128"/>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D33" s="118"/>
-      <c r="E33" s="120"/>
-      <c r="F33" s="122"/>
+      <c r="D33" s="79"/>
+      <c r="E33" s="107"/>
+      <c r="F33" s="143"/>
       <c r="G33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H33" s="105"/>
-      <c r="I33" s="106"/>
+      <c r="H33" s="113"/>
+      <c r="I33" s="114"/>
       <c r="J33" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="95"/>
-      <c r="L33" s="95"/>
+      <c r="K33" s="128"/>
+      <c r="L33" s="128"/>
     </row>
     <row r="34" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D34" s="118"/>
-      <c r="E34" s="120"/>
-      <c r="F34" s="123"/>
+      <c r="D34" s="79"/>
+      <c r="E34" s="107"/>
+      <c r="F34" s="144"/>
       <c r="G34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="105"/>
-      <c r="I34" s="106"/>
+      <c r="H34" s="113"/>
+      <c r="I34" s="114"/>
       <c r="J34" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="96"/>
-      <c r="L34" s="96"/>
+      <c r="K34" s="129"/>
+      <c r="L34" s="129"/>
     </row>
     <row r="35" spans="4:12" ht="33" x14ac:dyDescent="0.3">
-      <c r="D35" s="118"/>
-      <c r="E35" s="120"/>
-      <c r="F35" s="97" t="s">
+      <c r="D35" s="79"/>
+      <c r="E35" s="107"/>
+      <c r="F35" s="108" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H35" s="105"/>
-      <c r="I35" s="106"/>
+      <c r="H35" s="113"/>
+      <c r="I35" s="114"/>
       <c r="J35" s="40" t="s">
         <v>34</v>
       </c>
@@ -2865,14 +2855,14 @@
       </c>
     </row>
     <row r="36" spans="4:12" ht="31.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D36" s="118"/>
-      <c r="E36" s="120"/>
-      <c r="F36" s="98"/>
+      <c r="D36" s="79"/>
+      <c r="E36" s="107"/>
+      <c r="F36" s="109"/>
       <c r="G36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H36" s="105"/>
-      <c r="I36" s="106"/>
+      <c r="H36" s="113"/>
+      <c r="I36" s="114"/>
       <c r="J36" s="41" t="s">
         <v>35</v>
       </c>
@@ -2884,14 +2874,14 @@
       </c>
     </row>
     <row r="37" spans="4:12" ht="0.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D37" s="118"/>
-      <c r="E37" s="120"/>
-      <c r="F37" s="99"/>
+      <c r="D37" s="79"/>
+      <c r="E37" s="107"/>
+      <c r="F37" s="110"/>
       <c r="G37" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="105"/>
-      <c r="I37" s="106"/>
+      <c r="H37" s="113"/>
+      <c r="I37" s="114"/>
       <c r="J37" s="8" t="s">
         <v>15</v>
       </c>
@@ -2903,8 +2893,8 @@
       </c>
     </row>
     <row r="38" spans="4:12" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="118"/>
-      <c r="E38" s="100" t="s">
+      <c r="D38" s="79"/>
+      <c r="E38" s="103" t="s">
         <v>5</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -2913,10 +2903,10 @@
       <c r="G38" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="103" t="s">
+      <c r="H38" s="120" t="s">
         <v>53</v>
       </c>
-      <c r="I38" s="104"/>
+      <c r="I38" s="121"/>
       <c r="J38" s="42" t="s">
         <v>50</v>
       </c>
@@ -2928,65 +2918,65 @@
       </c>
     </row>
     <row r="39" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D39" s="118"/>
-      <c r="E39" s="101"/>
-      <c r="F39" s="109" t="s">
+      <c r="D39" s="79"/>
+      <c r="E39" s="104"/>
+      <c r="F39" s="99" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H39" s="105"/>
-      <c r="I39" s="106"/>
+      <c r="H39" s="113"/>
+      <c r="I39" s="114"/>
       <c r="J39" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="111" t="s">
+      <c r="K39" s="101" t="s">
         <v>38</v>
       </c>
-      <c r="L39" s="113">
+      <c r="L39" s="140">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D40" s="90"/>
-      <c r="E40" s="102"/>
-      <c r="F40" s="110"/>
+      <c r="D40" s="80"/>
+      <c r="E40" s="105"/>
+      <c r="F40" s="100"/>
       <c r="G40" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H40" s="107"/>
-      <c r="I40" s="108"/>
+      <c r="H40" s="122"/>
+      <c r="I40" s="123"/>
       <c r="J40" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="K40" s="112"/>
-      <c r="L40" s="114"/>
+      <c r="K40" s="102"/>
+      <c r="L40" s="141"/>
     </row>
     <row r="41" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D41" s="86"/>
-      <c r="E41" s="86"/>
-      <c r="F41" s="86"/>
-      <c r="G41" s="86"/>
-      <c r="H41" s="86"/>
-      <c r="I41" s="86"/>
-      <c r="J41" s="86"/>
-      <c r="K41" s="86"/>
-      <c r="L41" s="86"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="92"/>
     </row>
     <row r="42" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D42" s="86"/>
-      <c r="E42" s="86"/>
-      <c r="F42" s="86"/>
-      <c r="G42" s="86"/>
-      <c r="H42" s="86"/>
-      <c r="I42" s="86"/>
-      <c r="J42" s="86"/>
-      <c r="K42" s="86"/>
-      <c r="L42" s="86"/>
+      <c r="D42" s="92"/>
+      <c r="E42" s="92"/>
+      <c r="F42" s="92"/>
+      <c r="G42" s="92"/>
+      <c r="H42" s="92"/>
+      <c r="I42" s="92"/>
+      <c r="J42" s="92"/>
+      <c r="K42" s="92"/>
+      <c r="L42" s="92"/>
     </row>
     <row r="43" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D43" s="89" t="s">
+      <c r="D43" s="78" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="25"/>
@@ -3011,7 +3001,7 @@
       </c>
     </row>
     <row r="44" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D44" s="90"/>
+      <c r="D44" s="80"/>
       <c r="E44" s="25"/>
       <c r="F44" s="46" t="s">
         <v>0</v>
@@ -3035,6 +3025,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="D41:L42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="K31:K34"/>
+    <mergeCell ref="L31:L34"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="H38:I40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="D31:D40"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="F31:F34"/>
+    <mergeCell ref="H31:I37"/>
+    <mergeCell ref="O11:O13"/>
+    <mergeCell ref="H11:I13"/>
+    <mergeCell ref="M11:M13"/>
+    <mergeCell ref="L4:L7"/>
+    <mergeCell ref="N4:N7"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="O4:O7"/>
+    <mergeCell ref="O8:O9"/>
     <mergeCell ref="D16:D18"/>
     <mergeCell ref="G4:G7"/>
     <mergeCell ref="M4:M9"/>
@@ -3051,30 +3065,6 @@
     <mergeCell ref="F8:F10"/>
     <mergeCell ref="H4:I10"/>
     <mergeCell ref="F4:F7"/>
-    <mergeCell ref="O11:O13"/>
-    <mergeCell ref="H11:I13"/>
-    <mergeCell ref="M11:M13"/>
-    <mergeCell ref="L4:L7"/>
-    <mergeCell ref="N4:N7"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="O4:O7"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="D41:L42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="K31:K34"/>
-    <mergeCell ref="L31:L34"/>
-    <mergeCell ref="F35:F37"/>
-    <mergeCell ref="E38:E40"/>
-    <mergeCell ref="H38:I40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="K39:K40"/>
-    <mergeCell ref="L39:L40"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="D31:D40"/>
-    <mergeCell ref="E31:E37"/>
-    <mergeCell ref="F31:F34"/>
-    <mergeCell ref="H31:I37"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3187,30 +3177,30 @@
       <c r="B7">
         <v>3</v>
       </c>
-      <c r="C7" s="85" t="s">
+      <c r="C7" s="146" t="s">
         <v>79</v>
       </c>
-      <c r="D7" s="86"/>
-      <c r="E7" s="86"/>
-      <c r="F7" s="86"/>
+      <c r="D7" s="92"/>
+      <c r="E7" s="92"/>
+      <c r="F7" s="92"/>
       <c r="G7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H7" s="86" t="s">
+      <c r="H7" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="I7" s="86"/>
-      <c r="J7" s="86"/>
-      <c r="K7" s="86"/>
+      <c r="I7" s="92"/>
+      <c r="J7" s="92"/>
+      <c r="K7" s="92"/>
       <c r="L7" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M7" s="86" t="s">
+      <c r="M7" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="N7" s="86"/>
-      <c r="O7" s="86"/>
-      <c r="P7" s="86"/>
+      <c r="N7" s="92"/>
+      <c r="O7" s="92"/>
+      <c r="P7" s="92"/>
       <c r="Q7" s="1"/>
       <c r="R7" s="75"/>
     </row>
@@ -3218,22 +3208,22 @@
       <c r="B8">
         <v>4</v>
       </c>
-      <c r="C8" s="87" t="s">
+      <c r="C8" s="154" t="s">
         <v>82</v>
       </c>
-      <c r="D8" s="88"/>
-      <c r="E8" s="88"/>
-      <c r="F8" s="88"/>
-      <c r="G8" s="88"/>
+      <c r="D8" s="93"/>
+      <c r="E8" s="93"/>
+      <c r="F8" s="93"/>
+      <c r="G8" s="93"/>
       <c r="H8" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="I8" s="79" t="s">
+      <c r="I8" s="148" t="s">
         <v>83</v>
       </c>
-      <c r="J8" s="79"/>
-      <c r="K8" s="79"/>
-      <c r="L8" s="79"/>
+      <c r="J8" s="148"/>
+      <c r="K8" s="148"/>
+      <c r="L8" s="148"/>
       <c r="M8" s="69" t="s">
         <v>78</v>
       </c>
@@ -3301,19 +3291,19 @@
       <c r="B12">
         <v>1</v>
       </c>
-      <c r="C12" s="83" t="s">
+      <c r="C12" s="149" t="s">
         <v>87</v>
       </c>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
+      <c r="D12" s="150"/>
+      <c r="E12" s="150"/>
       <c r="F12" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="G12" s="84" t="s">
+      <c r="G12" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
+      <c r="H12" s="150"/>
+      <c r="I12" s="150"/>
       <c r="J12" s="72" t="s">
         <v>78</v>
       </c>
@@ -3336,53 +3326,53 @@
       <c r="B13">
         <v>2</v>
       </c>
-      <c r="C13" s="80" t="s">
+      <c r="C13" s="151" t="s">
         <v>86</v>
       </c>
-      <c r="D13" s="81"/>
-      <c r="E13" s="81"/>
-      <c r="F13" s="81"/>
-      <c r="G13" s="81"/>
-      <c r="H13" s="81"/>
-      <c r="I13" s="81"/>
-      <c r="J13" s="81"/>
-      <c r="K13" s="81"/>
-      <c r="L13" s="81"/>
-      <c r="M13" s="81"/>
-      <c r="N13" s="81"/>
-      <c r="O13" s="81"/>
-      <c r="P13" s="81"/>
-      <c r="Q13" s="81"/>
-      <c r="R13" s="82"/>
+      <c r="D13" s="152"/>
+      <c r="E13" s="152"/>
+      <c r="F13" s="152"/>
+      <c r="G13" s="152"/>
+      <c r="H13" s="152"/>
+      <c r="I13" s="152"/>
+      <c r="J13" s="152"/>
+      <c r="K13" s="152"/>
+      <c r="L13" s="152"/>
+      <c r="M13" s="152"/>
+      <c r="N13" s="152"/>
+      <c r="O13" s="152"/>
+      <c r="P13" s="152"/>
+      <c r="Q13" s="152"/>
+      <c r="R13" s="153"/>
     </row>
     <row r="14" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>3</v>
       </c>
-      <c r="C14" s="85" t="s">
+      <c r="C14" s="146" t="s">
         <v>79</v>
       </c>
-      <c r="D14" s="86"/>
-      <c r="E14" s="86"/>
-      <c r="F14" s="86"/>
+      <c r="D14" s="92"/>
+      <c r="E14" s="92"/>
+      <c r="F14" s="92"/>
       <c r="G14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="H14" s="86" t="s">
+      <c r="H14" s="92" t="s">
         <v>80</v>
       </c>
-      <c r="I14" s="86"/>
-      <c r="J14" s="86"/>
-      <c r="K14" s="86"/>
+      <c r="I14" s="92"/>
+      <c r="J14" s="92"/>
+      <c r="K14" s="92"/>
       <c r="L14" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="M14" s="86" t="s">
+      <c r="M14" s="92" t="s">
         <v>81</v>
       </c>
-      <c r="N14" s="86"/>
-      <c r="O14" s="86"/>
-      <c r="P14" s="86"/>
+      <c r="N14" s="92"/>
+      <c r="O14" s="92"/>
+      <c r="P14" s="92"/>
       <c r="Q14" s="1"/>
       <c r="R14" s="75"/>
     </row>
@@ -3390,22 +3380,22 @@
       <c r="B15">
         <v>4</v>
       </c>
-      <c r="C15" s="78" t="s">
+      <c r="C15" s="147" t="s">
         <v>90</v>
       </c>
-      <c r="D15" s="79"/>
-      <c r="E15" s="79"/>
-      <c r="F15" s="79"/>
-      <c r="G15" s="79"/>
+      <c r="D15" s="148"/>
+      <c r="E15" s="148"/>
+      <c r="F15" s="148"/>
+      <c r="G15" s="148"/>
       <c r="H15" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="I15" s="79" t="s">
+      <c r="I15" s="148" t="s">
         <v>83</v>
       </c>
-      <c r="J15" s="79"/>
-      <c r="K15" s="79"/>
-      <c r="L15" s="79"/>
+      <c r="J15" s="148"/>
+      <c r="K15" s="148"/>
+      <c r="L15" s="148"/>
       <c r="M15" s="69" t="s">
         <v>78</v>
       </c>
@@ -3473,19 +3463,19 @@
       <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" s="83" t="s">
+      <c r="C19" s="149" t="s">
         <v>87</v>
       </c>
-      <c r="D19" s="84"/>
-      <c r="E19" s="84"/>
+      <c r="D19" s="150"/>
+      <c r="E19" s="150"/>
       <c r="F19" s="72" t="s">
         <v>78</v>
       </c>
-      <c r="G19" s="84" t="s">
+      <c r="G19" s="150" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="84"/>
-      <c r="I19" s="84"/>
+      <c r="H19" s="150"/>
+      <c r="I19" s="150"/>
       <c r="J19" s="72" t="s">
         <v>78</v>
       </c>
@@ -3508,74 +3498,74 @@
       <c r="B20">
         <v>2</v>
       </c>
-      <c r="C20" s="80" t="s">
+      <c r="C20" s="151" t="s">
         <v>86</v>
       </c>
-      <c r="D20" s="81"/>
-      <c r="E20" s="81"/>
-      <c r="F20" s="81"/>
-      <c r="G20" s="81"/>
-      <c r="H20" s="81"/>
-      <c r="I20" s="81"/>
-      <c r="J20" s="81"/>
-      <c r="K20" s="81"/>
-      <c r="L20" s="81"/>
-      <c r="M20" s="81"/>
-      <c r="N20" s="81"/>
-      <c r="O20" s="81"/>
-      <c r="P20" s="81"/>
-      <c r="Q20" s="81"/>
-      <c r="R20" s="82"/>
+      <c r="D20" s="152"/>
+      <c r="E20" s="152"/>
+      <c r="F20" s="152"/>
+      <c r="G20" s="152"/>
+      <c r="H20" s="152"/>
+      <c r="I20" s="152"/>
+      <c r="J20" s="152"/>
+      <c r="K20" s="152"/>
+      <c r="L20" s="152"/>
+      <c r="M20" s="152"/>
+      <c r="N20" s="152"/>
+      <c r="O20" s="152"/>
+      <c r="P20" s="152"/>
+      <c r="Q20" s="152"/>
+      <c r="R20" s="153"/>
     </row>
     <row r="21" spans="2:18" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>3</v>
       </c>
-      <c r="C21" s="85" t="s">
+      <c r="C21" s="146" t="s">
         <v>92</v>
       </c>
-      <c r="D21" s="154"/>
-      <c r="E21" s="154"/>
-      <c r="F21" s="154"/>
-      <c r="G21" s="86" t="s">
+      <c r="D21" s="92"/>
+      <c r="E21" s="92"/>
+      <c r="F21" s="92"/>
+      <c r="G21" s="92" t="s">
         <v>93</v>
       </c>
-      <c r="H21" s="86"/>
-      <c r="I21" s="86"/>
-      <c r="J21" s="86"/>
-      <c r="K21" s="86" t="s">
+      <c r="H21" s="92"/>
+      <c r="I21" s="92"/>
+      <c r="J21" s="92"/>
+      <c r="K21" s="92" t="s">
         <v>94</v>
       </c>
-      <c r="L21" s="86"/>
-      <c r="M21" s="86"/>
-      <c r="N21" s="86"/>
-      <c r="O21" s="86" t="s">
+      <c r="L21" s="92"/>
+      <c r="M21" s="92"/>
+      <c r="N21" s="92"/>
+      <c r="O21" s="92" t="s">
         <v>95</v>
       </c>
-      <c r="P21" s="86"/>
-      <c r="Q21" s="86"/>
-      <c r="R21" s="155"/>
+      <c r="P21" s="92"/>
+      <c r="Q21" s="92"/>
+      <c r="R21" s="145"/>
     </row>
     <row r="22" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
       <c r="B22">
         <v>4</v>
       </c>
-      <c r="C22" s="78" t="s">
+      <c r="C22" s="147" t="s">
         <v>90</v>
       </c>
-      <c r="D22" s="79"/>
-      <c r="E22" s="79"/>
-      <c r="F22" s="79"/>
-      <c r="G22" s="79"/>
+      <c r="D22" s="148"/>
+      <c r="E22" s="148"/>
+      <c r="F22" s="148"/>
+      <c r="G22" s="148"/>
       <c r="H22" s="69" t="s">
         <v>78</v>
       </c>
-      <c r="I22" s="79" t="s">
+      <c r="I22" s="148" t="s">
         <v>83</v>
       </c>
-      <c r="J22" s="79"/>
-      <c r="K22" s="79"/>
-      <c r="L22" s="79"/>
+      <c r="J22" s="148"/>
+      <c r="K22" s="148"/>
+      <c r="L22" s="148"/>
       <c r="M22" s="69" t="s">
         <v>78</v>
       </c>
@@ -3612,12 +3602,6 @@
     </row>
   </sheetData>
   <mergeCells count="22">
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:N21"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="G19:I19"/>
     <mergeCell ref="C20:R20"/>
@@ -3634,6 +3618,12 @@
     <mergeCell ref="C14:F14"/>
     <mergeCell ref="H14:K14"/>
     <mergeCell ref="M14:P14"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:N21"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/can上层通信协议.xlsx
+++ b/can上层通信协议.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28324"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\DEV\FanArray\CODE\FA_Ctrl\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\FanArray\CODE\FA_Ctrl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F231857-7BD2-44F3-88D7-49F5D6341D82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898AD1EF-813A-4162-B9BA-C770DFE8500B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-24285" yWindow="2865" windowWidth="19740" windowHeight="13950" activeTab="1" xr2:uid="{33FD23F6-9F23-4515-98A3-37DCFD7DD961}"/>
+    <workbookView xWindow="2610" yWindow="1700" windowWidth="21600" windowHeight="13210" activeTab="1" xr2:uid="{33FD23F6-9F23-4515-98A3-37DCFD7DD961}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -55,7 +55,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="96">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="108">
   <si>
     <t>遥控帧</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -279,10 +279,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>风机模块id</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>0x01</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -304,10 +300,6 @@
   </si>
   <si>
     <t>5/6 = 失/使能跟踪曲线</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>7 = 保存参数</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
@@ -441,14 +433,6 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>open/close</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>rpm</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>m</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -461,30 +445,10 @@
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>txid</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>rxid</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>dlc</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>系统模式</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
   <si>
-    <t>同上 + 8=上传本机状态；9=停止上传、A=上传转速</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
-    <t>rpm1</t>
-    <phoneticPr fontId="6" type="noConversion"/>
-  </si>
-  <si>
     <t>rpm2</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
@@ -494,6 +458,93 @@
   </si>
   <si>
     <t>rpm4</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>通
+讯
+测
+试</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>rpm1_real</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>rpm1_want</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>请求重发数据</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>1=跟踪曲线</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>0x0E-a帧     0x0F-b帧</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>风机1&amp;2放a帧、3&amp;4放b帧</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>同上 + 8=上传本机状态；9=使能上传转速</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>7 = 保存参数，A=使能oled，B使能按键</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>电机测试</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>按钮模式</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>I</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>D</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>最大rpm</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>参数设定</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>a</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>x</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>=</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>：</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>rpm1——real</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>r/txid</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
 </sst>
@@ -504,7 +555,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -591,8 +642,15 @@
       <family val="2"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="9"/>
+      <color theme="1"/>
+      <name val="微软雅黑"/>
+      <family val="2"/>
+      <charset val="134"/>
+    </font>
   </fonts>
-  <fills count="17">
+  <fills count="18">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -689,6 +747,12 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-9.9978637043366805E-2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="51">
     <border>
@@ -1303,7 +1367,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="155">
+  <cellXfs count="176">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1514,9 +1578,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1535,16 +1596,154 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1578,9 +1777,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1592,63 +1788,6 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1658,116 +1797,104 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="50" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -2345,152 +2472,152 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D80C86E-B8D5-4F55-A52E-43C4564E8A86}">
   <dimension ref="D1:P44"/>
-  <sheetFormatPr defaultColWidth="9.21875" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.23046875" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="3" width="9.21875" style="1"/>
-    <col min="4" max="4" width="5.21875" style="1" customWidth="1"/>
-    <col min="5" max="5" width="4.21875" style="1" customWidth="1"/>
-    <col min="6" max="6" width="6.109375" style="1" customWidth="1"/>
+    <col min="1" max="3" width="9.23046875" style="1"/>
+    <col min="4" max="4" width="5.23046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.23046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.07421875" style="1" customWidth="1"/>
     <col min="7" max="7" width="17" style="1" customWidth="1"/>
     <col min="8" max="8" width="11" style="2" customWidth="1"/>
-    <col min="9" max="9" width="0.109375" style="2" hidden="1" customWidth="1"/>
-    <col min="10" max="10" width="18.5546875" style="1" customWidth="1"/>
-    <col min="11" max="11" width="25.44140625" style="1" customWidth="1"/>
-    <col min="12" max="12" width="10.33203125" style="1" customWidth="1"/>
-    <col min="13" max="13" width="25.88671875" style="1" customWidth="1"/>
-    <col min="14" max="14" width="6.88671875" style="1" customWidth="1"/>
-    <col min="15" max="15" width="7.33203125" style="1" customWidth="1"/>
-    <col min="16" max="16384" width="9.21875" style="1"/>
+    <col min="9" max="9" width="7.421875E-2" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.53515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.4609375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.3046875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="25.84375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.84375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.3046875" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.23046875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="4:16" x14ac:dyDescent="0.3">
+    <row r="1" spans="4:16" x14ac:dyDescent="0.45">
       <c r="M1"/>
       <c r="N1"/>
     </row>
-    <row r="2" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="3" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="2" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="3" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="F3" s="55" t="s">
         <v>55</v>
       </c>
       <c r="G3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="96" t="s">
+      <c r="H3" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="97"/>
-      <c r="J3" s="98"/>
+      <c r="I3" s="104"/>
+      <c r="J3" s="105"/>
       <c r="K3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="L3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="90" t="s">
+      <c r="M3" s="135" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="91"/>
+      <c r="N3" s="136"/>
       <c r="O3" s="32" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="4" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D4" s="78" t="s">
+    <row r="4" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="D4" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="106" t="s">
+      <c r="E4" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="115">
+      <c r="F4" s="140">
         <v>2</v>
       </c>
-      <c r="G4" s="81" t="s">
-        <v>64</v>
-      </c>
-      <c r="H4" s="111" t="s">
+      <c r="G4" s="126" t="s">
+        <v>62</v>
+      </c>
+      <c r="H4" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="112"/>
+      <c r="I4" s="113"/>
       <c r="J4" s="68" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="K4" s="56" t="s">
-        <v>58</v>
-      </c>
-      <c r="L4" s="127" t="s">
+      <c r="L4" s="82" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="84" t="s">
+      <c r="M4" s="129" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="130"/>
-      <c r="O4" s="135" t="s">
+      <c r="N4" s="119"/>
+      <c r="O4" s="124" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="5" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D5" s="79"/>
-      <c r="E5" s="107"/>
-      <c r="F5" s="116"/>
-      <c r="G5" s="82"/>
-      <c r="H5" s="113"/>
-      <c r="I5" s="114"/>
-      <c r="J5" s="133" t="s">
-        <v>72</v>
+    <row r="5" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="D5" s="106"/>
+      <c r="E5" s="108"/>
+      <c r="F5" s="141"/>
+      <c r="G5" s="127"/>
+      <c r="H5" s="93"/>
+      <c r="I5" s="94"/>
+      <c r="J5" s="122" t="s">
+        <v>70</v>
       </c>
       <c r="K5" s="47" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" s="83"/>
+      <c r="M5" s="130"/>
+      <c r="N5" s="120"/>
+      <c r="O5" s="114"/>
+    </row>
+    <row r="6" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="D6" s="106"/>
+      <c r="E6" s="108"/>
+      <c r="F6" s="141"/>
+      <c r="G6" s="127"/>
+      <c r="H6" s="93"/>
+      <c r="I6" s="94"/>
+      <c r="J6" s="122"/>
+      <c r="K6" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="L5" s="128"/>
-      <c r="M5" s="85"/>
-      <c r="N5" s="131"/>
-      <c r="O5" s="118"/>
-    </row>
-    <row r="6" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D6" s="79"/>
-      <c r="E6" s="107"/>
-      <c r="F6" s="116"/>
-      <c r="G6" s="82"/>
-      <c r="H6" s="113"/>
-      <c r="I6" s="114"/>
-      <c r="J6" s="133"/>
-      <c r="K6" s="47" t="s">
-        <v>62</v>
-      </c>
-      <c r="L6" s="128"/>
-      <c r="M6" s="85"/>
-      <c r="N6" s="131"/>
-      <c r="O6" s="118"/>
-    </row>
-    <row r="7" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D7" s="79"/>
-      <c r="E7" s="107"/>
-      <c r="F7" s="117"/>
-      <c r="G7" s="83"/>
-      <c r="H7" s="113"/>
-      <c r="I7" s="114"/>
-      <c r="J7" s="134"/>
+      <c r="L6" s="83"/>
+      <c r="M6" s="130"/>
+      <c r="N6" s="120"/>
+      <c r="O6" s="114"/>
+    </row>
+    <row r="7" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="D7" s="106"/>
+      <c r="E7" s="108"/>
+      <c r="F7" s="142"/>
+      <c r="G7" s="128"/>
+      <c r="H7" s="93"/>
+      <c r="I7" s="94"/>
+      <c r="J7" s="123"/>
       <c r="K7" s="48" t="s">
-        <v>63</v>
-      </c>
-      <c r="L7" s="129"/>
-      <c r="M7" s="85"/>
-      <c r="N7" s="132"/>
-      <c r="O7" s="118"/>
-    </row>
-    <row r="8" spans="4:16" ht="47.1" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D8" s="79"/>
-      <c r="E8" s="107"/>
-      <c r="F8" s="108">
+        <v>95</v>
+      </c>
+      <c r="L7" s="84"/>
+      <c r="M7" s="130"/>
+      <c r="N7" s="121"/>
+      <c r="O7" s="114"/>
+    </row>
+    <row r="8" spans="4:16" ht="47.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D8" s="106"/>
+      <c r="E8" s="108"/>
+      <c r="F8" s="85">
         <v>8</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="113"/>
-      <c r="I8" s="114"/>
+      <c r="H8" s="93"/>
+      <c r="I8" s="94"/>
       <c r="J8" s="57" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="K8" s="35" t="s">
         <v>36</v>
@@ -2498,46 +2625,46 @@
       <c r="L8" s="28">
         <v>2</v>
       </c>
-      <c r="M8" s="85"/>
+      <c r="M8" s="130"/>
       <c r="N8" s="33"/>
-      <c r="O8" s="118" t="s">
+      <c r="O8" s="114" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="9" spans="4:16" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D9" s="79"/>
-      <c r="E9" s="107"/>
-      <c r="F9" s="109"/>
+    <row r="9" spans="4:16" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D9" s="106"/>
+      <c r="E9" s="108"/>
+      <c r="F9" s="86"/>
       <c r="G9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="113"/>
-      <c r="I9" s="114"/>
+      <c r="H9" s="93"/>
+      <c r="I9" s="94"/>
       <c r="J9" s="41" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="K9" s="16" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="L9" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="86"/>
+      <c r="M9" s="131"/>
       <c r="N9" s="34"/>
-      <c r="O9" s="136"/>
+      <c r="O9" s="125"/>
       <c r="P9" s="1" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="10" spans="4:16" ht="3" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D10" s="79"/>
-      <c r="E10" s="107"/>
-      <c r="F10" s="110"/>
+    <row r="10" spans="4:16" ht="3" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D10" s="106"/>
+      <c r="E10" s="108"/>
+      <c r="F10" s="87"/>
       <c r="G10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="113"/>
-      <c r="I10" s="114"/>
+      <c r="H10" s="93"/>
+      <c r="I10" s="94"/>
       <c r="J10" s="8" t="s">
         <v>15</v>
       </c>
@@ -2549,81 +2676,81 @@
       </c>
       <c r="O10" s="15"/>
     </row>
-    <row r="11" spans="4:16" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="D11" s="79"/>
-      <c r="E11" s="103" t="s">
+    <row r="11" spans="4:16" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="D11" s="106"/>
+      <c r="E11" s="88" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="21">
         <v>2</v>
       </c>
       <c r="G11" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="H11" s="120" t="s">
-        <v>77</v>
-      </c>
-      <c r="I11" s="121"/>
+        <v>63</v>
+      </c>
+      <c r="H11" s="91" t="s">
+        <v>75</v>
+      </c>
+      <c r="I11" s="92"/>
       <c r="J11" s="42" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="K11" s="67" t="s">
-        <v>91</v>
+        <v>94</v>
       </c>
       <c r="L11" s="30"/>
-      <c r="M11" s="124" t="s">
+      <c r="M11" s="116" t="s">
         <v>22</v>
       </c>
       <c r="N11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="O11" s="118" t="s">
+      <c r="O11" s="114" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="4:16" x14ac:dyDescent="0.3">
-      <c r="D12" s="79"/>
-      <c r="E12" s="104"/>
-      <c r="F12" s="99">
+    <row r="12" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="D12" s="106"/>
+      <c r="E12" s="89"/>
+      <c r="F12" s="97">
         <v>8</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="113"/>
-      <c r="I12" s="114"/>
+      <c r="H12" s="93"/>
+      <c r="I12" s="94"/>
       <c r="J12" s="58" t="s">
-        <v>74</v>
-      </c>
-      <c r="K12" s="101" t="s">
+        <v>72</v>
+      </c>
+      <c r="K12" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="94" t="s">
-        <v>70</v>
-      </c>
-      <c r="M12" s="125"/>
-      <c r="N12" s="92"/>
-      <c r="O12" s="118"/>
-    </row>
-    <row r="13" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D13" s="80"/>
-      <c r="E13" s="105"/>
-      <c r="F13" s="100"/>
+      <c r="L12" s="138" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" s="117"/>
+      <c r="N12" s="76"/>
+      <c r="O12" s="114"/>
+    </row>
+    <row r="13" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D13" s="78"/>
+      <c r="E13" s="90"/>
+      <c r="F13" s="98"/>
       <c r="G13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="122"/>
-      <c r="I13" s="123"/>
+      <c r="H13" s="95"/>
+      <c r="I13" s="96"/>
       <c r="J13" s="44" t="s">
-        <v>76</v>
-      </c>
-      <c r="K13" s="102"/>
-      <c r="L13" s="95"/>
-      <c r="M13" s="126"/>
-      <c r="N13" s="93"/>
-      <c r="O13" s="119"/>
-    </row>
-    <row r="14" spans="4:16" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+      <c r="K13" s="100"/>
+      <c r="L13" s="139"/>
+      <c r="M13" s="118"/>
+      <c r="N13" s="137"/>
+      <c r="O13" s="115"/>
+    </row>
+    <row r="14" spans="4:16" x14ac:dyDescent="0.45">
       <c r="D14"/>
       <c r="E14"/>
       <c r="F14"/>
@@ -2634,7 +2761,7 @@
       <c r="K14"/>
       <c r="L14"/>
     </row>
-    <row r="15" spans="4:16" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="15" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="D15"/>
       <c r="E15"/>
       <c r="F15"/>
@@ -2645,26 +2772,26 @@
       <c r="K15"/>
       <c r="L15"/>
     </row>
-    <row r="16" spans="4:16" ht="32.450000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D16" s="78" t="s">
+    <row r="16" spans="4:16" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D16" s="77" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="87"/>
+      <c r="E16" s="132"/>
       <c r="F16" s="59">
         <v>8</v>
       </c>
       <c r="G16" s="61" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="H16" s="62" t="s">
-        <v>56</v>
+        <v>43</v>
       </c>
       <c r="I16" s="37"/>
       <c r="J16" s="45" t="s">
-        <v>31</v>
+        <v>92</v>
       </c>
       <c r="K16" s="27" t="s">
-        <v>11</v>
+        <v>93</v>
       </c>
       <c r="L16" s="31">
         <v>2</v>
@@ -2674,86 +2801,88 @@
       </c>
       <c r="N16" s="14"/>
     </row>
-    <row r="17" spans="4:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D17" s="79"/>
-      <c r="E17" s="88"/>
+    <row r="17" spans="4:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D17" s="106"/>
+      <c r="E17" s="133"/>
       <c r="F17" s="60">
         <v>8</v>
       </c>
       <c r="G17" s="4" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="H17" s="63" t="s">
         <v>43</v>
       </c>
       <c r="I17" s="9"/>
       <c r="J17" s="65" t="s">
+        <v>65</v>
+      </c>
+      <c r="K17" s="66" t="s">
         <v>67</v>
-      </c>
-      <c r="K17" s="66" t="s">
-        <v>69</v>
       </c>
       <c r="L17" s="64"/>
       <c r="N17" s="14"/>
     </row>
-    <row r="18" spans="4:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D18" s="80"/>
-      <c r="E18" s="89"/>
+    <row r="18" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D18" s="78"/>
+      <c r="E18" s="134"/>
       <c r="F18" s="60">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G18" s="61" t="s">
-        <v>44</v>
+        <v>90</v>
       </c>
       <c r="H18" s="50" t="s">
         <v>43</v>
       </c>
       <c r="I18" s="36"/>
       <c r="J18" s="26" t="s">
-        <v>59</v>
-      </c>
-      <c r="K18" s="27"/>
+        <v>58</v>
+      </c>
+      <c r="K18" s="27" t="s">
+        <v>91</v>
+      </c>
       <c r="L18" s="64"/>
       <c r="M18" s="13"/>
       <c r="N18" s="14"/>
     </row>
-    <row r="23" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="23" spans="4:14" x14ac:dyDescent="0.45">
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="24" spans="4:14" x14ac:dyDescent="0.45">
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="25" spans="4:14" x14ac:dyDescent="0.45">
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="26" spans="4:14" x14ac:dyDescent="0.45">
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="27" spans="4:14" x14ac:dyDescent="0.45">
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="4:14" x14ac:dyDescent="0.3">
+    <row r="28" spans="4:14" x14ac:dyDescent="0.45">
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="4:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35"/>
-    <row r="30" spans="4:14" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D30" s="137"/>
-      <c r="E30" s="138"/>
-      <c r="F30" s="139"/>
+    <row r="29" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="30" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D30" s="79"/>
+      <c r="E30" s="80"/>
+      <c r="F30" s="81"/>
       <c r="G30" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="96" t="s">
+      <c r="H30" s="103" t="s">
         <v>3</v>
       </c>
-      <c r="I30" s="97"/>
-      <c r="J30" s="98"/>
+      <c r="I30" s="104"/>
+      <c r="J30" s="105"/>
       <c r="K30" s="11" t="s">
         <v>2</v>
       </c>
@@ -2761,89 +2890,89 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D31" s="78" t="s">
+    <row r="31" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D31" s="77" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="106" t="s">
+      <c r="E31" s="107" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="142" t="s">
+      <c r="F31" s="109" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="111" t="s">
+      <c r="H31" s="112" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="112"/>
+      <c r="I31" s="113"/>
       <c r="J31" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="K31" s="127" t="s">
+      <c r="K31" s="82" t="s">
         <v>52</v>
       </c>
-      <c r="L31" s="127">
+      <c r="L31" s="82">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="4:14" x14ac:dyDescent="0.3">
-      <c r="D32" s="79"/>
-      <c r="E32" s="107"/>
-      <c r="F32" s="143"/>
+    <row r="32" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D32" s="106"/>
+      <c r="E32" s="108"/>
+      <c r="F32" s="110"/>
       <c r="G32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="113"/>
-      <c r="I32" s="114"/>
+      <c r="H32" s="93"/>
+      <c r="I32" s="94"/>
       <c r="J32" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K32" s="128"/>
-      <c r="L32" s="128"/>
-    </row>
-    <row r="33" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D33" s="79"/>
-      <c r="E33" s="107"/>
-      <c r="F33" s="143"/>
+      <c r="K32" s="83"/>
+      <c r="L32" s="83"/>
+    </row>
+    <row r="33" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D33" s="106"/>
+      <c r="E33" s="108"/>
+      <c r="F33" s="110"/>
       <c r="G33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H33" s="113"/>
-      <c r="I33" s="114"/>
+      <c r="H33" s="93"/>
+      <c r="I33" s="94"/>
       <c r="J33" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="128"/>
-      <c r="L33" s="128"/>
-    </row>
-    <row r="34" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D34" s="79"/>
-      <c r="E34" s="107"/>
-      <c r="F34" s="144"/>
+      <c r="K33" s="83"/>
+      <c r="L33" s="83"/>
+    </row>
+    <row r="34" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D34" s="106"/>
+      <c r="E34" s="108"/>
+      <c r="F34" s="111"/>
       <c r="G34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="113"/>
-      <c r="I34" s="114"/>
+      <c r="H34" s="93"/>
+      <c r="I34" s="94"/>
       <c r="J34" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="129"/>
-      <c r="L34" s="129"/>
-    </row>
-    <row r="35" spans="4:12" ht="33" x14ac:dyDescent="0.3">
-      <c r="D35" s="79"/>
-      <c r="E35" s="107"/>
-      <c r="F35" s="108" t="s">
+      <c r="K34" s="84"/>
+      <c r="L34" s="84"/>
+    </row>
+    <row r="35" spans="4:12" ht="33" x14ac:dyDescent="0.45">
+      <c r="D35" s="106"/>
+      <c r="E35" s="108"/>
+      <c r="F35" s="85" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H35" s="113"/>
-      <c r="I35" s="114"/>
+      <c r="H35" s="93"/>
+      <c r="I35" s="94"/>
       <c r="J35" s="40" t="s">
         <v>34</v>
       </c>
@@ -2854,15 +2983,15 @@
         <v>2</v>
       </c>
     </row>
-    <row r="36" spans="4:12" ht="31.35" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D36" s="79"/>
-      <c r="E36" s="107"/>
-      <c r="F36" s="109"/>
+    <row r="36" spans="4:12" ht="31.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D36" s="106"/>
+      <c r="E36" s="108"/>
+      <c r="F36" s="86"/>
       <c r="G36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H36" s="113"/>
-      <c r="I36" s="114"/>
+      <c r="H36" s="93"/>
+      <c r="I36" s="94"/>
       <c r="J36" s="41" t="s">
         <v>35</v>
       </c>
@@ -2873,15 +3002,15 @@
         <v>19</v>
       </c>
     </row>
-    <row r="37" spans="4:12" ht="0.95" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D37" s="79"/>
-      <c r="E37" s="107"/>
-      <c r="F37" s="110"/>
+    <row r="37" spans="4:12" ht="1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D37" s="106"/>
+      <c r="E37" s="108"/>
+      <c r="F37" s="87"/>
       <c r="G37" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="113"/>
-      <c r="I37" s="114"/>
+      <c r="H37" s="93"/>
+      <c r="I37" s="94"/>
       <c r="J37" s="8" t="s">
         <v>15</v>
       </c>
@@ -2892,9 +3021,9 @@
         <v>18</v>
       </c>
     </row>
-    <row r="38" spans="4:12" ht="17.25" thickTop="1" x14ac:dyDescent="0.3">
-      <c r="D38" s="79"/>
-      <c r="E38" s="103" t="s">
+    <row r="38" spans="4:12" ht="17" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="D38" s="106"/>
+      <c r="E38" s="88" t="s">
         <v>5</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -2903,10 +3032,10 @@
       <c r="G38" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="120" t="s">
+      <c r="H38" s="91" t="s">
         <v>53</v>
       </c>
-      <c r="I38" s="121"/>
+      <c r="I38" s="92"/>
       <c r="J38" s="42" t="s">
         <v>50</v>
       </c>
@@ -2917,66 +3046,66 @@
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D39" s="79"/>
-      <c r="E39" s="104"/>
-      <c r="F39" s="99" t="s">
+    <row r="39" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D39" s="106"/>
+      <c r="E39" s="89"/>
+      <c r="F39" s="97" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H39" s="113"/>
-      <c r="I39" s="114"/>
+      <c r="H39" s="93"/>
+      <c r="I39" s="94"/>
       <c r="J39" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="101" t="s">
+      <c r="K39" s="99" t="s">
         <v>38</v>
       </c>
-      <c r="L39" s="140">
+      <c r="L39" s="101">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D40" s="80"/>
-      <c r="E40" s="105"/>
-      <c r="F40" s="100"/>
+    <row r="40" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D40" s="78"/>
+      <c r="E40" s="90"/>
+      <c r="F40" s="98"/>
       <c r="G40" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H40" s="122"/>
-      <c r="I40" s="123"/>
+      <c r="H40" s="95"/>
+      <c r="I40" s="96"/>
       <c r="J40" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="K40" s="102"/>
-      <c r="L40" s="141"/>
-    </row>
-    <row r="41" spans="4:12" x14ac:dyDescent="0.3">
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="92"/>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="92"/>
-    </row>
-    <row r="42" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D42" s="92"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="92"/>
-      <c r="G42" s="92"/>
-      <c r="H42" s="92"/>
-      <c r="I42" s="92"/>
-      <c r="J42" s="92"/>
-      <c r="K42" s="92"/>
-      <c r="L42" s="92"/>
-    </row>
-    <row r="43" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D43" s="78" t="s">
+      <c r="K40" s="100"/>
+      <c r="L40" s="102"/>
+    </row>
+    <row r="41" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D41" s="76"/>
+      <c r="E41" s="76"/>
+      <c r="F41" s="76"/>
+      <c r="G41" s="76"/>
+      <c r="H41" s="76"/>
+      <c r="I41" s="76"/>
+      <c r="J41" s="76"/>
+      <c r="K41" s="76"/>
+      <c r="L41" s="76"/>
+    </row>
+    <row r="42" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D42" s="76"/>
+      <c r="E42" s="76"/>
+      <c r="F42" s="76"/>
+      <c r="G42" s="76"/>
+      <c r="H42" s="76"/>
+      <c r="I42" s="76"/>
+      <c r="J42" s="76"/>
+      <c r="K42" s="76"/>
+      <c r="L42" s="76"/>
+    </row>
+    <row r="43" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D43" s="77" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="25"/>
@@ -3000,8 +3129,8 @@
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="4:12" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="D44" s="80"/>
+    <row r="44" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D44" s="78"/>
       <c r="E44" s="25"/>
       <c r="F44" s="46" t="s">
         <v>0</v>
@@ -3025,6 +3154,30 @@
     </row>
   </sheetData>
   <mergeCells count="40">
+    <mergeCell ref="D16:D18"/>
+    <mergeCell ref="G4:G7"/>
+    <mergeCell ref="M4:M9"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="M3:N3"/>
+    <mergeCell ref="N12:N13"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="H3:J3"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="D4:D13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="E11:E13"/>
+    <mergeCell ref="E4:E10"/>
+    <mergeCell ref="F8:F10"/>
+    <mergeCell ref="H4:I10"/>
+    <mergeCell ref="F4:F7"/>
+    <mergeCell ref="O11:O13"/>
+    <mergeCell ref="H11:I13"/>
+    <mergeCell ref="M11:M13"/>
+    <mergeCell ref="L4:L7"/>
+    <mergeCell ref="N4:N7"/>
+    <mergeCell ref="J5:J7"/>
+    <mergeCell ref="O4:O7"/>
+    <mergeCell ref="O8:O9"/>
     <mergeCell ref="D41:L42"/>
     <mergeCell ref="D43:D44"/>
     <mergeCell ref="D30:F30"/>
@@ -3041,30 +3194,6 @@
     <mergeCell ref="E31:E37"/>
     <mergeCell ref="F31:F34"/>
     <mergeCell ref="H31:I37"/>
-    <mergeCell ref="O11:O13"/>
-    <mergeCell ref="H11:I13"/>
-    <mergeCell ref="M11:M13"/>
-    <mergeCell ref="L4:L7"/>
-    <mergeCell ref="N4:N7"/>
-    <mergeCell ref="J5:J7"/>
-    <mergeCell ref="O4:O7"/>
-    <mergeCell ref="O8:O9"/>
-    <mergeCell ref="D16:D18"/>
-    <mergeCell ref="G4:G7"/>
-    <mergeCell ref="M4:M9"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="M3:N3"/>
-    <mergeCell ref="N12:N13"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="H3:J3"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="D4:D13"/>
-    <mergeCell ref="K12:K13"/>
-    <mergeCell ref="E11:E13"/>
-    <mergeCell ref="E4:E10"/>
-    <mergeCell ref="F8:F10"/>
-    <mergeCell ref="H4:I10"/>
-    <mergeCell ref="F4:F7"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3075,555 +3204,769 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8521510C-1B37-40AB-AFA2-021412ADBA84}">
-  <dimension ref="B4:R24"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A4:AB37"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="3" max="18" width="2.77734375" customWidth="1"/>
+    <col min="3" max="18" width="2.765625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C4">
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A4" s="174"/>
+      <c r="B4" s="168"/>
+      <c r="C4" s="169"/>
+      <c r="D4" s="169"/>
+      <c r="E4" s="169"/>
+      <c r="F4" s="169"/>
+      <c r="G4" s="169"/>
+      <c r="H4" s="169"/>
+      <c r="I4" s="169"/>
+      <c r="J4" s="169"/>
+      <c r="K4" s="169"/>
+      <c r="L4" s="169"/>
+      <c r="M4" s="169"/>
+      <c r="N4" s="169"/>
+      <c r="O4" s="169"/>
+      <c r="P4" s="169"/>
+      <c r="Q4" s="169"/>
+      <c r="R4" s="169"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A5" s="173"/>
+      <c r="B5" s="168"/>
+      <c r="C5" s="170"/>
+      <c r="D5" s="170"/>
+      <c r="E5" s="170"/>
+      <c r="F5" s="169"/>
+      <c r="G5" s="170"/>
+      <c r="H5" s="170"/>
+      <c r="I5" s="170"/>
+      <c r="J5" s="169"/>
+      <c r="K5" s="171"/>
+      <c r="L5" s="169"/>
+      <c r="M5" s="172"/>
+      <c r="N5" s="169"/>
+      <c r="O5" s="169"/>
+      <c r="P5" s="169"/>
+      <c r="Q5" s="173"/>
+      <c r="R5" s="173"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A6" s="173"/>
+      <c r="B6" s="168"/>
+      <c r="C6" s="170"/>
+      <c r="D6" s="170"/>
+      <c r="E6" s="170"/>
+      <c r="F6" s="170"/>
+      <c r="G6" s="170"/>
+      <c r="H6" s="170"/>
+      <c r="I6" s="170"/>
+      <c r="J6" s="170"/>
+      <c r="K6" s="170"/>
+      <c r="L6" s="170"/>
+      <c r="M6" s="170"/>
+      <c r="N6" s="170"/>
+      <c r="O6" s="170"/>
+      <c r="P6" s="170"/>
+      <c r="Q6" s="170"/>
+      <c r="R6" s="170"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A7" s="173"/>
+      <c r="B7" s="168"/>
+      <c r="C7" s="173"/>
+      <c r="D7" s="173"/>
+      <c r="E7" s="173"/>
+      <c r="F7" s="173"/>
+      <c r="G7" s="169"/>
+      <c r="H7" s="173"/>
+      <c r="I7" s="173"/>
+      <c r="J7" s="173"/>
+      <c r="K7" s="173"/>
+      <c r="L7" s="169"/>
+      <c r="M7" s="173"/>
+      <c r="N7" s="173"/>
+      <c r="O7" s="173"/>
+      <c r="P7" s="173"/>
+      <c r="Q7" s="169"/>
+      <c r="R7" s="169"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A8" s="173"/>
+      <c r="B8" s="168"/>
+      <c r="C8" s="170"/>
+      <c r="D8" s="170"/>
+      <c r="E8" s="170"/>
+      <c r="F8" s="170"/>
+      <c r="G8" s="170"/>
+      <c r="H8" s="169"/>
+      <c r="I8" s="170"/>
+      <c r="J8" s="170"/>
+      <c r="K8" s="170"/>
+      <c r="L8" s="170"/>
+      <c r="M8" s="169"/>
+      <c r="N8" s="169"/>
+      <c r="O8" s="169"/>
+      <c r="P8" s="169"/>
+      <c r="Q8" s="169"/>
+      <c r="R8" s="169"/>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="B11" s="168"/>
+      <c r="C11" s="169"/>
+      <c r="D11" s="169"/>
+      <c r="E11" s="169"/>
+      <c r="F11" s="169"/>
+      <c r="G11" s="169"/>
+      <c r="H11" s="169"/>
+      <c r="I11" s="169"/>
+      <c r="J11" s="169"/>
+      <c r="K11" s="169"/>
+      <c r="L11" s="169"/>
+      <c r="M11" s="169"/>
+      <c r="N11" s="169"/>
+      <c r="O11" s="169"/>
+      <c r="P11" s="169"/>
+      <c r="Q11" s="169"/>
+      <c r="R11" s="169"/>
+    </row>
+    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="175" t="s">
+        <v>87</v>
+      </c>
+      <c r="B12" s="168"/>
+      <c r="C12" s="170"/>
+      <c r="D12" s="170"/>
+      <c r="E12" s="170"/>
+      <c r="F12" s="169"/>
+      <c r="G12" s="170"/>
+      <c r="H12" s="170"/>
+      <c r="I12" s="170"/>
+      <c r="J12" s="169"/>
+      <c r="K12" s="171"/>
+      <c r="L12" s="169"/>
+      <c r="M12" s="172"/>
+      <c r="N12" s="169"/>
+      <c r="O12" s="169"/>
+      <c r="P12" s="169"/>
+      <c r="Q12" s="173"/>
+      <c r="R12" s="173"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A13" s="152"/>
+      <c r="B13" s="168"/>
+      <c r="C13" s="170"/>
+      <c r="D13" s="170"/>
+      <c r="E13" s="170"/>
+      <c r="F13" s="170"/>
+      <c r="G13" s="170"/>
+      <c r="H13" s="170"/>
+      <c r="I13" s="170"/>
+      <c r="J13" s="170"/>
+      <c r="K13" s="170"/>
+      <c r="L13" s="170"/>
+      <c r="M13" s="170"/>
+      <c r="N13" s="170"/>
+      <c r="O13" s="170"/>
+      <c r="P13" s="170"/>
+      <c r="Q13" s="170"/>
+      <c r="R13" s="170"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A14" s="152"/>
+      <c r="B14" s="168"/>
+      <c r="C14" s="173"/>
+      <c r="D14" s="173"/>
+      <c r="E14" s="173"/>
+      <c r="F14" s="173"/>
+      <c r="G14" s="169"/>
+      <c r="H14" s="173"/>
+      <c r="I14" s="173"/>
+      <c r="J14" s="173"/>
+      <c r="K14" s="173"/>
+      <c r="L14" s="169"/>
+      <c r="M14" s="173"/>
+      <c r="N14" s="173"/>
+      <c r="O14" s="173"/>
+      <c r="P14" s="173"/>
+      <c r="Q14" s="169"/>
+      <c r="R14" s="169"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A15" s="152"/>
+      <c r="B15" s="168"/>
+      <c r="C15" s="170"/>
+      <c r="D15" s="170"/>
+      <c r="E15" s="170"/>
+      <c r="F15" s="170"/>
+      <c r="G15" s="170"/>
+      <c r="H15" s="169"/>
+      <c r="I15" s="170"/>
+      <c r="J15" s="170"/>
+      <c r="K15" s="170"/>
+      <c r="L15" s="170"/>
+      <c r="M15" s="169"/>
+      <c r="N15" s="169"/>
+      <c r="O15" s="169"/>
+      <c r="P15" s="169"/>
+      <c r="Q15" s="169"/>
+      <c r="R15" s="169"/>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A16" s="152"/>
+    </row>
+    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A17" s="152"/>
+    </row>
+    <row r="18" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="153" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="1">
         <v>1</v>
       </c>
-      <c r="D4">
+      <c r="D18" s="1">
         <v>2</v>
       </c>
-      <c r="E4">
+      <c r="E18" s="1">
         <v>3</v>
       </c>
-      <c r="F4">
+      <c r="F18" s="1">
         <v>4</v>
       </c>
-      <c r="G4">
+      <c r="G18" s="1">
         <v>5</v>
       </c>
-      <c r="H4">
+      <c r="H18" s="1">
         <v>6</v>
       </c>
-      <c r="I4">
+      <c r="I18" s="1">
         <v>7</v>
       </c>
-      <c r="J4">
+      <c r="J18" s="1">
         <v>8</v>
       </c>
-      <c r="K4">
+      <c r="K18" s="1">
         <v>9</v>
       </c>
-      <c r="L4">
+      <c r="L18" s="1">
         <v>10</v>
       </c>
-      <c r="M4">
+      <c r="M18" s="1">
         <v>11</v>
       </c>
-      <c r="N4">
+      <c r="N18" s="1">
         <v>12</v>
       </c>
-      <c r="O4">
+      <c r="O18" s="1">
         <v>13</v>
       </c>
-      <c r="P4">
+      <c r="P18" s="1">
         <v>14</v>
       </c>
-      <c r="Q4">
+      <c r="Q18" s="1">
         <v>15</v>
       </c>
-      <c r="R4">
+      <c r="R18" s="1">
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B5">
-        <v>1</v>
-      </c>
-      <c r="C5" s="71"/>
-      <c r="D5" s="72"/>
-      <c r="E5" s="72"/>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-      <c r="J5" s="72"/>
-      <c r="K5" s="72"/>
-      <c r="L5" s="72"/>
-      <c r="M5" s="72"/>
-      <c r="N5" s="72"/>
-      <c r="O5" s="72"/>
-      <c r="P5" s="72"/>
-      <c r="Q5" s="72"/>
-      <c r="R5" s="73"/>
-    </row>
-    <row r="6" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B6">
-        <v>2</v>
-      </c>
-      <c r="C6" s="74"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-      <c r="Q6" s="1"/>
-      <c r="R6" s="75"/>
-    </row>
-    <row r="7" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B7">
-        <v>3</v>
-      </c>
-      <c r="C7" s="146" t="s">
-        <v>79</v>
-      </c>
-      <c r="D7" s="92"/>
-      <c r="E7" s="92"/>
-      <c r="F7" s="92"/>
-      <c r="G7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H7" s="92" t="s">
-        <v>80</v>
-      </c>
-      <c r="I7" s="92"/>
-      <c r="J7" s="92"/>
-      <c r="K7" s="92"/>
-      <c r="L7" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M7" s="92" t="s">
-        <v>81</v>
-      </c>
-      <c r="N7" s="92"/>
-      <c r="O7" s="92"/>
-      <c r="P7" s="92"/>
-      <c r="Q7" s="1"/>
-      <c r="R7" s="75"/>
-    </row>
-    <row r="8" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B8">
-        <v>4</v>
-      </c>
-      <c r="C8" s="154" t="s">
-        <v>82</v>
-      </c>
-      <c r="D8" s="93"/>
-      <c r="E8" s="93"/>
-      <c r="F8" s="93"/>
-      <c r="G8" s="93"/>
-      <c r="H8" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="I8" s="148" t="s">
-        <v>83</v>
-      </c>
-      <c r="J8" s="148"/>
-      <c r="K8" s="148"/>
-      <c r="L8" s="148"/>
-      <c r="M8" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="N8" s="69"/>
-      <c r="O8" s="69"/>
-      <c r="P8" s="69"/>
-      <c r="Q8" s="69" t="s">
-        <v>84</v>
-      </c>
-      <c r="R8" s="15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="11" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C11">
-        <v>1</v>
-      </c>
-      <c r="D11">
-        <v>2</v>
-      </c>
-      <c r="E11">
-        <v>3</v>
-      </c>
-      <c r="F11">
-        <v>4</v>
-      </c>
-      <c r="G11">
-        <v>5</v>
-      </c>
-      <c r="H11">
-        <v>6</v>
-      </c>
-      <c r="I11">
-        <v>7</v>
-      </c>
-      <c r="J11">
-        <v>8</v>
-      </c>
-      <c r="K11">
-        <v>9</v>
-      </c>
-      <c r="L11">
-        <v>10</v>
-      </c>
-      <c r="M11">
-        <v>11</v>
-      </c>
-      <c r="N11">
-        <v>12</v>
-      </c>
-      <c r="O11">
-        <v>13</v>
-      </c>
-      <c r="P11">
-        <v>14</v>
-      </c>
-      <c r="Q11">
-        <v>15</v>
-      </c>
-      <c r="R11">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="12" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>1</v>
-      </c>
-      <c r="C12" s="149" t="s">
-        <v>87</v>
-      </c>
-      <c r="D12" s="150"/>
-      <c r="E12" s="150"/>
-      <c r="F12" s="72" t="s">
-        <v>78</v>
-      </c>
-      <c r="G12" s="150" t="s">
-        <v>88</v>
-      </c>
-      <c r="H12" s="150"/>
-      <c r="I12" s="150"/>
-      <c r="J12" s="72" t="s">
-        <v>78</v>
-      </c>
-      <c r="K12" s="77" t="s">
-        <v>65</v>
-      </c>
-      <c r="L12" s="70" t="s">
-        <v>78</v>
-      </c>
-      <c r="M12" s="76" t="s">
-        <v>89</v>
-      </c>
-      <c r="N12" s="72"/>
-      <c r="O12" s="72"/>
-      <c r="P12" s="72"/>
-      <c r="Q12" s="72"/>
-      <c r="R12" s="73"/>
-    </row>
-    <row r="13" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>2</v>
-      </c>
-      <c r="C13" s="151" t="s">
-        <v>86</v>
-      </c>
-      <c r="D13" s="152"/>
-      <c r="E13" s="152"/>
-      <c r="F13" s="152"/>
-      <c r="G13" s="152"/>
-      <c r="H13" s="152"/>
-      <c r="I13" s="152"/>
-      <c r="J13" s="152"/>
-      <c r="K13" s="152"/>
-      <c r="L13" s="152"/>
-      <c r="M13" s="152"/>
-      <c r="N13" s="152"/>
-      <c r="O13" s="152"/>
-      <c r="P13" s="152"/>
-      <c r="Q13" s="152"/>
-      <c r="R13" s="153"/>
-    </row>
-    <row r="14" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="B14">
-        <v>3</v>
-      </c>
-      <c r="C14" s="146" t="s">
-        <v>79</v>
-      </c>
-      <c r="D14" s="92"/>
-      <c r="E14" s="92"/>
-      <c r="F14" s="92"/>
-      <c r="G14" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="H14" s="92" t="s">
-        <v>80</v>
-      </c>
-      <c r="I14" s="92"/>
-      <c r="J14" s="92"/>
-      <c r="K14" s="92"/>
-      <c r="L14" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="M14" s="92" t="s">
-        <v>81</v>
-      </c>
-      <c r="N14" s="92"/>
-      <c r="O14" s="92"/>
-      <c r="P14" s="92"/>
-      <c r="Q14" s="1"/>
-      <c r="R14" s="75"/>
-    </row>
-    <row r="15" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="B15">
-        <v>4</v>
-      </c>
-      <c r="C15" s="147" t="s">
-        <v>90</v>
-      </c>
-      <c r="D15" s="148"/>
-      <c r="E15" s="148"/>
-      <c r="F15" s="148"/>
-      <c r="G15" s="148"/>
-      <c r="H15" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="I15" s="148" t="s">
-        <v>83</v>
-      </c>
-      <c r="J15" s="148"/>
-      <c r="K15" s="148"/>
-      <c r="L15" s="148"/>
-      <c r="M15" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="N15" s="69"/>
-      <c r="O15" s="69"/>
-      <c r="P15" s="69"/>
-      <c r="Q15" s="69" t="s">
-        <v>84</v>
-      </c>
-      <c r="R15" s="15" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="18" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="C18">
-        <v>1</v>
-      </c>
-      <c r="D18">
-        <v>2</v>
-      </c>
-      <c r="E18">
-        <v>3</v>
-      </c>
-      <c r="F18">
-        <v>4</v>
-      </c>
-      <c r="G18">
-        <v>5</v>
-      </c>
-      <c r="H18">
-        <v>6</v>
-      </c>
-      <c r="I18">
-        <v>7</v>
-      </c>
-      <c r="J18">
-        <v>8</v>
-      </c>
-      <c r="K18">
-        <v>9</v>
-      </c>
-      <c r="L18">
-        <v>10</v>
-      </c>
-      <c r="M18">
-        <v>11</v>
-      </c>
-      <c r="N18">
-        <v>12</v>
-      </c>
-      <c r="O18">
-        <v>13</v>
-      </c>
-      <c r="P18">
-        <v>14</v>
-      </c>
-      <c r="Q18">
-        <v>15</v>
-      </c>
-      <c r="R18">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="2:18" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A19" s="76"/>
       <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" s="149" t="s">
-        <v>87</v>
-      </c>
-      <c r="D19" s="150"/>
-      <c r="E19" s="150"/>
-      <c r="F19" s="72" t="s">
-        <v>78</v>
-      </c>
-      <c r="G19" s="150" t="s">
-        <v>88</v>
-      </c>
-      <c r="H19" s="150"/>
-      <c r="I19" s="150"/>
-      <c r="J19" s="72" t="s">
-        <v>78</v>
-      </c>
-      <c r="K19" s="77" t="s">
-        <v>65</v>
-      </c>
-      <c r="L19" s="70" t="s">
-        <v>78</v>
-      </c>
-      <c r="M19" s="76" t="s">
-        <v>89</v>
-      </c>
-      <c r="N19" s="72"/>
-      <c r="O19" s="72"/>
-      <c r="P19" s="72"/>
-      <c r="Q19" s="72"/>
-      <c r="R19" s="73"/>
-    </row>
-    <row r="20" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C19" s="143" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="144"/>
+      <c r="E19" s="144"/>
+      <c r="F19" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="158"/>
+      <c r="H19" s="158"/>
+      <c r="I19" s="158"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="159"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="75"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="156"/>
+      <c r="R19" s="157"/>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A20" s="76"/>
       <c r="B20">
         <v>2</v>
       </c>
-      <c r="C20" s="151" t="s">
-        <v>86</v>
-      </c>
-      <c r="D20" s="152"/>
-      <c r="E20" s="152"/>
-      <c r="F20" s="152"/>
-      <c r="G20" s="152"/>
-      <c r="H20" s="152"/>
-      <c r="I20" s="152"/>
-      <c r="J20" s="152"/>
-      <c r="K20" s="152"/>
-      <c r="L20" s="152"/>
-      <c r="M20" s="152"/>
-      <c r="N20" s="152"/>
-      <c r="O20" s="152"/>
-      <c r="P20" s="152"/>
-      <c r="Q20" s="152"/>
-      <c r="R20" s="153"/>
-    </row>
-    <row r="21" spans="2:18" x14ac:dyDescent="0.3">
+      <c r="C20" s="145" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="146"/>
+      <c r="E20" s="146"/>
+      <c r="F20" s="146"/>
+      <c r="G20" s="146"/>
+      <c r="H20" s="146"/>
+      <c r="I20" s="146"/>
+      <c r="J20" s="146"/>
+      <c r="K20" s="146"/>
+      <c r="L20" s="146"/>
+      <c r="M20" s="146"/>
+      <c r="N20" s="146"/>
+      <c r="O20" s="146"/>
+      <c r="P20" s="146"/>
+      <c r="Q20" s="146"/>
+      <c r="R20" s="147"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A21" s="76"/>
       <c r="B21">
         <v>3</v>
       </c>
-      <c r="C21" s="146" t="s">
-        <v>92</v>
-      </c>
-      <c r="D21" s="92"/>
-      <c r="E21" s="92"/>
-      <c r="F21" s="92"/>
-      <c r="G21" s="92" t="s">
-        <v>93</v>
-      </c>
-      <c r="H21" s="92"/>
-      <c r="I21" s="92"/>
-      <c r="J21" s="92"/>
-      <c r="K21" s="92" t="s">
-        <v>94</v>
-      </c>
-      <c r="L21" s="92"/>
-      <c r="M21" s="92"/>
-      <c r="N21" s="92"/>
-      <c r="O21" s="92" t="s">
-        <v>95</v>
-      </c>
-      <c r="P21" s="92"/>
-      <c r="Q21" s="92"/>
-      <c r="R21" s="145"/>
-    </row>
-    <row r="22" spans="2:18" ht="17.25" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="C21" s="163" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="164"/>
+      <c r="E21" s="164"/>
+      <c r="F21" s="164"/>
+      <c r="G21" s="164" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="164"/>
+      <c r="I21" s="164"/>
+      <c r="J21" s="164"/>
+      <c r="K21" s="164" t="s">
+        <v>85</v>
+      </c>
+      <c r="L21" s="164"/>
+      <c r="M21" s="164"/>
+      <c r="N21" s="164"/>
+      <c r="O21" s="164" t="s">
+        <v>86</v>
+      </c>
+      <c r="P21" s="164"/>
+      <c r="Q21" s="164"/>
+      <c r="R21" s="165"/>
+    </row>
+    <row r="22" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="76"/>
       <c r="B22">
         <v>4</v>
       </c>
-      <c r="C22" s="147" t="s">
-        <v>90</v>
-      </c>
-      <c r="D22" s="148"/>
-      <c r="E22" s="148"/>
-      <c r="F22" s="148"/>
-      <c r="G22" s="148"/>
+      <c r="C22" s="150" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="149"/>
+      <c r="E22" s="149"/>
+      <c r="F22" s="149"/>
+      <c r="G22" s="149"/>
       <c r="H22" s="69" t="s">
-        <v>78</v>
-      </c>
-      <c r="I22" s="148" t="s">
-        <v>83</v>
-      </c>
-      <c r="J22" s="148"/>
-      <c r="K22" s="148"/>
-      <c r="L22" s="148"/>
+        <v>76</v>
+      </c>
+      <c r="I22" s="149" t="s">
+        <v>97</v>
+      </c>
+      <c r="J22" s="149"/>
+      <c r="K22" s="149"/>
+      <c r="L22" s="149"/>
       <c r="M22" s="69" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="N22" s="69"/>
       <c r="O22" s="69"/>
       <c r="P22" s="69"/>
-      <c r="Q22" s="69" t="s">
+      <c r="Q22" s="69"/>
+      <c r="R22" s="15"/>
+    </row>
+    <row r="26" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1">
+        <v>4</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1">
+        <v>6</v>
+      </c>
+      <c r="I26" s="1">
+        <v>7</v>
+      </c>
+      <c r="J26" s="1">
+        <v>8</v>
+      </c>
+      <c r="K26" s="1">
+        <v>9</v>
+      </c>
+      <c r="L26" s="1">
+        <v>10</v>
+      </c>
+      <c r="M26" s="1">
+        <v>11</v>
+      </c>
+      <c r="N26" s="1">
+        <v>12</v>
+      </c>
+      <c r="O26" s="1">
+        <v>13</v>
+      </c>
+      <c r="P26" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>15</v>
+      </c>
+      <c r="R26" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A27" s="76" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" s="143"/>
+      <c r="D27" s="144"/>
+      <c r="E27" s="144"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="144"/>
+      <c r="H27" s="144"/>
+      <c r="I27" s="144"/>
+      <c r="J27" s="71"/>
+      <c r="K27" s="159"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A28" s="76"/>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28" s="148" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="76"/>
+      <c r="E28" s="76"/>
+      <c r="F28" s="76"/>
+      <c r="G28" s="76" t="s">
         <v>84</v>
       </c>
-      <c r="R22" s="15" t="s">
+      <c r="H28" s="76"/>
+      <c r="I28" s="76"/>
+      <c r="J28" s="76"/>
+      <c r="K28" s="76" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="23" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="G23">
+      <c r="L28" s="76"/>
+      <c r="M28" s="76"/>
+      <c r="N28" s="76"/>
+      <c r="O28" s="76" t="s">
+        <v>86</v>
+      </c>
+      <c r="P28" s="76"/>
+      <c r="Q28" s="76"/>
+      <c r="R28" s="151"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A29" s="76"/>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29" s="163" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="164"/>
+      <c r="E29" s="164"/>
+      <c r="F29" s="164"/>
+      <c r="G29" s="164" t="s">
+        <v>84</v>
+      </c>
+      <c r="H29" s="164"/>
+      <c r="I29" s="164"/>
+      <c r="J29" s="164"/>
+      <c r="K29" s="164" t="s">
+        <v>85</v>
+      </c>
+      <c r="L29" s="164"/>
+      <c r="M29" s="164"/>
+      <c r="N29" s="164"/>
+      <c r="O29" s="164" t="s">
+        <v>86</v>
+      </c>
+      <c r="P29" s="164"/>
+      <c r="Q29" s="164"/>
+      <c r="R29" s="165"/>
+    </row>
+    <row r="30" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="76"/>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30" s="150" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="149"/>
+      <c r="E30" s="149"/>
+      <c r="F30" s="149"/>
+      <c r="G30" s="149"/>
+      <c r="H30" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="I30" s="149" t="s">
+        <v>97</v>
+      </c>
+      <c r="J30" s="149"/>
+      <c r="K30" s="149"/>
+      <c r="L30" s="149"/>
+      <c r="M30" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="N30" s="69"/>
+      <c r="O30" s="160"/>
+      <c r="P30" s="160"/>
+      <c r="Q30" s="69"/>
+      <c r="R30" s="15"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="V31" s="73"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+    </row>
+    <row r="33" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C33" s="69">
         <v>1</v>
       </c>
-      <c r="H23">
+      <c r="D33" s="69">
+        <v>2</v>
+      </c>
+      <c r="E33" s="69">
+        <v>3</v>
+      </c>
+      <c r="F33" s="69">
+        <v>4</v>
+      </c>
+      <c r="G33" s="69">
+        <v>5</v>
+      </c>
+      <c r="H33" s="69">
         <v>6</v>
       </c>
-      <c r="I23">
+      <c r="I33" s="69">
+        <v>7</v>
+      </c>
+      <c r="J33" s="69">
+        <v>8</v>
+      </c>
+      <c r="K33" s="69">
+        <v>9</v>
+      </c>
+      <c r="L33" s="1">
+        <v>10</v>
+      </c>
+      <c r="M33" s="1">
         <v>11</v>
       </c>
-    </row>
-    <row r="24" spans="2:18" x14ac:dyDescent="0.3">
-      <c r="G24">
-        <f>H23-G23</f>
-        <v>5</v>
-      </c>
-      <c r="H24">
-        <f>I23-H23</f>
-        <v>5</v>
+      <c r="N33" s="1">
+        <v>12</v>
+      </c>
+      <c r="O33" s="1">
+        <v>13</v>
+      </c>
+      <c r="P33" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>15</v>
+      </c>
+      <c r="R33" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A34" s="76" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" s="70" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="71" t="s">
+        <v>103</v>
+      </c>
+      <c r="F34" s="71" t="s">
+        <v>105</v>
+      </c>
+      <c r="G34" s="156" t="s">
+        <v>100</v>
+      </c>
+      <c r="H34" s="156"/>
+      <c r="I34" s="156"/>
+      <c r="J34" s="156"/>
+      <c r="K34" s="156"/>
+      <c r="L34" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="M34" s="71"/>
+      <c r="N34" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="O34" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="P34" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q34" s="156"/>
+      <c r="R34" s="157"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A35" s="76"/>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35" s="148" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="155"/>
+      <c r="E35" s="155"/>
+      <c r="F35" s="155"/>
+      <c r="G35" s="154" t="s">
+        <v>76</v>
+      </c>
+      <c r="H35" s="155" t="s">
+        <v>78</v>
+      </c>
+      <c r="I35" s="155"/>
+      <c r="J35" s="155"/>
+      <c r="K35" s="155"/>
+      <c r="L35" s="154" t="s">
+        <v>76</v>
+      </c>
+      <c r="M35" s="155" t="s">
+        <v>79</v>
+      </c>
+      <c r="N35" s="155"/>
+      <c r="O35" s="155"/>
+      <c r="P35" s="155"/>
+      <c r="Q35" s="154"/>
+      <c r="R35" s="74"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A36" s="76"/>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36" s="161"/>
+      <c r="D36" s="166"/>
+      <c r="E36" s="166"/>
+      <c r="F36" s="166"/>
+      <c r="G36" s="166"/>
+      <c r="H36" s="166"/>
+      <c r="I36" s="166"/>
+      <c r="J36" s="166"/>
+      <c r="K36" s="166"/>
+      <c r="L36" s="166"/>
+      <c r="M36" s="166"/>
+      <c r="N36" s="166"/>
+      <c r="O36" s="166"/>
+      <c r="P36" s="166"/>
+      <c r="Q36" s="167"/>
+      <c r="R36" s="162"/>
+    </row>
+    <row r="37" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="76"/>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37" s="150"/>
+      <c r="D37" s="149"/>
+      <c r="E37" s="149"/>
+      <c r="F37" s="149"/>
+      <c r="G37" s="149"/>
+      <c r="H37" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" s="149" t="s">
+        <v>97</v>
+      </c>
+      <c r="J37" s="149"/>
+      <c r="K37" s="149"/>
+      <c r="L37" s="149"/>
+      <c r="M37" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="N37" s="149">
+        <v>250</v>
+      </c>
+      <c r="O37" s="149"/>
+      <c r="P37" s="149"/>
+      <c r="Q37" s="69" t="s">
+        <v>80</v>
+      </c>
+      <c r="R37" s="15" t="s">
+        <v>81</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="22">
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="G19:I19"/>
-    <mergeCell ref="C20:R20"/>
-    <mergeCell ref="C7:F7"/>
-    <mergeCell ref="H7:K7"/>
-    <mergeCell ref="M7:P7"/>
-    <mergeCell ref="C8:G8"/>
-    <mergeCell ref="I8:L8"/>
-    <mergeCell ref="C15:G15"/>
-    <mergeCell ref="I15:L15"/>
-    <mergeCell ref="C13:R13"/>
-    <mergeCell ref="C12:E12"/>
-    <mergeCell ref="G12:I12"/>
-    <mergeCell ref="C14:F14"/>
-    <mergeCell ref="H14:K14"/>
-    <mergeCell ref="M14:P14"/>
+  <mergeCells count="32">
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="M35:P35"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="Q19:R19"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="G27:I27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O28:R28"/>
     <mergeCell ref="O21:R21"/>
     <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="I22:L22"/>
     <mergeCell ref="G21:J21"/>
     <mergeCell ref="K21:N21"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:R20"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/can上层通信协议.xlsx
+++ b/can上层通信协议.xlsx
@@ -8,13 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\FanArray\CODE\FA_Ctrl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{898AD1EF-813A-4162-B9BA-C770DFE8500B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027AF4B7-2394-4739-97FF-F1C17BC8269F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="2610" yWindow="1700" windowWidth="21600" windowHeight="13210" activeTab="1" xr2:uid="{33FD23F6-9F23-4515-98A3-37DCFD7DD961}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{33FD23F6-9F23-4515-98A3-37DCFD7DD961}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
+    <sheet name="通信协议" sheetId="3" r:id="rId1"/>
+    <sheet name="通信协议-old" sheetId="1" r:id="rId2"/>
+    <sheet name="oled配置" sheetId="2" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,6 +40,24 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
+    <author>tc={15055951-46A0-4E16-B7EA-AD1CC4CF0E6A}</author>
+  </authors>
+  <commentList>
+    <comment ref="J12" authorId="0" shapeId="0" xr:uid="{15055951-46A0-4E16-B7EA-AD1CC4CF0E6A}">
+      <text>
+        <t>[线程批注]
+你的Excel版本可读取此线程批注; 但如果在更新版本的Excel中打开文件，则对批注所作的任何改动都将被删除。了解详细信息: https://go.microsoft.com/fwlink/?linkid=870924
+注释:
+    暂时只用一帧，4个数据一起</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
+<file path=xl/comments2.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
+  <authors>
     <author>tc={884D21C7-659A-4E91-B8F0-6D588451F1B6}</author>
   </authors>
   <commentList>
@@ -55,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="159" uniqueCount="108">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="117">
   <si>
     <t>遥控帧</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -547,6 +566,48 @@
     <t>r/txid</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>ccri</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ovf_cnti</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>ARR(pwm)、T采样、p；        I 、d</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>节点id（4个风机）
+000 0000              (高7位)</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>8=上传本机状态
+9=使能上传转速</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>7 = 保存参数
+A=使能oled
+B使能按键</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>16位列表
+ID&lt;&lt;5</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>err</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
+  <si>
+    <t>16位屏蔽、功能码
+MASK=0x00F</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -555,7 +616,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -647,6 +708,12 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -754,7 +821,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="51">
+  <borders count="56">
     <border>
       <left/>
       <right/>
@@ -1358,6 +1425,67 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
@@ -1367,7 +1495,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="176">
+  <cellXfs count="252">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1596,305 +1724,533 @@
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="9" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="9" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1915,6 +2271,232 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:oneCellAnchor>
+    <xdr:from>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>102028</xdr:colOff>
+      <xdr:row>17</xdr:row>
+      <xdr:rowOff>122593</xdr:rowOff>
+    </xdr:from>
+    <xdr:ext cx="3046027" cy="837793"/>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="2" name="文本框 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{98B6C0DB-61F2-43F2-853E-EAA3C8386AB7}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvSpPr txBox="1"/>
+      </xdr:nvSpPr>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="16053228" y="5577243"/>
+          <a:ext cx="3046027" cy="837793"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:solidFill>
+          <a:schemeClr val="accent6">
+            <a:lumMod val="20000"/>
+            <a:lumOff val="80000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </xdr:spPr>
+      <xdr:style>
+        <a:lnRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:lnRef>
+        <a:fillRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:fillRef>
+        <a:effectRef idx="0">
+          <a:scrgbClr r="0" g="0" b="0"/>
+        </a:effectRef>
+        <a:fontRef idx="minor">
+          <a:schemeClr val="tx1"/>
+        </a:fontRef>
+      </xdr:style>
+      <xdr:txBody>
+        <a:bodyPr vertOverflow="clip" horzOverflow="clip" wrap="none" rtlCol="0" anchor="t">
+          <a:spAutoFit/>
+        </a:bodyPr>
+        <a:lstStyle/>
+        <a:p>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>备注：</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+            <a:solidFill>
+              <a:schemeClr val="tx1"/>
+            </a:solidFill>
+            <a:effectLst/>
+            <a:latin typeface="+mn-lt"/>
+            <a:ea typeface="+mn-ea"/>
+            <a:cs typeface="+mn-cs"/>
+          </a:endParaRPr>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0" u="none" strike="noStrike" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1.</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>数据类型默认为</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>float</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>（</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>32</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>位），</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US" sz="1100" b="0" i="0" u="none" strike="noStrike">
+              <a:solidFill>
+                <a:schemeClr val="tx1"/>
+              </a:solidFill>
+              <a:effectLst/>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:rPr>
+            <a:t>帧两个数据</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US"/>
+            <a:t> </a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+        </a:p>
+        <a:p>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN"/>
+            <a:t>2.FIFO_0</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US"/>
+            <a:t>轮询，</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN"/>
+            <a:t>FIFO_1</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US"/>
+            <a:t>进中断（优先级</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN"/>
+            <a:t>0</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US"/>
+            <a:t>，</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="en-US" altLang="zh-CN"/>
+            <a:t>0</a:t>
+          </a:r>
+          <a:r>
+            <a:rPr lang="zh-CN" altLang="en-US"/>
+            <a:t>）</a:t>
+          </a:r>
+          <a:endParaRPr lang="en-US" altLang="zh-CN"/>
+        </a:p>
+        <a:p>
+          <a:endParaRPr lang="zh-CN" altLang="en-US" sz="1100"/>
+        </a:p>
+      </xdr:txBody>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:oneCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:oneCellAnchor>
     <xdr:from>
@@ -2463,6 +3045,14 @@
 
 <file path=xl/threadedComments/threadedComment1.xml><?xml version="1.0" encoding="utf-8"?>
 <ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <threadedComment ref="J12" dT="2026-10-11T16:21:09.51" personId="{C53B3D0C-41A5-4772-BD6A-75C33DE0B9F3}" id="{15055951-46A0-4E16-B7EA-AD1CC4CF0E6A}">
+    <text>暂时只用一帧，4个数据一起</text>
+  </threadedComment>
+</ThreadedComments>
+</file>
+
+<file path=xl/threadedComments/threadedComment2.xml><?xml version="1.0" encoding="utf-8"?>
+<ThreadedComments xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <threadedComment ref="J12" dT="2026-10-11T16:21:09.51" personId="{C53B3D0C-41A5-4772-BD6A-75C33DE0B9F3}" id="{884D21C7-659A-4E91-B8F0-6D588451F1B6}">
     <text>暂时只用一帧，4个数据一起</text>
   </threadedComment>
@@ -2470,6 +3060,691 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3AD21DF4-5752-4C2A-96A8-9E7CB020E65D}">
+  <dimension ref="D2:P44"/>
+  <sheetFormatPr defaultColWidth="9.23046875" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="3" width="9.23046875" style="1"/>
+    <col min="4" max="4" width="5.23046875" style="1" customWidth="1"/>
+    <col min="5" max="5" width="4.23046875" style="1" customWidth="1"/>
+    <col min="6" max="6" width="6.07421875" style="1" customWidth="1"/>
+    <col min="7" max="7" width="17" style="1" customWidth="1"/>
+    <col min="8" max="8" width="11" style="2" customWidth="1"/>
+    <col min="9" max="9" width="7.421875E-2" style="2" hidden="1" customWidth="1"/>
+    <col min="10" max="10" width="18.53515625" style="1" customWidth="1"/>
+    <col min="11" max="11" width="25.4609375" style="1" customWidth="1"/>
+    <col min="12" max="12" width="10.3046875" style="1" customWidth="1"/>
+    <col min="13" max="13" width="12.4609375" style="1" customWidth="1"/>
+    <col min="14" max="14" width="6.84375" style="1" customWidth="1"/>
+    <col min="15" max="15" width="7.3046875" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="9.23046875" style="1"/>
+  </cols>
+  <sheetData>
+    <row r="2" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="3" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D3" s="91"/>
+      <c r="E3" s="91"/>
+      <c r="F3" s="212" t="s">
+        <v>55</v>
+      </c>
+      <c r="G3" s="177" t="s">
+        <v>10</v>
+      </c>
+      <c r="H3" s="178" t="s">
+        <v>3</v>
+      </c>
+      <c r="I3" s="179"/>
+      <c r="J3" s="180"/>
+      <c r="K3" s="181" t="s">
+        <v>2</v>
+      </c>
+      <c r="L3" s="182" t="s">
+        <v>29</v>
+      </c>
+      <c r="M3" s="243" t="s">
+        <v>20</v>
+      </c>
+      <c r="N3" s="213" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="4:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D4" s="244"/>
+      <c r="E4" s="174" t="s">
+        <v>8</v>
+      </c>
+      <c r="F4" s="156">
+        <v>2</v>
+      </c>
+      <c r="G4" s="183" t="s">
+        <v>63</v>
+      </c>
+      <c r="H4" s="220" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="88"/>
+      <c r="J4" s="184" t="s">
+        <v>56</v>
+      </c>
+      <c r="K4" s="214" t="s">
+        <v>57</v>
+      </c>
+      <c r="L4" s="185" t="s">
+        <v>37</v>
+      </c>
+      <c r="M4" s="205" t="s">
+        <v>114</v>
+      </c>
+      <c r="N4" s="186" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="5" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="D5" s="244"/>
+      <c r="E5" s="175"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="187"/>
+      <c r="H5" s="221"/>
+      <c r="I5" s="89"/>
+      <c r="J5" s="188" t="s">
+        <v>50</v>
+      </c>
+      <c r="K5" s="208" t="s">
+        <v>60</v>
+      </c>
+      <c r="L5" s="189"/>
+      <c r="M5" s="206"/>
+      <c r="N5" s="190"/>
+    </row>
+    <row r="6" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="D6" s="244"/>
+      <c r="E6" s="175"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="187"/>
+      <c r="H6" s="221"/>
+      <c r="I6" s="89"/>
+      <c r="J6" s="188"/>
+      <c r="K6" s="208" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" s="189"/>
+      <c r="M6" s="206"/>
+      <c r="N6" s="190"/>
+    </row>
+    <row r="7" spans="4:16" ht="49.5" x14ac:dyDescent="0.45">
+      <c r="D7" s="244"/>
+      <c r="E7" s="175"/>
+      <c r="F7" s="157"/>
+      <c r="G7" s="187"/>
+      <c r="H7" s="221"/>
+      <c r="I7" s="89"/>
+      <c r="J7" s="188"/>
+      <c r="K7" s="208" t="s">
+        <v>113</v>
+      </c>
+      <c r="L7" s="189"/>
+      <c r="M7" s="206"/>
+      <c r="N7" s="190"/>
+    </row>
+    <row r="8" spans="4:16" ht="47.15" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="D8" s="244"/>
+      <c r="E8" s="175"/>
+      <c r="F8" s="158"/>
+      <c r="G8" s="191"/>
+      <c r="H8" s="221"/>
+      <c r="I8" s="9"/>
+      <c r="J8" s="192"/>
+      <c r="K8" s="204" t="s">
+        <v>112</v>
+      </c>
+      <c r="L8" s="189"/>
+      <c r="M8" s="206"/>
+      <c r="N8" s="218" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="9" spans="4:16" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D9" s="244"/>
+      <c r="E9" s="175"/>
+      <c r="F9" s="250">
+        <v>8</v>
+      </c>
+      <c r="G9" s="246" t="s">
+        <v>45</v>
+      </c>
+      <c r="H9" s="221"/>
+      <c r="I9" s="89"/>
+      <c r="J9" s="247" t="s">
+        <v>64</v>
+      </c>
+      <c r="K9" s="248" t="s">
+        <v>69</v>
+      </c>
+      <c r="L9" s="249" t="s">
+        <v>19</v>
+      </c>
+      <c r="M9" s="206"/>
+      <c r="N9" s="190"/>
+      <c r="P9" s="1" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="10" spans="4:16" ht="3" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D10" s="244"/>
+      <c r="E10" s="175"/>
+      <c r="F10" s="203"/>
+      <c r="G10" s="210" t="s">
+        <v>17</v>
+      </c>
+      <c r="H10" s="221"/>
+      <c r="I10" s="89"/>
+      <c r="J10" s="194" t="s">
+        <v>15</v>
+      </c>
+      <c r="K10" s="215" t="s">
+        <v>16</v>
+      </c>
+      <c r="L10" s="195" t="s">
+        <v>18</v>
+      </c>
+      <c r="M10" s="206"/>
+      <c r="N10" s="190"/>
+    </row>
+    <row r="11" spans="4:16" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="D11" s="244"/>
+      <c r="E11" s="175"/>
+      <c r="F11" s="196">
+        <v>2</v>
+      </c>
+      <c r="G11" s="211" t="s">
+        <v>6</v>
+      </c>
+      <c r="H11" s="221"/>
+      <c r="I11" s="89"/>
+      <c r="J11" s="193" t="s">
+        <v>73</v>
+      </c>
+      <c r="K11" s="35" t="s">
+        <v>110</v>
+      </c>
+      <c r="L11" s="251">
+        <v>2</v>
+      </c>
+      <c r="M11" s="206"/>
+      <c r="N11" s="219"/>
+    </row>
+    <row r="12" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="D12" s="244"/>
+      <c r="E12" s="175"/>
+      <c r="F12" s="197">
+        <v>8</v>
+      </c>
+      <c r="G12" s="211" t="s">
+        <v>48</v>
+      </c>
+      <c r="H12" s="221"/>
+      <c r="I12" s="89"/>
+      <c r="J12" s="198" t="s">
+        <v>72</v>
+      </c>
+      <c r="K12" s="199" t="s">
+        <v>38</v>
+      </c>
+      <c r="L12" s="154" t="s">
+        <v>68</v>
+      </c>
+      <c r="M12" s="206"/>
+      <c r="N12" s="216" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="13" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D13" s="244"/>
+      <c r="E13" s="176"/>
+      <c r="F13" s="200"/>
+      <c r="G13" s="209" t="s">
+        <v>51</v>
+      </c>
+      <c r="H13" s="222"/>
+      <c r="I13" s="90"/>
+      <c r="J13" s="201" t="s">
+        <v>74</v>
+      </c>
+      <c r="K13" s="202"/>
+      <c r="L13" s="155"/>
+      <c r="M13" s="207"/>
+      <c r="N13" s="217"/>
+    </row>
+    <row r="14" spans="4:16" x14ac:dyDescent="0.45">
+      <c r="D14" s="245"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="1"/>
+    </row>
+    <row r="15" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D15" s="245"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="1"/>
+    </row>
+    <row r="16" spans="4:16" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D16" s="245"/>
+      <c r="E16" s="148" t="s">
+        <v>9</v>
+      </c>
+      <c r="F16" s="231">
+        <v>8</v>
+      </c>
+      <c r="G16" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="H16" s="223" t="s">
+        <v>43</v>
+      </c>
+      <c r="I16" s="50"/>
+      <c r="J16" s="225" t="s">
+        <v>92</v>
+      </c>
+      <c r="K16" s="230" t="s">
+        <v>93</v>
+      </c>
+      <c r="L16" s="232">
+        <v>2</v>
+      </c>
+      <c r="M16" s="240" t="s">
+        <v>116</v>
+      </c>
+      <c r="N16" s="239"/>
+    </row>
+    <row r="17" spans="4:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D17" s="245"/>
+      <c r="E17" s="228"/>
+      <c r="F17" s="237">
+        <v>8</v>
+      </c>
+      <c r="G17" s="236" t="s">
+        <v>59</v>
+      </c>
+      <c r="H17" s="229"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="227" t="s">
+        <v>65</v>
+      </c>
+      <c r="K17" s="235" t="s">
+        <v>67</v>
+      </c>
+      <c r="L17" s="238"/>
+      <c r="M17" s="241"/>
+      <c r="N17" s="239"/>
+    </row>
+    <row r="18" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D18" s="245"/>
+      <c r="E18" s="150"/>
+      <c r="F18" s="233">
+        <v>1</v>
+      </c>
+      <c r="G18" s="6" t="s">
+        <v>115</v>
+      </c>
+      <c r="H18" s="224"/>
+      <c r="I18" s="51"/>
+      <c r="J18" s="226" t="s">
+        <v>58</v>
+      </c>
+      <c r="K18" s="87" t="s">
+        <v>91</v>
+      </c>
+      <c r="L18" s="234"/>
+      <c r="M18" s="242"/>
+      <c r="N18" s="239"/>
+    </row>
+    <row r="23" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+    </row>
+    <row r="24" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+    </row>
+    <row r="25" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+    </row>
+    <row r="26" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+    </row>
+    <row r="27" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+    </row>
+    <row r="28" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+    </row>
+    <row r="29" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="30" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D30" s="95"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="97"/>
+      <c r="G30" s="10" t="s">
+        <v>10</v>
+      </c>
+      <c r="H30" s="119" t="s">
+        <v>3</v>
+      </c>
+      <c r="I30" s="120"/>
+      <c r="J30" s="121"/>
+      <c r="K30" s="11" t="s">
+        <v>2</v>
+      </c>
+      <c r="L30" s="12" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="31" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D31" s="93" t="s">
+        <v>8</v>
+      </c>
+      <c r="E31" s="123" t="s">
+        <v>4</v>
+      </c>
+      <c r="F31" s="125" t="s">
+        <v>0</v>
+      </c>
+      <c r="G31" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="H31" s="128" t="s">
+        <v>42</v>
+      </c>
+      <c r="I31" s="129"/>
+      <c r="J31" s="38" t="s">
+        <v>27</v>
+      </c>
+      <c r="K31" s="98" t="s">
+        <v>52</v>
+      </c>
+      <c r="L31" s="98">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="D32" s="122"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="126"/>
+      <c r="G32" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32" s="109"/>
+      <c r="I32" s="110"/>
+      <c r="J32" s="39" t="s">
+        <v>28</v>
+      </c>
+      <c r="K32" s="99"/>
+      <c r="L32" s="99"/>
+    </row>
+    <row r="33" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D33" s="122"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="126"/>
+      <c r="G33" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="H33" s="109"/>
+      <c r="I33" s="110"/>
+      <c r="J33" s="39" t="s">
+        <v>47</v>
+      </c>
+      <c r="K33" s="99"/>
+      <c r="L33" s="99"/>
+    </row>
+    <row r="34" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D34" s="122"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="127"/>
+      <c r="G34" s="4" t="s">
+        <v>32</v>
+      </c>
+      <c r="H34" s="109"/>
+      <c r="I34" s="110"/>
+      <c r="J34" s="39" t="s">
+        <v>33</v>
+      </c>
+      <c r="K34" s="100"/>
+      <c r="L34" s="100"/>
+    </row>
+    <row r="35" spans="4:12" ht="33" x14ac:dyDescent="0.45">
+      <c r="D35" s="122"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="101" t="s">
+        <v>1</v>
+      </c>
+      <c r="G35" s="5" t="s">
+        <v>6</v>
+      </c>
+      <c r="H35" s="109"/>
+      <c r="I35" s="110"/>
+      <c r="J35" s="40" t="s">
+        <v>34</v>
+      </c>
+      <c r="K35" s="35" t="s">
+        <v>36</v>
+      </c>
+      <c r="L35" s="52">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="36" spans="4:12" ht="31.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D36" s="122"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="102"/>
+      <c r="G36" s="6" t="s">
+        <v>45</v>
+      </c>
+      <c r="H36" s="109"/>
+      <c r="I36" s="110"/>
+      <c r="J36" s="41" t="s">
+        <v>35</v>
+      </c>
+      <c r="K36" s="16" t="s">
+        <v>39</v>
+      </c>
+      <c r="L36" s="53" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="37" spans="4:12" ht="1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D37" s="122"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="103"/>
+      <c r="G37" s="19" t="s">
+        <v>17</v>
+      </c>
+      <c r="H37" s="109"/>
+      <c r="I37" s="110"/>
+      <c r="J37" s="8" t="s">
+        <v>15</v>
+      </c>
+      <c r="K37" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="L37" s="54" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="38" spans="4:12" ht="17" thickTop="1" x14ac:dyDescent="0.45">
+      <c r="D38" s="122"/>
+      <c r="E38" s="104" t="s">
+        <v>5</v>
+      </c>
+      <c r="F38" s="21" t="s">
+        <v>0</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>14</v>
+      </c>
+      <c r="H38" s="107" t="s">
+        <v>53</v>
+      </c>
+      <c r="I38" s="108"/>
+      <c r="J38" s="42" t="s">
+        <v>50</v>
+      </c>
+      <c r="K38" s="18" t="s">
+        <v>52</v>
+      </c>
+      <c r="L38" s="18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D39" s="122"/>
+      <c r="E39" s="105"/>
+      <c r="F39" s="113" t="s">
+        <v>1</v>
+      </c>
+      <c r="G39" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="H39" s="109"/>
+      <c r="I39" s="110"/>
+      <c r="J39" s="43" t="s">
+        <v>46</v>
+      </c>
+      <c r="K39" s="115" t="s">
+        <v>38</v>
+      </c>
+      <c r="L39" s="117">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="40" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D40" s="94"/>
+      <c r="E40" s="106"/>
+      <c r="F40" s="114"/>
+      <c r="G40" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="H40" s="111"/>
+      <c r="I40" s="112"/>
+      <c r="J40" s="44" t="s">
+        <v>47</v>
+      </c>
+      <c r="K40" s="116"/>
+      <c r="L40" s="118"/>
+    </row>
+    <row r="41" spans="4:12" x14ac:dyDescent="0.45">
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="92"/>
+    </row>
+    <row r="42" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D42" s="92"/>
+      <c r="E42" s="92"/>
+      <c r="F42" s="92"/>
+      <c r="G42" s="92"/>
+      <c r="H42" s="92"/>
+      <c r="I42" s="92"/>
+      <c r="J42" s="92"/>
+      <c r="K42" s="92"/>
+      <c r="L42" s="92"/>
+    </row>
+    <row r="43" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D43" s="93" t="s">
+        <v>9</v>
+      </c>
+      <c r="E43" s="25"/>
+      <c r="F43" s="24" t="s">
+        <v>1</v>
+      </c>
+      <c r="G43" s="7" t="s">
+        <v>7</v>
+      </c>
+      <c r="H43" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="I43" s="50"/>
+      <c r="J43" s="45" t="s">
+        <v>31</v>
+      </c>
+      <c r="K43" s="27" t="s">
+        <v>11</v>
+      </c>
+      <c r="L43" s="31">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="44" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D44" s="94"/>
+      <c r="E44" s="25"/>
+      <c r="F44" s="46" t="s">
+        <v>0</v>
+      </c>
+      <c r="G44" s="7" t="s">
+        <v>44</v>
+      </c>
+      <c r="H44" s="49" t="s">
+        <v>54</v>
+      </c>
+      <c r="I44" s="51"/>
+      <c r="J44" s="26" t="s">
+        <v>41</v>
+      </c>
+      <c r="K44" s="27" t="s">
+        <v>52</v>
+      </c>
+      <c r="L44" s="31">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="N8:N11"/>
+    <mergeCell ref="H16:H18"/>
+    <mergeCell ref="K39:K40"/>
+    <mergeCell ref="L39:L40"/>
+    <mergeCell ref="D41:L42"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="H4:H13"/>
+    <mergeCell ref="E4:E13"/>
+    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="L4:L8"/>
+    <mergeCell ref="F4:F8"/>
+    <mergeCell ref="G4:G8"/>
+    <mergeCell ref="D31:D40"/>
+    <mergeCell ref="E31:E37"/>
+    <mergeCell ref="F31:F34"/>
+    <mergeCell ref="H31:I37"/>
+    <mergeCell ref="K31:K34"/>
+    <mergeCell ref="L31:L34"/>
+    <mergeCell ref="F35:F37"/>
+    <mergeCell ref="E38:E40"/>
+    <mergeCell ref="H38:I40"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="M4:M13"/>
+    <mergeCell ref="M16:M18"/>
+    <mergeCell ref="N4:N7"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="K12:K13"/>
+    <mergeCell ref="H3:J3"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D80C86E-B8D5-4F55-A52E-43C4564E8A86}">
   <dimension ref="D1:P44"/>
   <sheetFormatPr defaultColWidth="9.23046875" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
@@ -2502,144 +3777,144 @@
       <c r="G3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="103" t="s">
+      <c r="H3" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="104"/>
-      <c r="J3" s="105"/>
+      <c r="I3" s="120"/>
+      <c r="J3" s="121"/>
       <c r="K3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="L3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="135" t="s">
+      <c r="M3" s="151" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="136"/>
+      <c r="N3" s="152"/>
       <c r="O3" s="32" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D4" s="77" t="s">
+      <c r="D4" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="107" t="s">
+      <c r="E4" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="140">
+      <c r="F4" s="156">
         <v>2</v>
       </c>
-      <c r="G4" s="126" t="s">
+      <c r="G4" s="142" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="112" t="s">
+      <c r="H4" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="113"/>
+      <c r="I4" s="129"/>
       <c r="J4" s="68" t="s">
         <v>56</v>
       </c>
       <c r="K4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="L4" s="82" t="s">
+      <c r="L4" s="98" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="129" t="s">
+      <c r="M4" s="145" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="119"/>
-      <c r="O4" s="124" t="s">
+      <c r="N4" s="135"/>
+      <c r="O4" s="140" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D5" s="106"/>
-      <c r="E5" s="108"/>
-      <c r="F5" s="141"/>
-      <c r="G5" s="127"/>
-      <c r="H5" s="93"/>
-      <c r="I5" s="94"/>
-      <c r="J5" s="122" t="s">
+      <c r="D5" s="122"/>
+      <c r="E5" s="124"/>
+      <c r="F5" s="157"/>
+      <c r="G5" s="143"/>
+      <c r="H5" s="109"/>
+      <c r="I5" s="110"/>
+      <c r="J5" s="138" t="s">
         <v>70</v>
       </c>
       <c r="K5" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="L5" s="83"/>
-      <c r="M5" s="130"/>
-      <c r="N5" s="120"/>
-      <c r="O5" s="114"/>
+      <c r="L5" s="99"/>
+      <c r="M5" s="146"/>
+      <c r="N5" s="136"/>
+      <c r="O5" s="130"/>
     </row>
     <row r="6" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D6" s="106"/>
-      <c r="E6" s="108"/>
-      <c r="F6" s="141"/>
-      <c r="G6" s="127"/>
-      <c r="H6" s="93"/>
-      <c r="I6" s="94"/>
-      <c r="J6" s="122"/>
+      <c r="D6" s="122"/>
+      <c r="E6" s="124"/>
+      <c r="F6" s="157"/>
+      <c r="G6" s="143"/>
+      <c r="H6" s="109"/>
+      <c r="I6" s="110"/>
+      <c r="J6" s="138"/>
       <c r="K6" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="83"/>
-      <c r="M6" s="130"/>
-      <c r="N6" s="120"/>
-      <c r="O6" s="114"/>
+      <c r="L6" s="99"/>
+      <c r="M6" s="146"/>
+      <c r="N6" s="136"/>
+      <c r="O6" s="130"/>
     </row>
     <row r="7" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D7" s="106"/>
-      <c r="E7" s="108"/>
-      <c r="F7" s="142"/>
-      <c r="G7" s="128"/>
-      <c r="H7" s="93"/>
-      <c r="I7" s="94"/>
-      <c r="J7" s="123"/>
+      <c r="D7" s="122"/>
+      <c r="E7" s="124"/>
+      <c r="F7" s="158"/>
+      <c r="G7" s="144"/>
+      <c r="H7" s="109"/>
+      <c r="I7" s="110"/>
+      <c r="J7" s="139"/>
       <c r="K7" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="L7" s="84"/>
-      <c r="M7" s="130"/>
-      <c r="N7" s="121"/>
-      <c r="O7" s="114"/>
+      <c r="L7" s="100"/>
+      <c r="M7" s="146"/>
+      <c r="N7" s="137"/>
+      <c r="O7" s="130"/>
     </row>
     <row r="8" spans="4:16" ht="47.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D8" s="106"/>
-      <c r="E8" s="108"/>
-      <c r="F8" s="85">
+      <c r="D8" s="122"/>
+      <c r="E8" s="124"/>
+      <c r="F8" s="101">
         <v>8</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="93"/>
-      <c r="I8" s="94"/>
+      <c r="H8" s="109"/>
+      <c r="I8" s="110"/>
       <c r="J8" s="57" t="s">
         <v>73</v>
       </c>
       <c r="K8" s="35" t="s">
-        <v>36</v>
+        <v>110</v>
       </c>
       <c r="L8" s="28">
         <v>2</v>
       </c>
-      <c r="M8" s="130"/>
+      <c r="M8" s="146"/>
       <c r="N8" s="33"/>
-      <c r="O8" s="114" t="s">
+      <c r="O8" s="130" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="4:16" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D9" s="106"/>
-      <c r="E9" s="108"/>
-      <c r="F9" s="86"/>
+      <c r="D9" s="122"/>
+      <c r="E9" s="124"/>
+      <c r="F9" s="102"/>
       <c r="G9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="93"/>
-      <c r="I9" s="94"/>
+      <c r="H9" s="109"/>
+      <c r="I9" s="110"/>
       <c r="J9" s="41" t="s">
         <v>64</v>
       </c>
@@ -2649,22 +3924,22 @@
       <c r="L9" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="131"/>
+      <c r="M9" s="147"/>
       <c r="N9" s="34"/>
-      <c r="O9" s="125"/>
+      <c r="O9" s="141"/>
       <c r="P9" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="4:16" ht="3" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D10" s="106"/>
-      <c r="E10" s="108"/>
-      <c r="F10" s="87"/>
+      <c r="D10" s="122"/>
+      <c r="E10" s="124"/>
+      <c r="F10" s="103"/>
       <c r="G10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="93"/>
-      <c r="I10" s="94"/>
+      <c r="H10" s="109"/>
+      <c r="I10" s="110"/>
       <c r="J10" s="8" t="s">
         <v>15</v>
       </c>
@@ -2677,8 +3952,8 @@
       <c r="O10" s="15"/>
     </row>
     <row r="11" spans="4:16" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="D11" s="106"/>
-      <c r="E11" s="88" t="s">
+      <c r="D11" s="122"/>
+      <c r="E11" s="104" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="21">
@@ -2687,10 +3962,10 @@
       <c r="G11" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="91" t="s">
+      <c r="H11" s="107" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="92"/>
+      <c r="I11" s="108"/>
       <c r="J11" s="42" t="s">
         <v>71</v>
       </c>
@@ -2698,57 +3973,57 @@
         <v>94</v>
       </c>
       <c r="L11" s="30"/>
-      <c r="M11" s="116" t="s">
+      <c r="M11" s="132" t="s">
         <v>22</v>
       </c>
       <c r="N11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="O11" s="114" t="s">
+      <c r="O11" s="130" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D12" s="106"/>
-      <c r="E12" s="89"/>
-      <c r="F12" s="97">
+      <c r="D12" s="122"/>
+      <c r="E12" s="105"/>
+      <c r="F12" s="113">
         <v>8</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="93"/>
-      <c r="I12" s="94"/>
+      <c r="H12" s="109"/>
+      <c r="I12" s="110"/>
       <c r="J12" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="K12" s="99" t="s">
+      <c r="K12" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="138" t="s">
+      <c r="L12" s="154" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="117"/>
-      <c r="N12" s="76"/>
-      <c r="O12" s="114"/>
+      <c r="M12" s="133"/>
+      <c r="N12" s="92"/>
+      <c r="O12" s="130"/>
     </row>
     <row r="13" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D13" s="78"/>
-      <c r="E13" s="90"/>
-      <c r="F13" s="98"/>
+      <c r="D13" s="94"/>
+      <c r="E13" s="106"/>
+      <c r="F13" s="114"/>
       <c r="G13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="95"/>
-      <c r="I13" s="96"/>
+      <c r="H13" s="111"/>
+      <c r="I13" s="112"/>
       <c r="J13" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="K13" s="100"/>
-      <c r="L13" s="139"/>
-      <c r="M13" s="118"/>
-      <c r="N13" s="137"/>
-      <c r="O13" s="115"/>
+      <c r="K13" s="116"/>
+      <c r="L13" s="155"/>
+      <c r="M13" s="134"/>
+      <c r="N13" s="153"/>
+      <c r="O13" s="131"/>
     </row>
     <row r="14" spans="4:16" x14ac:dyDescent="0.45">
       <c r="D14"/>
@@ -2773,10 +4048,10 @@
       <c r="L15"/>
     </row>
     <row r="16" spans="4:16" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D16" s="77" t="s">
+      <c r="D16" s="93" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="132"/>
+      <c r="E16" s="148"/>
       <c r="F16" s="59">
         <v>8</v>
       </c>
@@ -2802,8 +4077,8 @@
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="4:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D17" s="106"/>
-      <c r="E17" s="133"/>
+      <c r="D17" s="122"/>
+      <c r="E17" s="149"/>
       <c r="F17" s="60">
         <v>8</v>
       </c>
@@ -2824,8 +4099,8 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D18" s="78"/>
-      <c r="E18" s="134"/>
+      <c r="D18" s="94"/>
+      <c r="E18" s="150"/>
       <c r="F18" s="60">
         <v>1</v>
       </c>
@@ -2872,17 +4147,17 @@
     </row>
     <row r="29" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="30" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D30" s="79"/>
-      <c r="E30" s="80"/>
-      <c r="F30" s="81"/>
+      <c r="D30" s="95"/>
+      <c r="E30" s="96"/>
+      <c r="F30" s="97"/>
       <c r="G30" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="103" t="s">
+      <c r="H30" s="119" t="s">
         <v>3</v>
       </c>
-      <c r="I30" s="104"/>
-      <c r="J30" s="105"/>
+      <c r="I30" s="120"/>
+      <c r="J30" s="121"/>
       <c r="K30" s="11" t="s">
         <v>2</v>
       </c>
@@ -2891,88 +4166,88 @@
       </c>
     </row>
     <row r="31" spans="4:14" x14ac:dyDescent="0.45">
-      <c r="D31" s="77" t="s">
+      <c r="D31" s="93" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="107" t="s">
+      <c r="E31" s="123" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="109" t="s">
+      <c r="F31" s="125" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="112" t="s">
+      <c r="H31" s="128" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="113"/>
+      <c r="I31" s="129"/>
       <c r="J31" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="K31" s="82" t="s">
+      <c r="K31" s="98" t="s">
         <v>52</v>
       </c>
-      <c r="L31" s="82">
+      <c r="L31" s="98">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="4:14" x14ac:dyDescent="0.45">
-      <c r="D32" s="106"/>
-      <c r="E32" s="108"/>
-      <c r="F32" s="110"/>
+      <c r="D32" s="122"/>
+      <c r="E32" s="124"/>
+      <c r="F32" s="126"/>
       <c r="G32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="93"/>
-      <c r="I32" s="94"/>
+      <c r="H32" s="109"/>
+      <c r="I32" s="110"/>
       <c r="J32" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K32" s="83"/>
-      <c r="L32" s="83"/>
+      <c r="K32" s="99"/>
+      <c r="L32" s="99"/>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D33" s="106"/>
-      <c r="E33" s="108"/>
-      <c r="F33" s="110"/>
+      <c r="D33" s="122"/>
+      <c r="E33" s="124"/>
+      <c r="F33" s="126"/>
       <c r="G33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H33" s="93"/>
-      <c r="I33" s="94"/>
+      <c r="H33" s="109"/>
+      <c r="I33" s="110"/>
       <c r="J33" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="83"/>
-      <c r="L33" s="83"/>
+      <c r="K33" s="99"/>
+      <c r="L33" s="99"/>
     </row>
     <row r="34" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D34" s="106"/>
-      <c r="E34" s="108"/>
-      <c r="F34" s="111"/>
+      <c r="D34" s="122"/>
+      <c r="E34" s="124"/>
+      <c r="F34" s="127"/>
       <c r="G34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="93"/>
-      <c r="I34" s="94"/>
+      <c r="H34" s="109"/>
+      <c r="I34" s="110"/>
       <c r="J34" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="84"/>
-      <c r="L34" s="84"/>
+      <c r="K34" s="100"/>
+      <c r="L34" s="100"/>
     </row>
     <row r="35" spans="4:12" ht="33" x14ac:dyDescent="0.45">
-      <c r="D35" s="106"/>
-      <c r="E35" s="108"/>
-      <c r="F35" s="85" t="s">
+      <c r="D35" s="122"/>
+      <c r="E35" s="124"/>
+      <c r="F35" s="101" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H35" s="93"/>
-      <c r="I35" s="94"/>
+      <c r="H35" s="109"/>
+      <c r="I35" s="110"/>
       <c r="J35" s="40" t="s">
         <v>34</v>
       </c>
@@ -2984,14 +4259,14 @@
       </c>
     </row>
     <row r="36" spans="4:12" ht="31.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D36" s="106"/>
-      <c r="E36" s="108"/>
-      <c r="F36" s="86"/>
+      <c r="D36" s="122"/>
+      <c r="E36" s="124"/>
+      <c r="F36" s="102"/>
       <c r="G36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H36" s="93"/>
-      <c r="I36" s="94"/>
+      <c r="H36" s="109"/>
+      <c r="I36" s="110"/>
       <c r="J36" s="41" t="s">
         <v>35</v>
       </c>
@@ -3003,14 +4278,14 @@
       </c>
     </row>
     <row r="37" spans="4:12" ht="1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D37" s="106"/>
-      <c r="E37" s="108"/>
-      <c r="F37" s="87"/>
+      <c r="D37" s="122"/>
+      <c r="E37" s="124"/>
+      <c r="F37" s="103"/>
       <c r="G37" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="93"/>
-      <c r="I37" s="94"/>
+      <c r="H37" s="109"/>
+      <c r="I37" s="110"/>
       <c r="J37" s="8" t="s">
         <v>15</v>
       </c>
@@ -3022,8 +4297,8 @@
       </c>
     </row>
     <row r="38" spans="4:12" ht="17" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="D38" s="106"/>
-      <c r="E38" s="88" t="s">
+      <c r="D38" s="122"/>
+      <c r="E38" s="104" t="s">
         <v>5</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -3032,10 +4307,10 @@
       <c r="G38" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="91" t="s">
+      <c r="H38" s="107" t="s">
         <v>53</v>
       </c>
-      <c r="I38" s="92"/>
+      <c r="I38" s="108"/>
       <c r="J38" s="42" t="s">
         <v>50</v>
       </c>
@@ -3047,65 +4322,65 @@
       </c>
     </row>
     <row r="39" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D39" s="106"/>
-      <c r="E39" s="89"/>
-      <c r="F39" s="97" t="s">
+      <c r="D39" s="122"/>
+      <c r="E39" s="105"/>
+      <c r="F39" s="113" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H39" s="93"/>
-      <c r="I39" s="94"/>
+      <c r="H39" s="109"/>
+      <c r="I39" s="110"/>
       <c r="J39" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="99" t="s">
+      <c r="K39" s="115" t="s">
         <v>38</v>
       </c>
-      <c r="L39" s="101">
+      <c r="L39" s="117">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="78"/>
-      <c r="E40" s="90"/>
-      <c r="F40" s="98"/>
+      <c r="D40" s="94"/>
+      <c r="E40" s="106"/>
+      <c r="F40" s="114"/>
       <c r="G40" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H40" s="95"/>
-      <c r="I40" s="96"/>
+      <c r="H40" s="111"/>
+      <c r="I40" s="112"/>
       <c r="J40" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="K40" s="100"/>
-      <c r="L40" s="102"/>
+      <c r="K40" s="116"/>
+      <c r="L40" s="118"/>
     </row>
     <row r="41" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D41" s="76"/>
-      <c r="E41" s="76"/>
-      <c r="F41" s="76"/>
-      <c r="G41" s="76"/>
-      <c r="H41" s="76"/>
-      <c r="I41" s="76"/>
-      <c r="J41" s="76"/>
-      <c r="K41" s="76"/>
-      <c r="L41" s="76"/>
+      <c r="D41" s="92"/>
+      <c r="E41" s="92"/>
+      <c r="F41" s="92"/>
+      <c r="G41" s="92"/>
+      <c r="H41" s="92"/>
+      <c r="I41" s="92"/>
+      <c r="J41" s="92"/>
+      <c r="K41" s="92"/>
+      <c r="L41" s="92"/>
     </row>
     <row r="42" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D42" s="76"/>
-      <c r="E42" s="76"/>
-      <c r="F42" s="76"/>
-      <c r="G42" s="76"/>
-      <c r="H42" s="76"/>
-      <c r="I42" s="76"/>
-      <c r="J42" s="76"/>
-      <c r="K42" s="76"/>
-      <c r="L42" s="76"/>
+      <c r="D42" s="92"/>
+      <c r="E42" s="92"/>
+      <c r="F42" s="92"/>
+      <c r="G42" s="92"/>
+      <c r="H42" s="92"/>
+      <c r="I42" s="92"/>
+      <c r="J42" s="92"/>
+      <c r="K42" s="92"/>
+      <c r="L42" s="92"/>
     </row>
     <row r="43" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D43" s="77" t="s">
+      <c r="D43" s="93" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="25"/>
@@ -3130,7 +4405,7 @@
       </c>
     </row>
     <row r="44" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D44" s="78"/>
+      <c r="D44" s="94"/>
       <c r="E44" s="25"/>
       <c r="F44" s="46" t="s">
         <v>0</v>
@@ -3202,7 +4477,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8521510C-1B37-40AB-AFA2-021412ADBA84}">
   <dimension ref="A4:AB37"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
@@ -3211,214 +4486,123 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A4" s="174"/>
-      <c r="B4" s="168"/>
-      <c r="C4" s="169"/>
-      <c r="D4" s="169"/>
-      <c r="E4" s="169"/>
-      <c r="F4" s="169"/>
-      <c r="G4" s="169"/>
-      <c r="H4" s="169"/>
-      <c r="I4" s="169"/>
-      <c r="J4" s="169"/>
-      <c r="K4" s="169"/>
-      <c r="L4" s="169"/>
-      <c r="M4" s="169"/>
-      <c r="N4" s="169"/>
-      <c r="O4" s="169"/>
-      <c r="P4" s="169"/>
-      <c r="Q4" s="169"/>
-      <c r="R4" s="169"/>
+      <c r="A4" s="86"/>
     </row>
     <row r="5" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A5" s="173"/>
-      <c r="B5" s="168"/>
-      <c r="C5" s="170"/>
-      <c r="D5" s="170"/>
-      <c r="E5" s="170"/>
-      <c r="F5" s="169"/>
-      <c r="G5" s="170"/>
-      <c r="H5" s="170"/>
-      <c r="I5" s="170"/>
-      <c r="J5" s="169"/>
-      <c r="K5" s="171"/>
-      <c r="L5" s="169"/>
-      <c r="M5" s="172"/>
-      <c r="N5" s="169"/>
-      <c r="O5" s="169"/>
-      <c r="P5" s="169"/>
-      <c r="Q5" s="173"/>
-      <c r="R5" s="173"/>
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="K5" s="85"/>
+      <c r="M5" s="76"/>
+      <c r="Q5"/>
+      <c r="R5"/>
     </row>
     <row r="6" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A6" s="173"/>
-      <c r="B6" s="168"/>
-      <c r="C6" s="170"/>
-      <c r="D6" s="170"/>
-      <c r="E6" s="170"/>
-      <c r="F6" s="170"/>
-      <c r="G6" s="170"/>
-      <c r="H6" s="170"/>
-      <c r="I6" s="170"/>
-      <c r="J6" s="170"/>
-      <c r="K6" s="170"/>
-      <c r="L6" s="170"/>
-      <c r="M6" s="170"/>
-      <c r="N6" s="170"/>
-      <c r="O6" s="170"/>
-      <c r="P6" s="170"/>
-      <c r="Q6" s="170"/>
-      <c r="R6" s="170"/>
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="84"/>
+      <c r="O6" s="84"/>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="84"/>
     </row>
     <row r="7" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A7" s="173"/>
-      <c r="B7" s="168"/>
-      <c r="C7" s="173"/>
-      <c r="D7" s="173"/>
-      <c r="E7" s="173"/>
-      <c r="F7" s="173"/>
-      <c r="G7" s="169"/>
-      <c r="H7" s="173"/>
-      <c r="I7" s="173"/>
-      <c r="J7" s="173"/>
-      <c r="K7" s="173"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="173"/>
-      <c r="N7" s="173"/>
-      <c r="O7" s="173"/>
-      <c r="P7" s="173"/>
-      <c r="Q7" s="169"/>
-      <c r="R7" s="169"/>
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
     </row>
     <row r="8" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A8" s="173"/>
-      <c r="B8" s="168"/>
-      <c r="C8" s="170"/>
-      <c r="D8" s="170"/>
-      <c r="E8" s="170"/>
-      <c r="F8" s="170"/>
-      <c r="G8" s="170"/>
-      <c r="H8" s="169"/>
-      <c r="I8" s="170"/>
-      <c r="J8" s="170"/>
-      <c r="K8" s="170"/>
-      <c r="L8" s="170"/>
-      <c r="M8" s="169"/>
-      <c r="N8" s="169"/>
-      <c r="O8" s="169"/>
-      <c r="P8" s="169"/>
-      <c r="Q8" s="169"/>
-      <c r="R8" s="169"/>
-    </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="B11" s="168"/>
-      <c r="C11" s="169"/>
-      <c r="D11" s="169"/>
-      <c r="E11" s="169"/>
-      <c r="F11" s="169"/>
-      <c r="G11" s="169"/>
-      <c r="H11" s="169"/>
-      <c r="I11" s="169"/>
-      <c r="J11" s="169"/>
-      <c r="K11" s="169"/>
-      <c r="L11" s="169"/>
-      <c r="M11" s="169"/>
-      <c r="N11" s="169"/>
-      <c r="O11" s="169"/>
-      <c r="P11" s="169"/>
-      <c r="Q11" s="169"/>
-      <c r="R11" s="169"/>
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="I8" s="84"/>
+      <c r="J8" s="84"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
     </row>
     <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="175" t="s">
+      <c r="A12" s="86" t="s">
         <v>87</v>
       </c>
-      <c r="B12" s="168"/>
-      <c r="C12" s="170"/>
-      <c r="D12" s="170"/>
-      <c r="E12" s="170"/>
-      <c r="F12" s="169"/>
-      <c r="G12" s="170"/>
-      <c r="H12" s="170"/>
-      <c r="I12" s="170"/>
-      <c r="J12" s="169"/>
-      <c r="K12" s="171"/>
-      <c r="L12" s="169"/>
-      <c r="M12" s="172"/>
-      <c r="N12" s="169"/>
-      <c r="O12" s="169"/>
-      <c r="P12" s="169"/>
-      <c r="Q12" s="173"/>
-      <c r="R12" s="173"/>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="K12" s="85"/>
+      <c r="M12" s="76"/>
+      <c r="Q12"/>
+      <c r="R12"/>
     </row>
     <row r="13" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A13" s="152"/>
-      <c r="B13" s="168"/>
-      <c r="C13" s="170"/>
-      <c r="D13" s="170"/>
-      <c r="E13" s="170"/>
-      <c r="F13" s="170"/>
-      <c r="G13" s="170"/>
-      <c r="H13" s="170"/>
-      <c r="I13" s="170"/>
-      <c r="J13" s="170"/>
-      <c r="K13" s="170"/>
-      <c r="L13" s="170"/>
-      <c r="M13" s="170"/>
-      <c r="N13" s="170"/>
-      <c r="O13" s="170"/>
-      <c r="P13" s="170"/>
-      <c r="Q13" s="170"/>
-      <c r="R13" s="170"/>
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="84"/>
+      <c r="P13" s="84"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="84"/>
     </row>
     <row r="14" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A14" s="152"/>
-      <c r="B14" s="168"/>
-      <c r="C14" s="173"/>
-      <c r="D14" s="173"/>
-      <c r="E14" s="173"/>
-      <c r="F14" s="173"/>
-      <c r="G14" s="169"/>
-      <c r="H14" s="173"/>
-      <c r="I14" s="173"/>
-      <c r="J14" s="173"/>
-      <c r="K14" s="173"/>
-      <c r="L14" s="169"/>
-      <c r="M14" s="173"/>
-      <c r="N14" s="173"/>
-      <c r="O14" s="173"/>
-      <c r="P14" s="173"/>
-      <c r="Q14" s="169"/>
-      <c r="R14" s="169"/>
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
     </row>
     <row r="15" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A15" s="152"/>
-      <c r="B15" s="168"/>
-      <c r="C15" s="170"/>
-      <c r="D15" s="170"/>
-      <c r="E15" s="170"/>
-      <c r="F15" s="170"/>
-      <c r="G15" s="170"/>
-      <c r="H15" s="169"/>
-      <c r="I15" s="170"/>
-      <c r="J15" s="170"/>
-      <c r="K15" s="170"/>
-      <c r="L15" s="170"/>
-      <c r="M15" s="169"/>
-      <c r="N15" s="169"/>
-      <c r="O15" s="169"/>
-      <c r="P15" s="169"/>
-      <c r="Q15" s="169"/>
-      <c r="R15" s="169"/>
-    </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A16" s="152"/>
-    </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A17" s="152"/>
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
     </row>
     <row r="18" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="153" t="s">
+      <c r="A18" s="169" t="s">
         <v>87</v>
       </c>
       <c r="C18" s="1">
@@ -3471,106 +4655,106 @@
       </c>
     </row>
     <row r="19" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A19" s="76"/>
+      <c r="A19" s="92"/>
       <c r="B19">
         <v>1</v>
       </c>
-      <c r="C19" s="143" t="s">
+      <c r="C19" s="162" t="s">
         <v>107</v>
       </c>
-      <c r="D19" s="144"/>
-      <c r="E19" s="144"/>
+      <c r="D19" s="163"/>
+      <c r="E19" s="163"/>
       <c r="F19" s="71" t="s">
         <v>76</v>
       </c>
-      <c r="G19" s="158"/>
-      <c r="H19" s="158"/>
-      <c r="I19" s="158"/>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
       <c r="J19" s="71"/>
-      <c r="K19" s="159"/>
+      <c r="K19" s="78"/>
       <c r="L19" s="71"/>
       <c r="M19" s="75"/>
       <c r="N19" s="71"/>
       <c r="O19" s="71"/>
       <c r="P19" s="71"/>
-      <c r="Q19" s="156"/>
-      <c r="R19" s="157"/>
+      <c r="Q19" s="167"/>
+      <c r="R19" s="168"/>
     </row>
     <row r="20" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A20" s="76"/>
+      <c r="A20" s="92"/>
       <c r="B20">
         <v>2</v>
       </c>
-      <c r="C20" s="145" t="s">
+      <c r="C20" s="164" t="s">
         <v>82</v>
       </c>
-      <c r="D20" s="146"/>
-      <c r="E20" s="146"/>
-      <c r="F20" s="146"/>
-      <c r="G20" s="146"/>
-      <c r="H20" s="146"/>
-      <c r="I20" s="146"/>
-      <c r="J20" s="146"/>
-      <c r="K20" s="146"/>
-      <c r="L20" s="146"/>
-      <c r="M20" s="146"/>
-      <c r="N20" s="146"/>
-      <c r="O20" s="146"/>
-      <c r="P20" s="146"/>
-      <c r="Q20" s="146"/>
-      <c r="R20" s="147"/>
+      <c r="D20" s="165"/>
+      <c r="E20" s="165"/>
+      <c r="F20" s="165"/>
+      <c r="G20" s="165"/>
+      <c r="H20" s="165"/>
+      <c r="I20" s="165"/>
+      <c r="J20" s="165"/>
+      <c r="K20" s="165"/>
+      <c r="L20" s="165"/>
+      <c r="M20" s="165"/>
+      <c r="N20" s="165"/>
+      <c r="O20" s="165"/>
+      <c r="P20" s="165"/>
+      <c r="Q20" s="165"/>
+      <c r="R20" s="166"/>
     </row>
     <row r="21" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A21" s="76"/>
+      <c r="A21" s="92"/>
       <c r="B21">
         <v>3</v>
       </c>
-      <c r="C21" s="163" t="s">
+      <c r="C21" s="171" t="s">
         <v>106</v>
       </c>
-      <c r="D21" s="164"/>
-      <c r="E21" s="164"/>
-      <c r="F21" s="164"/>
-      <c r="G21" s="164" t="s">
+      <c r="D21" s="161"/>
+      <c r="E21" s="161"/>
+      <c r="F21" s="161"/>
+      <c r="G21" s="161" t="s">
         <v>84</v>
       </c>
-      <c r="H21" s="164"/>
-      <c r="I21" s="164"/>
-      <c r="J21" s="164"/>
-      <c r="K21" s="164" t="s">
+      <c r="H21" s="161"/>
+      <c r="I21" s="161"/>
+      <c r="J21" s="161"/>
+      <c r="K21" s="161" t="s">
         <v>85</v>
       </c>
-      <c r="L21" s="164"/>
-      <c r="M21" s="164"/>
-      <c r="N21" s="164"/>
-      <c r="O21" s="164" t="s">
+      <c r="L21" s="161"/>
+      <c r="M21" s="161"/>
+      <c r="N21" s="161"/>
+      <c r="O21" s="161" t="s">
         <v>86</v>
       </c>
-      <c r="P21" s="164"/>
-      <c r="Q21" s="164"/>
-      <c r="R21" s="165"/>
+      <c r="P21" s="161"/>
+      <c r="Q21" s="161"/>
+      <c r="R21" s="172"/>
     </row>
     <row r="22" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="76"/>
+      <c r="A22" s="92"/>
       <c r="B22">
         <v>4</v>
       </c>
-      <c r="C22" s="150" t="s">
+      <c r="C22" s="159" t="s">
         <v>83</v>
       </c>
-      <c r="D22" s="149"/>
-      <c r="E22" s="149"/>
-      <c r="F22" s="149"/>
-      <c r="G22" s="149"/>
+      <c r="D22" s="160"/>
+      <c r="E22" s="160"/>
+      <c r="F22" s="160"/>
+      <c r="G22" s="160"/>
       <c r="H22" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="I22" s="149" t="s">
+      <c r="I22" s="160" t="s">
         <v>97</v>
       </c>
-      <c r="J22" s="149"/>
-      <c r="K22" s="149"/>
-      <c r="L22" s="149"/>
+      <c r="J22" s="160"/>
+      <c r="K22" s="160"/>
+      <c r="L22" s="160"/>
       <c r="M22" s="69" t="s">
         <v>76</v>
       </c>
@@ -3631,21 +4815,25 @@
       </c>
     </row>
     <row r="27" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A27" s="76" t="s">
+      <c r="A27" s="92" t="s">
         <v>96</v>
       </c>
       <c r="B27">
         <v>1</v>
       </c>
-      <c r="C27" s="143"/>
-      <c r="D27" s="144"/>
-      <c r="E27" s="144"/>
+      <c r="C27" s="162" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="163"/>
+      <c r="E27" s="163"/>
       <c r="F27" s="71"/>
-      <c r="G27" s="144"/>
-      <c r="H27" s="144"/>
-      <c r="I27" s="144"/>
-      <c r="J27" s="71"/>
-      <c r="K27" s="159"/>
+      <c r="G27" s="163" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" s="163"/>
+      <c r="I27" s="163"/>
+      <c r="J27" s="163"/>
+      <c r="K27" s="163"/>
       <c r="L27" s="71"/>
       <c r="M27" s="71"/>
       <c r="N27" s="71"/>
@@ -3655,92 +4843,92 @@
       <c r="R27" s="72"/>
     </row>
     <row r="28" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A28" s="76"/>
+      <c r="A28" s="92"/>
       <c r="B28">
         <v>2</v>
       </c>
-      <c r="C28" s="148" t="s">
+      <c r="C28" s="170" t="s">
         <v>89</v>
       </c>
-      <c r="D28" s="76"/>
-      <c r="E28" s="76"/>
-      <c r="F28" s="76"/>
-      <c r="G28" s="76" t="s">
+      <c r="D28" s="92"/>
+      <c r="E28" s="92"/>
+      <c r="F28" s="92"/>
+      <c r="G28" s="92" t="s">
         <v>84</v>
       </c>
-      <c r="H28" s="76"/>
-      <c r="I28" s="76"/>
-      <c r="J28" s="76"/>
-      <c r="K28" s="76" t="s">
+      <c r="H28" s="92"/>
+      <c r="I28" s="92"/>
+      <c r="J28" s="92"/>
+      <c r="K28" s="92" t="s">
         <v>85</v>
       </c>
-      <c r="L28" s="76"/>
-      <c r="M28" s="76"/>
-      <c r="N28" s="76"/>
-      <c r="O28" s="76" t="s">
+      <c r="L28" s="92"/>
+      <c r="M28" s="92"/>
+      <c r="N28" s="92"/>
+      <c r="O28" s="92" t="s">
         <v>86</v>
       </c>
-      <c r="P28" s="76"/>
-      <c r="Q28" s="76"/>
-      <c r="R28" s="151"/>
+      <c r="P28" s="92"/>
+      <c r="Q28" s="92"/>
+      <c r="R28" s="173"/>
     </row>
     <row r="29" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A29" s="76"/>
+      <c r="A29" s="92"/>
       <c r="B29">
         <v>3</v>
       </c>
-      <c r="C29" s="163" t="s">
+      <c r="C29" s="171" t="s">
         <v>88</v>
       </c>
-      <c r="D29" s="164"/>
-      <c r="E29" s="164"/>
-      <c r="F29" s="164"/>
-      <c r="G29" s="164" t="s">
+      <c r="D29" s="161"/>
+      <c r="E29" s="161"/>
+      <c r="F29" s="161"/>
+      <c r="G29" s="161" t="s">
         <v>84</v>
       </c>
-      <c r="H29" s="164"/>
-      <c r="I29" s="164"/>
-      <c r="J29" s="164"/>
-      <c r="K29" s="164" t="s">
+      <c r="H29" s="161"/>
+      <c r="I29" s="161"/>
+      <c r="J29" s="161"/>
+      <c r="K29" s="161" t="s">
         <v>85</v>
       </c>
-      <c r="L29" s="164"/>
-      <c r="M29" s="164"/>
-      <c r="N29" s="164"/>
-      <c r="O29" s="164" t="s">
+      <c r="L29" s="161"/>
+      <c r="M29" s="161"/>
+      <c r="N29" s="161"/>
+      <c r="O29" s="161" t="s">
         <v>86</v>
       </c>
-      <c r="P29" s="164"/>
-      <c r="Q29" s="164"/>
-      <c r="R29" s="165"/>
+      <c r="P29" s="161"/>
+      <c r="Q29" s="161"/>
+      <c r="R29" s="172"/>
     </row>
     <row r="30" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="76"/>
+      <c r="A30" s="92"/>
       <c r="B30">
         <v>4</v>
       </c>
-      <c r="C30" s="150" t="s">
+      <c r="C30" s="159" t="s">
         <v>83</v>
       </c>
-      <c r="D30" s="149"/>
-      <c r="E30" s="149"/>
-      <c r="F30" s="149"/>
-      <c r="G30" s="149"/>
+      <c r="D30" s="160"/>
+      <c r="E30" s="160"/>
+      <c r="F30" s="160"/>
+      <c r="G30" s="160"/>
       <c r="H30" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="I30" s="149" t="s">
+      <c r="I30" s="160" t="s">
         <v>97</v>
       </c>
-      <c r="J30" s="149"/>
-      <c r="K30" s="149"/>
-      <c r="L30" s="149"/>
+      <c r="J30" s="160"/>
+      <c r="K30" s="160"/>
+      <c r="L30" s="160"/>
       <c r="M30" s="69" t="s">
         <v>76</v>
       </c>
       <c r="N30" s="69"/>
-      <c r="O30" s="160"/>
-      <c r="P30" s="160"/>
+      <c r="O30" s="79"/>
+      <c r="P30" s="79"/>
       <c r="Q30" s="69"/>
       <c r="R30" s="15"/>
     </row>
@@ -3804,7 +4992,7 @@
       </c>
     </row>
     <row r="34" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A34" s="76" t="s">
+      <c r="A34" s="92" t="s">
         <v>101</v>
       </c>
       <c r="B34">
@@ -3822,13 +5010,13 @@
       <c r="F34" s="71" t="s">
         <v>105</v>
       </c>
-      <c r="G34" s="156" t="s">
+      <c r="G34" s="167" t="s">
         <v>100</v>
       </c>
-      <c r="H34" s="156"/>
-      <c r="I34" s="156"/>
-      <c r="J34" s="156"/>
-      <c r="K34" s="156"/>
+      <c r="H34" s="167"/>
+      <c r="I34" s="167"/>
+      <c r="J34" s="167"/>
+      <c r="K34" s="167"/>
       <c r="L34" s="71" t="s">
         <v>76</v>
       </c>
@@ -3842,90 +5030,89 @@
       <c r="P34" s="71" t="s">
         <v>104</v>
       </c>
-      <c r="Q34" s="156"/>
-      <c r="R34" s="157"/>
+      <c r="Q34" s="167"/>
+      <c r="R34" s="168"/>
     </row>
     <row r="35" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A35" s="76"/>
+      <c r="A35" s="92"/>
       <c r="B35">
         <v>2</v>
       </c>
-      <c r="C35" s="148" t="s">
+      <c r="C35" s="170" t="s">
         <v>77</v>
       </c>
-      <c r="D35" s="155"/>
-      <c r="E35" s="155"/>
-      <c r="F35" s="155"/>
-      <c r="G35" s="154" t="s">
+      <c r="D35" s="92"/>
+      <c r="E35" s="92"/>
+      <c r="F35" s="92"/>
+      <c r="G35" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="H35" s="155" t="s">
+      <c r="H35" s="92" t="s">
         <v>78</v>
       </c>
-      <c r="I35" s="155"/>
-      <c r="J35" s="155"/>
-      <c r="K35" s="155"/>
-      <c r="L35" s="154" t="s">
+      <c r="I35" s="92"/>
+      <c r="J35" s="92"/>
+      <c r="K35" s="92"/>
+      <c r="L35" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="M35" s="155" t="s">
+      <c r="M35" s="92" t="s">
         <v>79</v>
       </c>
-      <c r="N35" s="155"/>
-      <c r="O35" s="155"/>
-      <c r="P35" s="155"/>
-      <c r="Q35" s="154"/>
+      <c r="N35" s="92"/>
+      <c r="O35" s="92"/>
+      <c r="P35" s="92"/>
       <c r="R35" s="74"/>
     </row>
     <row r="36" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A36" s="76"/>
+      <c r="A36" s="92"/>
       <c r="B36">
         <v>3</v>
       </c>
-      <c r="C36" s="161"/>
-      <c r="D36" s="166"/>
-      <c r="E36" s="166"/>
-      <c r="F36" s="166"/>
-      <c r="G36" s="166"/>
-      <c r="H36" s="166"/>
-      <c r="I36" s="166"/>
-      <c r="J36" s="166"/>
-      <c r="K36" s="166"/>
-      <c r="L36" s="166"/>
-      <c r="M36" s="166"/>
-      <c r="N36" s="166"/>
-      <c r="O36" s="166"/>
-      <c r="P36" s="166"/>
-      <c r="Q36" s="167"/>
-      <c r="R36" s="162"/>
+      <c r="C36" s="80"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="83"/>
+      <c r="L36" s="83"/>
+      <c r="M36" s="83"/>
+      <c r="N36" s="83"/>
+      <c r="O36" s="83"/>
+      <c r="P36" s="83"/>
+      <c r="Q36" s="82"/>
+      <c r="R36" s="81"/>
     </row>
     <row r="37" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="76"/>
+      <c r="A37" s="92"/>
       <c r="B37">
         <v>4</v>
       </c>
-      <c r="C37" s="150"/>
-      <c r="D37" s="149"/>
-      <c r="E37" s="149"/>
-      <c r="F37" s="149"/>
-      <c r="G37" s="149"/>
+      <c r="C37" s="159"/>
+      <c r="D37" s="160"/>
+      <c r="E37" s="160"/>
+      <c r="F37" s="160"/>
+      <c r="G37" s="160"/>
       <c r="H37" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="I37" s="149" t="s">
+      <c r="I37" s="160" t="s">
         <v>97</v>
       </c>
-      <c r="J37" s="149"/>
-      <c r="K37" s="149"/>
-      <c r="L37" s="149"/>
+      <c r="J37" s="160"/>
+      <c r="K37" s="160"/>
+      <c r="L37" s="160"/>
       <c r="M37" s="69" t="s">
         <v>76</v>
       </c>
-      <c r="N37" s="149">
+      <c r="N37" s="160">
         <v>250</v>
       </c>
-      <c r="O37" s="149"/>
-      <c r="P37" s="149"/>
+      <c r="O37" s="160"/>
+      <c r="P37" s="160"/>
       <c r="Q37" s="69" t="s">
         <v>80</v>
       </c>
@@ -3935,17 +5122,21 @@
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="G27:K27"/>
     <mergeCell ref="G34:K34"/>
     <mergeCell ref="Q34:R34"/>
     <mergeCell ref="H35:K35"/>
     <mergeCell ref="M35:P35"/>
     <mergeCell ref="N37:P37"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="Q19:R19"/>
     <mergeCell ref="A18:A22"/>
     <mergeCell ref="C30:G30"/>
     <mergeCell ref="I30:L30"/>
@@ -3953,20 +5144,16 @@
     <mergeCell ref="G28:J28"/>
     <mergeCell ref="K28:N28"/>
     <mergeCell ref="C27:E27"/>
-    <mergeCell ref="G27:I27"/>
     <mergeCell ref="C29:F29"/>
     <mergeCell ref="G29:J29"/>
     <mergeCell ref="K29:N29"/>
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="C21:F21"/>
     <mergeCell ref="C22:G22"/>
     <mergeCell ref="I22:L22"/>
     <mergeCell ref="G21:J21"/>
     <mergeCell ref="K21:N21"/>
     <mergeCell ref="C19:E19"/>
     <mergeCell ref="C20:R20"/>
+    <mergeCell ref="Q19:R19"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/can上层通信协议.xlsx
+++ b/can上层通信协议.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Dev\FanArray\CODE\FA_Ctrl\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{027AF4B7-2394-4739-97FF-F1C17BC8269F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{75231C8B-79A3-4A3D-9826-51888C50038F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="29020" windowHeight="18220" xr2:uid="{33FD23F6-9F23-4515-98A3-37DCFD7DD961}"/>
+    <workbookView xWindow="3550" yWindow="1400" windowWidth="21600" windowHeight="13210" xr2:uid="{33FD23F6-9F23-4515-98A3-37DCFD7DD961}"/>
   </bookViews>
   <sheets>
     <sheet name="通信协议" sheetId="3" r:id="rId1"/>
-    <sheet name="通信协议-old" sheetId="1" r:id="rId2"/>
-    <sheet name="oled配置" sheetId="2" r:id="rId3"/>
+    <sheet name="oled配置" sheetId="2" r:id="rId2"/>
+    <sheet name="通信协议-old" sheetId="1" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -74,7 +74,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="117">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="265" uniqueCount="118">
   <si>
     <t>遥控帧</t>
     <phoneticPr fontId="6" type="noConversion"/>
@@ -608,6 +608,10 @@
 MASK=0x00F</t>
     <phoneticPr fontId="6" type="noConversion"/>
   </si>
+  <si>
+    <t>07F</t>
+    <phoneticPr fontId="6" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -616,7 +620,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_ &quot;¥&quot;* #,##0.00_ ;_ &quot;¥&quot;* \-#,##0.00_ ;_ &quot;¥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -708,12 +712,6 @@
       <color theme="1"/>
       <name val="微软雅黑"/>
       <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color indexed="81"/>
-      <name val="宋体"/>
       <charset val="134"/>
     </font>
   </fonts>
@@ -1495,7 +1493,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="252">
+  <cellXfs count="249">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1772,13 +1770,313 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="4" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1790,163 +2088,148 @@
     <xf numFmtId="0" fontId="0" fillId="15" borderId="10" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="24" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="42" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="34" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="35" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="15" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="38" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="14" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="15" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1957,300 +2240,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="24" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="50" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="17" borderId="5" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="49" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="43" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="44" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="2" fillId="8" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="40" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="17" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="27" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="1" fillId="4" borderId="26" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="4" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="36" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="23" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="48" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="5" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="22" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="39" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="46" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="18" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="17" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="28" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="52" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="53" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="20" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="21" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="22" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="16" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="22" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="5" borderId="54" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="20" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="20" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="22" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="48" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="48" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="48" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="26" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="55" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="48" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -3084,355 +3073,347 @@
     <row r="3" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
       <c r="D3" s="91"/>
       <c r="E3" s="91"/>
-      <c r="F3" s="212" t="s">
+      <c r="F3" s="109" t="s">
         <v>55</v>
       </c>
-      <c r="G3" s="177" t="s">
+      <c r="G3" s="92" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="178" t="s">
+      <c r="H3" s="133" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="179"/>
-      <c r="J3" s="180"/>
-      <c r="K3" s="181" t="s">
+      <c r="I3" s="134"/>
+      <c r="J3" s="135"/>
+      <c r="K3" s="93" t="s">
         <v>2</v>
       </c>
-      <c r="L3" s="182" t="s">
+      <c r="L3" s="94" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="243" t="s">
+      <c r="M3" s="126" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="213" t="s">
+      <c r="N3" s="110" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="4:16" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D4" s="244"/>
-      <c r="E4" s="174" t="s">
+      <c r="D4" s="91"/>
+      <c r="E4" s="141" t="s">
         <v>8</v>
       </c>
-      <c r="F4" s="156">
+      <c r="F4" s="148">
         <v>2</v>
       </c>
-      <c r="G4" s="183" t="s">
+      <c r="G4" s="151" t="s">
         <v>63</v>
       </c>
-      <c r="H4" s="220" t="s">
+      <c r="H4" s="138" t="s">
         <v>111</v>
       </c>
       <c r="I4" s="88"/>
-      <c r="J4" s="184" t="s">
+      <c r="J4" s="95" t="s">
         <v>56</v>
       </c>
-      <c r="K4" s="214" t="s">
+      <c r="K4" s="111" t="s">
         <v>57</v>
       </c>
-      <c r="L4" s="185" t="s">
+      <c r="L4" s="146" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="205" t="s">
+      <c r="M4" s="201" t="s">
         <v>114</v>
       </c>
-      <c r="N4" s="186" t="s">
+      <c r="N4" s="207" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D5" s="244"/>
-      <c r="E5" s="175"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="187"/>
-      <c r="H5" s="221"/>
+      <c r="D5" s="91"/>
+      <c r="E5" s="142"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="152"/>
+      <c r="H5" s="139"/>
       <c r="I5" s="89"/>
-      <c r="J5" s="188" t="s">
+      <c r="J5" s="144" t="s">
         <v>50</v>
       </c>
-      <c r="K5" s="208" t="s">
+      <c r="K5" s="96" t="s">
         <v>60</v>
       </c>
-      <c r="L5" s="189"/>
-      <c r="M5" s="206"/>
-      <c r="N5" s="190"/>
+      <c r="L5" s="147"/>
+      <c r="M5" s="202"/>
+      <c r="N5" s="178"/>
     </row>
     <row r="6" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D6" s="244"/>
-      <c r="E6" s="175"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="187"/>
-      <c r="H6" s="221"/>
+      <c r="D6" s="91"/>
+      <c r="E6" s="142"/>
+      <c r="F6" s="149"/>
+      <c r="G6" s="152"/>
+      <c r="H6" s="139"/>
       <c r="I6" s="89"/>
-      <c r="J6" s="188"/>
-      <c r="K6" s="208" t="s">
+      <c r="J6" s="144"/>
+      <c r="K6" s="96" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="189"/>
-      <c r="M6" s="206"/>
-      <c r="N6" s="190"/>
+      <c r="L6" s="147"/>
+      <c r="M6" s="202"/>
+      <c r="N6" s="178"/>
     </row>
     <row r="7" spans="4:16" ht="49.5" x14ac:dyDescent="0.45">
-      <c r="D7" s="244"/>
-      <c r="E7" s="175"/>
-      <c r="F7" s="157"/>
-      <c r="G7" s="187"/>
-      <c r="H7" s="221"/>
+      <c r="D7" s="91"/>
+      <c r="E7" s="142"/>
+      <c r="F7" s="149"/>
+      <c r="G7" s="152"/>
+      <c r="H7" s="139"/>
       <c r="I7" s="89"/>
-      <c r="J7" s="188"/>
-      <c r="K7" s="208" t="s">
+      <c r="J7" s="144"/>
+      <c r="K7" s="96" t="s">
         <v>113</v>
       </c>
-      <c r="L7" s="189"/>
-      <c r="M7" s="206"/>
-      <c r="N7" s="190"/>
+      <c r="L7" s="147"/>
+      <c r="M7" s="202"/>
+      <c r="N7" s="178"/>
     </row>
     <row r="8" spans="4:16" ht="47.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D8" s="244"/>
-      <c r="E8" s="175"/>
-      <c r="F8" s="158"/>
-      <c r="G8" s="191"/>
-      <c r="H8" s="221"/>
+      <c r="D8" s="91"/>
+      <c r="E8" s="142"/>
+      <c r="F8" s="150"/>
+      <c r="G8" s="153"/>
+      <c r="H8" s="139"/>
       <c r="I8" s="9"/>
-      <c r="J8" s="192"/>
-      <c r="K8" s="204" t="s">
+      <c r="J8" s="145"/>
+      <c r="K8" s="105" t="s">
         <v>112</v>
       </c>
-      <c r="L8" s="189"/>
-      <c r="M8" s="206"/>
-      <c r="N8" s="218" t="s">
+      <c r="L8" s="147"/>
+      <c r="M8" s="202"/>
+      <c r="N8" s="177" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="4:16" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D9" s="244"/>
-      <c r="E9" s="175"/>
-      <c r="F9" s="250">
+      <c r="D9" s="91"/>
+      <c r="E9" s="142"/>
+      <c r="F9" s="131">
         <v>8</v>
       </c>
-      <c r="G9" s="246" t="s">
+      <c r="G9" s="127" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="221"/>
+      <c r="H9" s="139"/>
       <c r="I9" s="89"/>
-      <c r="J9" s="247" t="s">
+      <c r="J9" s="128" t="s">
         <v>64</v>
       </c>
-      <c r="K9" s="248" t="s">
+      <c r="K9" s="129" t="s">
         <v>69</v>
       </c>
-      <c r="L9" s="249" t="s">
+      <c r="L9" s="130" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="206"/>
-      <c r="N9" s="190"/>
+      <c r="M9" s="202"/>
+      <c r="N9" s="178"/>
       <c r="P9" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="4:16" ht="3" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D10" s="244"/>
-      <c r="E10" s="175"/>
-      <c r="F10" s="203"/>
-      <c r="G10" s="210" t="s">
+      <c r="D10" s="91"/>
+      <c r="E10" s="142"/>
+      <c r="F10" s="104"/>
+      <c r="G10" s="107" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="221"/>
+      <c r="H10" s="139"/>
       <c r="I10" s="89"/>
-      <c r="J10" s="194" t="s">
+      <c r="J10" s="99" t="s">
         <v>15</v>
       </c>
-      <c r="K10" s="215" t="s">
+      <c r="K10" s="112" t="s">
         <v>16</v>
       </c>
-      <c r="L10" s="195" t="s">
+      <c r="L10" s="100" t="s">
         <v>18</v>
       </c>
-      <c r="M10" s="206"/>
-      <c r="N10" s="190"/>
+      <c r="M10" s="202"/>
+      <c r="N10" s="178"/>
     </row>
     <row r="11" spans="4:16" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="D11" s="244"/>
-      <c r="E11" s="175"/>
-      <c r="F11" s="196">
+      <c r="D11" s="91"/>
+      <c r="E11" s="142"/>
+      <c r="F11" s="101">
         <v>2</v>
       </c>
-      <c r="G11" s="211" t="s">
+      <c r="G11" s="108" t="s">
         <v>6</v>
       </c>
-      <c r="H11" s="221"/>
+      <c r="H11" s="139"/>
       <c r="I11" s="89"/>
-      <c r="J11" s="193" t="s">
+      <c r="J11" s="98" t="s">
         <v>73</v>
       </c>
       <c r="K11" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="L11" s="251">
+      <c r="L11" s="132">
         <v>2</v>
       </c>
-      <c r="M11" s="206"/>
-      <c r="N11" s="219"/>
+      <c r="M11" s="202"/>
+      <c r="N11" s="179"/>
     </row>
     <row r="12" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D12" s="244"/>
-      <c r="E12" s="175"/>
-      <c r="F12" s="197">
+      <c r="D12" s="91"/>
+      <c r="E12" s="142"/>
+      <c r="F12" s="208">
         <v>8</v>
       </c>
-      <c r="G12" s="211" t="s">
+      <c r="G12" s="108" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="221"/>
+      <c r="H12" s="139"/>
       <c r="I12" s="89"/>
-      <c r="J12" s="198" t="s">
+      <c r="J12" s="102" t="s">
         <v>72</v>
       </c>
-      <c r="K12" s="199" t="s">
+      <c r="K12" s="210" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="154" t="s">
+      <c r="L12" s="190" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="206"/>
-      <c r="N12" s="216" t="s">
+      <c r="M12" s="202"/>
+      <c r="N12" s="97" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="13" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D13" s="244"/>
-      <c r="E13" s="176"/>
-      <c r="F13" s="200"/>
-      <c r="G13" s="209" t="s">
+      <c r="D13" s="91"/>
+      <c r="E13" s="143"/>
+      <c r="F13" s="209"/>
+      <c r="G13" s="106" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="222"/>
+      <c r="H13" s="140"/>
       <c r="I13" s="90"/>
-      <c r="J13" s="201" t="s">
+      <c r="J13" s="103" t="s">
         <v>74</v>
       </c>
-      <c r="K13" s="202"/>
-      <c r="L13" s="155"/>
-      <c r="M13" s="207"/>
-      <c r="N13" s="217"/>
+      <c r="K13" s="211"/>
+      <c r="L13" s="191"/>
+      <c r="M13" s="203"/>
+      <c r="N13" s="113"/>
     </row>
     <row r="14" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D14" s="245"/>
       <c r="H14" s="1"/>
       <c r="I14" s="1"/>
     </row>
     <row r="15" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D15" s="245"/>
       <c r="H15" s="1"/>
       <c r="I15" s="1"/>
     </row>
     <row r="16" spans="4:16" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D16" s="245"/>
-      <c r="E16" s="148" t="s">
+      <c r="E16" s="192" t="s">
         <v>9</v>
       </c>
-      <c r="F16" s="231">
+      <c r="F16" s="118">
         <v>8</v>
       </c>
       <c r="G16" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="H16" s="223" t="s">
-        <v>43</v>
+      <c r="H16" s="180" t="s">
+        <v>117</v>
       </c>
       <c r="I16" s="50"/>
-      <c r="J16" s="225" t="s">
+      <c r="J16" s="114" t="s">
         <v>92</v>
       </c>
-      <c r="K16" s="230" t="s">
+      <c r="K16" s="117" t="s">
         <v>93</v>
       </c>
-      <c r="L16" s="232">
+      <c r="L16" s="119">
         <v>2</v>
       </c>
-      <c r="M16" s="240" t="s">
+      <c r="M16" s="204" t="s">
         <v>116</v>
       </c>
-      <c r="N16" s="239"/>
-    </row>
-    <row r="17" spans="4:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D17" s="245"/>
-      <c r="E17" s="228"/>
-      <c r="F17" s="237">
+    </row>
+    <row r="17" spans="4:13" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E17" s="193"/>
+      <c r="F17" s="124">
         <v>8</v>
       </c>
-      <c r="G17" s="236" t="s">
+      <c r="G17" s="123" t="s">
         <v>59</v>
       </c>
-      <c r="H17" s="229"/>
+      <c r="H17" s="181"/>
       <c r="I17" s="9"/>
-      <c r="J17" s="227" t="s">
+      <c r="J17" s="116" t="s">
         <v>65</v>
       </c>
-      <c r="K17" s="235" t="s">
+      <c r="K17" s="122" t="s">
         <v>67</v>
       </c>
-      <c r="L17" s="238"/>
-      <c r="M17" s="241"/>
-      <c r="N17" s="239"/>
-    </row>
-    <row r="18" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D18" s="245"/>
-      <c r="E18" s="150"/>
-      <c r="F18" s="233">
+      <c r="L17" s="125"/>
+      <c r="M17" s="205"/>
+    </row>
+    <row r="18" spans="4:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="E18" s="194"/>
+      <c r="F18" s="120">
         <v>1</v>
       </c>
       <c r="G18" s="6" t="s">
         <v>115</v>
       </c>
-      <c r="H18" s="224"/>
+      <c r="H18" s="182"/>
       <c r="I18" s="51"/>
-      <c r="J18" s="226" t="s">
+      <c r="J18" s="115" t="s">
         <v>58</v>
       </c>
       <c r="K18" s="87" t="s">
         <v>91</v>
       </c>
-      <c r="L18" s="234"/>
-      <c r="M18" s="242"/>
-      <c r="N18" s="239"/>
-    </row>
-    <row r="23" spans="4:14" x14ac:dyDescent="0.45">
+      <c r="L18" s="121"/>
+      <c r="M18" s="206"/>
+    </row>
+    <row r="23" spans="4:13" x14ac:dyDescent="0.45">
       <c r="H23" s="9"/>
       <c r="I23" s="9"/>
     </row>
-    <row r="24" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="24" spans="4:13" x14ac:dyDescent="0.45">
       <c r="H24" s="9"/>
       <c r="I24" s="9"/>
     </row>
-    <row r="25" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="25" spans="4:13" x14ac:dyDescent="0.45">
       <c r="H25" s="9"/>
       <c r="I25" s="9"/>
     </row>
-    <row r="26" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="26" spans="4:13" x14ac:dyDescent="0.45">
       <c r="H26" s="9"/>
       <c r="I26" s="9"/>
     </row>
-    <row r="27" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="27" spans="4:13" x14ac:dyDescent="0.45">
       <c r="H27" s="9"/>
       <c r="I27" s="9"/>
     </row>
-    <row r="28" spans="4:14" x14ac:dyDescent="0.45">
+    <row r="28" spans="4:13" x14ac:dyDescent="0.45">
       <c r="H28" s="9"/>
       <c r="I28" s="9"/>
     </row>
-    <row r="29" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
-    <row r="30" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D30" s="95"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="97"/>
+    <row r="29" spans="4:13" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
+    <row r="30" spans="4:13" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="D30" s="195"/>
+      <c r="E30" s="196"/>
+      <c r="F30" s="197"/>
       <c r="G30" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="119" t="s">
+      <c r="H30" s="198" t="s">
         <v>3</v>
       </c>
-      <c r="I30" s="120"/>
-      <c r="J30" s="121"/>
+      <c r="I30" s="199"/>
+      <c r="J30" s="200"/>
       <c r="K30" s="11" t="s">
         <v>2</v>
       </c>
@@ -3440,89 +3421,89 @@
         <v>29</v>
       </c>
     </row>
-    <row r="31" spans="4:14" x14ac:dyDescent="0.45">
-      <c r="D31" s="93" t="s">
+    <row r="31" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D31" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="123" t="s">
+      <c r="E31" s="155" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="125" t="s">
+      <c r="F31" s="157" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="128" t="s">
+      <c r="H31" s="160" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="129"/>
+      <c r="I31" s="161"/>
       <c r="J31" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="K31" s="98" t="s">
+      <c r="K31" s="164" t="s">
         <v>52</v>
       </c>
-      <c r="L31" s="98">
+      <c r="L31" s="164">
         <v>1</v>
       </c>
     </row>
-    <row r="32" spans="4:14" x14ac:dyDescent="0.45">
-      <c r="D32" s="122"/>
-      <c r="E32" s="124"/>
-      <c r="F32" s="126"/>
+    <row r="32" spans="4:13" x14ac:dyDescent="0.45">
+      <c r="D32" s="154"/>
+      <c r="E32" s="156"/>
+      <c r="F32" s="158"/>
       <c r="G32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="109"/>
-      <c r="I32" s="110"/>
+      <c r="H32" s="162"/>
+      <c r="I32" s="163"/>
       <c r="J32" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K32" s="99"/>
-      <c r="L32" s="99"/>
+      <c r="K32" s="165"/>
+      <c r="L32" s="165"/>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D33" s="122"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="126"/>
+      <c r="D33" s="154"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="158"/>
       <c r="G33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H33" s="109"/>
-      <c r="I33" s="110"/>
+      <c r="H33" s="162"/>
+      <c r="I33" s="163"/>
       <c r="J33" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="99"/>
-      <c r="L33" s="99"/>
+      <c r="K33" s="165"/>
+      <c r="L33" s="165"/>
     </row>
     <row r="34" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D34" s="122"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="127"/>
+      <c r="D34" s="154"/>
+      <c r="E34" s="156"/>
+      <c r="F34" s="159"/>
       <c r="G34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="109"/>
-      <c r="I34" s="110"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="163"/>
       <c r="J34" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="100"/>
-      <c r="L34" s="100"/>
+      <c r="K34" s="166"/>
+      <c r="L34" s="166"/>
     </row>
     <row r="35" spans="4:12" ht="33" x14ac:dyDescent="0.45">
-      <c r="D35" s="122"/>
-      <c r="E35" s="124"/>
-      <c r="F35" s="101" t="s">
+      <c r="D35" s="154"/>
+      <c r="E35" s="156"/>
+      <c r="F35" s="167" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H35" s="109"/>
-      <c r="I35" s="110"/>
+      <c r="H35" s="162"/>
+      <c r="I35" s="163"/>
       <c r="J35" s="40" t="s">
         <v>34</v>
       </c>
@@ -3534,14 +3515,14 @@
       </c>
     </row>
     <row r="36" spans="4:12" ht="31.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D36" s="122"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="102"/>
+      <c r="D36" s="154"/>
+      <c r="E36" s="156"/>
+      <c r="F36" s="168"/>
       <c r="G36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H36" s="109"/>
-      <c r="I36" s="110"/>
+      <c r="H36" s="162"/>
+      <c r="I36" s="163"/>
       <c r="J36" s="41" t="s">
         <v>35</v>
       </c>
@@ -3553,14 +3534,14 @@
       </c>
     </row>
     <row r="37" spans="4:12" ht="1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D37" s="122"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="103"/>
+      <c r="D37" s="154"/>
+      <c r="E37" s="156"/>
+      <c r="F37" s="169"/>
       <c r="G37" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="109"/>
-      <c r="I37" s="110"/>
+      <c r="H37" s="162"/>
+      <c r="I37" s="163"/>
       <c r="J37" s="8" t="s">
         <v>15</v>
       </c>
@@ -3572,8 +3553,8 @@
       </c>
     </row>
     <row r="38" spans="4:12" ht="17" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="D38" s="122"/>
-      <c r="E38" s="104" t="s">
+      <c r="D38" s="154"/>
+      <c r="E38" s="170" t="s">
         <v>5</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -3582,10 +3563,10 @@
       <c r="G38" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="107" t="s">
+      <c r="H38" s="173" t="s">
         <v>53</v>
       </c>
-      <c r="I38" s="108"/>
+      <c r="I38" s="174"/>
       <c r="J38" s="42" t="s">
         <v>50</v>
       </c>
@@ -3597,65 +3578,65 @@
       </c>
     </row>
     <row r="39" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D39" s="122"/>
-      <c r="E39" s="105"/>
-      <c r="F39" s="113" t="s">
+      <c r="D39" s="154"/>
+      <c r="E39" s="171"/>
+      <c r="F39" s="188" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H39" s="109"/>
-      <c r="I39" s="110"/>
+      <c r="H39" s="162"/>
+      <c r="I39" s="163"/>
       <c r="J39" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="115" t="s">
+      <c r="K39" s="183" t="s">
         <v>38</v>
       </c>
-      <c r="L39" s="117">
+      <c r="L39" s="185">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="94"/>
-      <c r="E40" s="106"/>
-      <c r="F40" s="114"/>
+      <c r="D40" s="137"/>
+      <c r="E40" s="172"/>
+      <c r="F40" s="189"/>
       <c r="G40" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H40" s="111"/>
-      <c r="I40" s="112"/>
+      <c r="H40" s="175"/>
+      <c r="I40" s="176"/>
       <c r="J40" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="K40" s="116"/>
-      <c r="L40" s="118"/>
+      <c r="K40" s="184"/>
+      <c r="L40" s="186"/>
     </row>
     <row r="41" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="92"/>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="92"/>
+      <c r="D41" s="187"/>
+      <c r="E41" s="187"/>
+      <c r="F41" s="187"/>
+      <c r="G41" s="187"/>
+      <c r="H41" s="187"/>
+      <c r="I41" s="187"/>
+      <c r="J41" s="187"/>
+      <c r="K41" s="187"/>
+      <c r="L41" s="187"/>
     </row>
     <row r="42" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D42" s="92"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="92"/>
-      <c r="G42" s="92"/>
-      <c r="H42" s="92"/>
-      <c r="I42" s="92"/>
-      <c r="J42" s="92"/>
-      <c r="K42" s="92"/>
-      <c r="L42" s="92"/>
+      <c r="D42" s="187"/>
+      <c r="E42" s="187"/>
+      <c r="F42" s="187"/>
+      <c r="G42" s="187"/>
+      <c r="H42" s="187"/>
+      <c r="I42" s="187"/>
+      <c r="J42" s="187"/>
+      <c r="K42" s="187"/>
+      <c r="L42" s="187"/>
     </row>
     <row r="43" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D43" s="93" t="s">
+      <c r="D43" s="136" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="25"/>
@@ -3680,7 +3661,7 @@
       </c>
     </row>
     <row r="44" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D44" s="94"/>
+      <c r="D44" s="137"/>
       <c r="E44" s="25"/>
       <c r="F44" s="46" t="s">
         <v>0</v>
@@ -3709,10 +3690,16 @@
     <mergeCell ref="K39:K40"/>
     <mergeCell ref="L39:L40"/>
     <mergeCell ref="D41:L42"/>
-    <mergeCell ref="D43:D44"/>
-    <mergeCell ref="H4:H13"/>
-    <mergeCell ref="E4:E13"/>
-    <mergeCell ref="J5:J8"/>
+    <mergeCell ref="F39:F40"/>
+    <mergeCell ref="L12:L13"/>
+    <mergeCell ref="E16:E18"/>
+    <mergeCell ref="D30:F30"/>
+    <mergeCell ref="H30:J30"/>
+    <mergeCell ref="M4:M13"/>
+    <mergeCell ref="M16:M18"/>
+    <mergeCell ref="N4:N7"/>
+    <mergeCell ref="F12:F13"/>
+    <mergeCell ref="K12:K13"/>
     <mergeCell ref="L4:L8"/>
     <mergeCell ref="F4:F8"/>
     <mergeCell ref="G4:G8"/>
@@ -3725,17 +3712,11 @@
     <mergeCell ref="F35:F37"/>
     <mergeCell ref="E38:E40"/>
     <mergeCell ref="H38:I40"/>
-    <mergeCell ref="F39:F40"/>
-    <mergeCell ref="L12:L13"/>
-    <mergeCell ref="E16:E18"/>
-    <mergeCell ref="D30:F30"/>
-    <mergeCell ref="H30:J30"/>
-    <mergeCell ref="M4:M13"/>
-    <mergeCell ref="M16:M18"/>
-    <mergeCell ref="N4:N7"/>
-    <mergeCell ref="F12:F13"/>
-    <mergeCell ref="K12:K13"/>
     <mergeCell ref="H3:J3"/>
+    <mergeCell ref="D43:D44"/>
+    <mergeCell ref="H4:H13"/>
+    <mergeCell ref="E4:E13"/>
+    <mergeCell ref="J5:J8"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3745,6 +3726,689 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8521510C-1B37-40AB-AFA2-021412ADBA84}">
+  <dimension ref="A4:AB37"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="3" max="18" width="2.765625" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A4" s="86"/>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="C5" s="84"/>
+      <c r="D5" s="84"/>
+      <c r="E5" s="84"/>
+      <c r="G5" s="84"/>
+      <c r="H5" s="84"/>
+      <c r="I5" s="84"/>
+      <c r="K5" s="85"/>
+      <c r="M5" s="76"/>
+      <c r="Q5"/>
+      <c r="R5"/>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="C6" s="84"/>
+      <c r="D6" s="84"/>
+      <c r="E6" s="84"/>
+      <c r="F6" s="84"/>
+      <c r="G6" s="84"/>
+      <c r="H6" s="84"/>
+      <c r="I6" s="84"/>
+      <c r="J6" s="84"/>
+      <c r="K6" s="84"/>
+      <c r="L6" s="84"/>
+      <c r="M6" s="84"/>
+      <c r="N6" s="84"/>
+      <c r="O6" s="84"/>
+      <c r="P6" s="84"/>
+      <c r="Q6" s="84"/>
+      <c r="R6" s="84"/>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="C7"/>
+      <c r="D7"/>
+      <c r="E7"/>
+      <c r="F7"/>
+      <c r="H7"/>
+      <c r="I7"/>
+      <c r="J7"/>
+      <c r="K7"/>
+      <c r="M7"/>
+      <c r="N7"/>
+      <c r="O7"/>
+      <c r="P7"/>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="C8" s="84"/>
+      <c r="D8" s="84"/>
+      <c r="E8" s="84"/>
+      <c r="F8" s="84"/>
+      <c r="G8" s="84"/>
+      <c r="I8" s="84"/>
+      <c r="J8" s="84"/>
+      <c r="K8" s="84"/>
+      <c r="L8" s="84"/>
+    </row>
+    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A12" s="86" t="s">
+        <v>87</v>
+      </c>
+      <c r="C12" s="84"/>
+      <c r="D12" s="84"/>
+      <c r="E12" s="84"/>
+      <c r="G12" s="84"/>
+      <c r="H12" s="84"/>
+      <c r="I12" s="84"/>
+      <c r="K12" s="85"/>
+      <c r="M12" s="76"/>
+      <c r="Q12"/>
+      <c r="R12"/>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="C13" s="84"/>
+      <c r="D13" s="84"/>
+      <c r="E13" s="84"/>
+      <c r="F13" s="84"/>
+      <c r="G13" s="84"/>
+      <c r="H13" s="84"/>
+      <c r="I13" s="84"/>
+      <c r="J13" s="84"/>
+      <c r="K13" s="84"/>
+      <c r="L13" s="84"/>
+      <c r="M13" s="84"/>
+      <c r="N13" s="84"/>
+      <c r="O13" s="84"/>
+      <c r="P13" s="84"/>
+      <c r="Q13" s="84"/>
+      <c r="R13" s="84"/>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="C14"/>
+      <c r="D14"/>
+      <c r="E14"/>
+      <c r="F14"/>
+      <c r="H14"/>
+      <c r="I14"/>
+      <c r="J14"/>
+      <c r="K14"/>
+      <c r="M14"/>
+      <c r="N14"/>
+      <c r="O14"/>
+      <c r="P14"/>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="C15" s="84"/>
+      <c r="D15" s="84"/>
+      <c r="E15" s="84"/>
+      <c r="F15" s="84"/>
+      <c r="G15" s="84"/>
+      <c r="I15" s="84"/>
+      <c r="J15" s="84"/>
+      <c r="K15" s="84"/>
+      <c r="L15" s="84"/>
+    </row>
+    <row r="18" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A18" s="226" t="s">
+        <v>87</v>
+      </c>
+      <c r="C18" s="1">
+        <v>1</v>
+      </c>
+      <c r="D18" s="1">
+        <v>2</v>
+      </c>
+      <c r="E18" s="1">
+        <v>3</v>
+      </c>
+      <c r="F18" s="1">
+        <v>4</v>
+      </c>
+      <c r="G18" s="1">
+        <v>5</v>
+      </c>
+      <c r="H18" s="1">
+        <v>6</v>
+      </c>
+      <c r="I18" s="1">
+        <v>7</v>
+      </c>
+      <c r="J18" s="1">
+        <v>8</v>
+      </c>
+      <c r="K18" s="1">
+        <v>9</v>
+      </c>
+      <c r="L18" s="1">
+        <v>10</v>
+      </c>
+      <c r="M18" s="1">
+        <v>11</v>
+      </c>
+      <c r="N18" s="1">
+        <v>12</v>
+      </c>
+      <c r="O18" s="1">
+        <v>13</v>
+      </c>
+      <c r="P18" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q18" s="1">
+        <v>15</v>
+      </c>
+      <c r="R18" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A19" s="187"/>
+      <c r="B19">
+        <v>1</v>
+      </c>
+      <c r="C19" s="213" t="s">
+        <v>107</v>
+      </c>
+      <c r="D19" s="214"/>
+      <c r="E19" s="214"/>
+      <c r="F19" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="G19" s="77"/>
+      <c r="H19" s="77"/>
+      <c r="I19" s="77"/>
+      <c r="J19" s="71"/>
+      <c r="K19" s="78"/>
+      <c r="L19" s="71"/>
+      <c r="M19" s="75"/>
+      <c r="N19" s="71"/>
+      <c r="O19" s="71"/>
+      <c r="P19" s="71"/>
+      <c r="Q19" s="218"/>
+      <c r="R19" s="219"/>
+    </row>
+    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A20" s="187"/>
+      <c r="B20">
+        <v>2</v>
+      </c>
+      <c r="C20" s="215" t="s">
+        <v>82</v>
+      </c>
+      <c r="D20" s="216"/>
+      <c r="E20" s="216"/>
+      <c r="F20" s="216"/>
+      <c r="G20" s="216"/>
+      <c r="H20" s="216"/>
+      <c r="I20" s="216"/>
+      <c r="J20" s="216"/>
+      <c r="K20" s="216"/>
+      <c r="L20" s="216"/>
+      <c r="M20" s="216"/>
+      <c r="N20" s="216"/>
+      <c r="O20" s="216"/>
+      <c r="P20" s="216"/>
+      <c r="Q20" s="216"/>
+      <c r="R20" s="217"/>
+    </row>
+    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A21" s="187"/>
+      <c r="B21">
+        <v>3</v>
+      </c>
+      <c r="C21" s="220" t="s">
+        <v>106</v>
+      </c>
+      <c r="D21" s="212"/>
+      <c r="E21" s="212"/>
+      <c r="F21" s="212"/>
+      <c r="G21" s="212" t="s">
+        <v>84</v>
+      </c>
+      <c r="H21" s="212"/>
+      <c r="I21" s="212"/>
+      <c r="J21" s="212"/>
+      <c r="K21" s="212" t="s">
+        <v>85</v>
+      </c>
+      <c r="L21" s="212"/>
+      <c r="M21" s="212"/>
+      <c r="N21" s="212"/>
+      <c r="O21" s="212" t="s">
+        <v>86</v>
+      </c>
+      <c r="P21" s="212"/>
+      <c r="Q21" s="212"/>
+      <c r="R21" s="224"/>
+    </row>
+    <row r="22" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A22" s="187"/>
+      <c r="B22">
+        <v>4</v>
+      </c>
+      <c r="C22" s="221" t="s">
+        <v>83</v>
+      </c>
+      <c r="D22" s="222"/>
+      <c r="E22" s="222"/>
+      <c r="F22" s="222"/>
+      <c r="G22" s="222"/>
+      <c r="H22" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="I22" s="222" t="s">
+        <v>97</v>
+      </c>
+      <c r="J22" s="222"/>
+      <c r="K22" s="222"/>
+      <c r="L22" s="222"/>
+      <c r="M22" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="N22" s="69"/>
+      <c r="O22" s="69"/>
+      <c r="P22" s="69"/>
+      <c r="Q22" s="69"/>
+      <c r="R22" s="15"/>
+    </row>
+    <row r="26" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C26" s="1">
+        <v>1</v>
+      </c>
+      <c r="D26" s="1">
+        <v>2</v>
+      </c>
+      <c r="E26" s="1">
+        <v>3</v>
+      </c>
+      <c r="F26" s="1">
+        <v>4</v>
+      </c>
+      <c r="G26" s="1">
+        <v>5</v>
+      </c>
+      <c r="H26" s="1">
+        <v>6</v>
+      </c>
+      <c r="I26" s="1">
+        <v>7</v>
+      </c>
+      <c r="J26" s="1">
+        <v>8</v>
+      </c>
+      <c r="K26" s="1">
+        <v>9</v>
+      </c>
+      <c r="L26" s="1">
+        <v>10</v>
+      </c>
+      <c r="M26" s="1">
+        <v>11</v>
+      </c>
+      <c r="N26" s="1">
+        <v>12</v>
+      </c>
+      <c r="O26" s="1">
+        <v>13</v>
+      </c>
+      <c r="P26" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q26" s="1">
+        <v>15</v>
+      </c>
+      <c r="R26" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A27" s="187" t="s">
+        <v>96</v>
+      </c>
+      <c r="B27">
+        <v>1</v>
+      </c>
+      <c r="C27" s="213" t="s">
+        <v>109</v>
+      </c>
+      <c r="D27" s="214"/>
+      <c r="E27" s="214"/>
+      <c r="F27" s="71"/>
+      <c r="G27" s="214" t="s">
+        <v>108</v>
+      </c>
+      <c r="H27" s="214"/>
+      <c r="I27" s="214"/>
+      <c r="J27" s="214"/>
+      <c r="K27" s="214"/>
+      <c r="L27" s="71"/>
+      <c r="M27" s="71"/>
+      <c r="N27" s="71"/>
+      <c r="O27" s="71"/>
+      <c r="P27" s="71"/>
+      <c r="Q27" s="71"/>
+      <c r="R27" s="72"/>
+    </row>
+    <row r="28" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A28" s="187"/>
+      <c r="B28">
+        <v>2</v>
+      </c>
+      <c r="C28" s="223" t="s">
+        <v>89</v>
+      </c>
+      <c r="D28" s="187"/>
+      <c r="E28" s="187"/>
+      <c r="F28" s="187"/>
+      <c r="G28" s="187" t="s">
+        <v>84</v>
+      </c>
+      <c r="H28" s="187"/>
+      <c r="I28" s="187"/>
+      <c r="J28" s="187"/>
+      <c r="K28" s="187" t="s">
+        <v>85</v>
+      </c>
+      <c r="L28" s="187"/>
+      <c r="M28" s="187"/>
+      <c r="N28" s="187"/>
+      <c r="O28" s="187" t="s">
+        <v>86</v>
+      </c>
+      <c r="P28" s="187"/>
+      <c r="Q28" s="187"/>
+      <c r="R28" s="225"/>
+    </row>
+    <row r="29" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="A29" s="187"/>
+      <c r="B29">
+        <v>3</v>
+      </c>
+      <c r="C29" s="220" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="212"/>
+      <c r="E29" s="212"/>
+      <c r="F29" s="212"/>
+      <c r="G29" s="212" t="s">
+        <v>84</v>
+      </c>
+      <c r="H29" s="212"/>
+      <c r="I29" s="212"/>
+      <c r="J29" s="212"/>
+      <c r="K29" s="212" t="s">
+        <v>85</v>
+      </c>
+      <c r="L29" s="212"/>
+      <c r="M29" s="212"/>
+      <c r="N29" s="212"/>
+      <c r="O29" s="212" t="s">
+        <v>86</v>
+      </c>
+      <c r="P29" s="212"/>
+      <c r="Q29" s="212"/>
+      <c r="R29" s="224"/>
+    </row>
+    <row r="30" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A30" s="187"/>
+      <c r="B30">
+        <v>4</v>
+      </c>
+      <c r="C30" s="221" t="s">
+        <v>83</v>
+      </c>
+      <c r="D30" s="222"/>
+      <c r="E30" s="222"/>
+      <c r="F30" s="222"/>
+      <c r="G30" s="222"/>
+      <c r="H30" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="I30" s="222" t="s">
+        <v>97</v>
+      </c>
+      <c r="J30" s="222"/>
+      <c r="K30" s="222"/>
+      <c r="L30" s="222"/>
+      <c r="M30" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="N30" s="69"/>
+      <c r="O30" s="79"/>
+      <c r="P30" s="79"/>
+      <c r="Q30" s="69"/>
+      <c r="R30" s="15"/>
+    </row>
+    <row r="31" spans="1:28" x14ac:dyDescent="0.45">
+      <c r="V31" s="73"/>
+      <c r="W31" s="1"/>
+      <c r="X31" s="1"/>
+      <c r="Y31" s="1"/>
+      <c r="Z31" s="1"/>
+      <c r="AA31" s="1"/>
+      <c r="AB31" s="1"/>
+    </row>
+    <row r="33" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="C33" s="69">
+        <v>1</v>
+      </c>
+      <c r="D33" s="69">
+        <v>2</v>
+      </c>
+      <c r="E33" s="69">
+        <v>3</v>
+      </c>
+      <c r="F33" s="69">
+        <v>4</v>
+      </c>
+      <c r="G33" s="69">
+        <v>5</v>
+      </c>
+      <c r="H33" s="69">
+        <v>6</v>
+      </c>
+      <c r="I33" s="69">
+        <v>7</v>
+      </c>
+      <c r="J33" s="69">
+        <v>8</v>
+      </c>
+      <c r="K33" s="69">
+        <v>9</v>
+      </c>
+      <c r="L33" s="1">
+        <v>10</v>
+      </c>
+      <c r="M33" s="1">
+        <v>11</v>
+      </c>
+      <c r="N33" s="1">
+        <v>12</v>
+      </c>
+      <c r="O33" s="1">
+        <v>13</v>
+      </c>
+      <c r="P33" s="1">
+        <v>14</v>
+      </c>
+      <c r="Q33" s="1">
+        <v>15</v>
+      </c>
+      <c r="R33" s="1">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A34" s="187" t="s">
+        <v>101</v>
+      </c>
+      <c r="B34">
+        <v>1</v>
+      </c>
+      <c r="C34" s="70" t="s">
+        <v>80</v>
+      </c>
+      <c r="D34" s="71" t="s">
+        <v>102</v>
+      </c>
+      <c r="E34" s="71" t="s">
+        <v>103</v>
+      </c>
+      <c r="F34" s="71" t="s">
+        <v>105</v>
+      </c>
+      <c r="G34" s="218" t="s">
+        <v>100</v>
+      </c>
+      <c r="H34" s="218"/>
+      <c r="I34" s="218"/>
+      <c r="J34" s="218"/>
+      <c r="K34" s="218"/>
+      <c r="L34" s="71" t="s">
+        <v>76</v>
+      </c>
+      <c r="M34" s="71"/>
+      <c r="N34" s="71" t="s">
+        <v>98</v>
+      </c>
+      <c r="O34" s="71" t="s">
+        <v>99</v>
+      </c>
+      <c r="P34" s="71" t="s">
+        <v>104</v>
+      </c>
+      <c r="Q34" s="218"/>
+      <c r="R34" s="219"/>
+    </row>
+    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A35" s="187"/>
+      <c r="B35">
+        <v>2</v>
+      </c>
+      <c r="C35" s="223" t="s">
+        <v>77</v>
+      </c>
+      <c r="D35" s="187"/>
+      <c r="E35" s="187"/>
+      <c r="F35" s="187"/>
+      <c r="G35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="H35" s="187" t="s">
+        <v>78</v>
+      </c>
+      <c r="I35" s="187"/>
+      <c r="J35" s="187"/>
+      <c r="K35" s="187"/>
+      <c r="L35" s="1" t="s">
+        <v>76</v>
+      </c>
+      <c r="M35" s="187" t="s">
+        <v>79</v>
+      </c>
+      <c r="N35" s="187"/>
+      <c r="O35" s="187"/>
+      <c r="P35" s="187"/>
+      <c r="R35" s="74"/>
+    </row>
+    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
+      <c r="A36" s="187"/>
+      <c r="B36">
+        <v>3</v>
+      </c>
+      <c r="C36" s="80"/>
+      <c r="D36" s="83"/>
+      <c r="E36" s="83"/>
+      <c r="F36" s="83"/>
+      <c r="G36" s="83"/>
+      <c r="H36" s="83"/>
+      <c r="I36" s="83"/>
+      <c r="J36" s="83"/>
+      <c r="K36" s="83"/>
+      <c r="L36" s="83"/>
+      <c r="M36" s="83"/>
+      <c r="N36" s="83"/>
+      <c r="O36" s="83"/>
+      <c r="P36" s="83"/>
+      <c r="Q36" s="82"/>
+      <c r="R36" s="81"/>
+    </row>
+    <row r="37" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
+      <c r="A37" s="187"/>
+      <c r="B37">
+        <v>4</v>
+      </c>
+      <c r="C37" s="221"/>
+      <c r="D37" s="222"/>
+      <c r="E37" s="222"/>
+      <c r="F37" s="222"/>
+      <c r="G37" s="222"/>
+      <c r="H37" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="I37" s="222" t="s">
+        <v>97</v>
+      </c>
+      <c r="J37" s="222"/>
+      <c r="K37" s="222"/>
+      <c r="L37" s="222"/>
+      <c r="M37" s="69" t="s">
+        <v>76</v>
+      </c>
+      <c r="N37" s="222">
+        <v>250</v>
+      </c>
+      <c r="O37" s="222"/>
+      <c r="P37" s="222"/>
+      <c r="Q37" s="69" t="s">
+        <v>80</v>
+      </c>
+      <c r="R37" s="15" t="s">
+        <v>81</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="32">
+    <mergeCell ref="O29:R29"/>
+    <mergeCell ref="O28:R28"/>
+    <mergeCell ref="O21:R21"/>
+    <mergeCell ref="C21:F21"/>
+    <mergeCell ref="A34:A37"/>
+    <mergeCell ref="C35:F35"/>
+    <mergeCell ref="C37:G37"/>
+    <mergeCell ref="I37:L37"/>
+    <mergeCell ref="A27:A30"/>
+    <mergeCell ref="G27:K27"/>
+    <mergeCell ref="G34:K34"/>
+    <mergeCell ref="Q34:R34"/>
+    <mergeCell ref="H35:K35"/>
+    <mergeCell ref="M35:P35"/>
+    <mergeCell ref="N37:P37"/>
+    <mergeCell ref="A18:A22"/>
+    <mergeCell ref="C30:G30"/>
+    <mergeCell ref="I30:L30"/>
+    <mergeCell ref="C28:F28"/>
+    <mergeCell ref="G28:J28"/>
+    <mergeCell ref="K28:N28"/>
+    <mergeCell ref="C27:E27"/>
+    <mergeCell ref="C29:F29"/>
+    <mergeCell ref="G29:J29"/>
+    <mergeCell ref="K29:N29"/>
+    <mergeCell ref="C22:G22"/>
+    <mergeCell ref="I22:L22"/>
+    <mergeCell ref="G21:J21"/>
+    <mergeCell ref="K21:N21"/>
+    <mergeCell ref="C19:E19"/>
+    <mergeCell ref="C20:R20"/>
+    <mergeCell ref="Q19:R19"/>
+  </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9D80C86E-B8D5-4F55-A52E-43C4564E8A86}">
   <dimension ref="D1:P44"/>
   <sheetFormatPr defaultColWidth="9.23046875" defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
@@ -3777,120 +4441,120 @@
       <c r="G3" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H3" s="119" t="s">
+      <c r="H3" s="198" t="s">
         <v>3</v>
       </c>
-      <c r="I3" s="120"/>
-      <c r="J3" s="121"/>
+      <c r="I3" s="199"/>
+      <c r="J3" s="200"/>
       <c r="K3" s="11" t="s">
         <v>2</v>
       </c>
       <c r="L3" s="12" t="s">
         <v>29</v>
       </c>
-      <c r="M3" s="151" t="s">
+      <c r="M3" s="246" t="s">
         <v>20</v>
       </c>
-      <c r="N3" s="152"/>
+      <c r="N3" s="247"/>
       <c r="O3" s="32" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="4" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D4" s="93" t="s">
+      <c r="D4" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="E4" s="123" t="s">
+      <c r="E4" s="155" t="s">
         <v>4</v>
       </c>
-      <c r="F4" s="156">
+      <c r="F4" s="148">
         <v>2</v>
       </c>
-      <c r="G4" s="142" t="s">
+      <c r="G4" s="239" t="s">
         <v>62</v>
       </c>
-      <c r="H4" s="128" t="s">
+      <c r="H4" s="160" t="s">
         <v>42</v>
       </c>
-      <c r="I4" s="129"/>
+      <c r="I4" s="161"/>
       <c r="J4" s="68" t="s">
         <v>56</v>
       </c>
       <c r="K4" s="56" t="s">
         <v>57</v>
       </c>
-      <c r="L4" s="98" t="s">
+      <c r="L4" s="164" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="145" t="s">
+      <c r="M4" s="242" t="s">
         <v>21</v>
       </c>
-      <c r="N4" s="135"/>
-      <c r="O4" s="140" t="s">
+      <c r="N4" s="232"/>
+      <c r="O4" s="237" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="5" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D5" s="122"/>
-      <c r="E5" s="124"/>
-      <c r="F5" s="157"/>
-      <c r="G5" s="143"/>
-      <c r="H5" s="109"/>
-      <c r="I5" s="110"/>
-      <c r="J5" s="138" t="s">
+      <c r="D5" s="154"/>
+      <c r="E5" s="156"/>
+      <c r="F5" s="149"/>
+      <c r="G5" s="240"/>
+      <c r="H5" s="162"/>
+      <c r="I5" s="163"/>
+      <c r="J5" s="235" t="s">
         <v>70</v>
       </c>
       <c r="K5" s="47" t="s">
         <v>60</v>
       </c>
-      <c r="L5" s="99"/>
-      <c r="M5" s="146"/>
-      <c r="N5" s="136"/>
-      <c r="O5" s="130"/>
+      <c r="L5" s="165"/>
+      <c r="M5" s="243"/>
+      <c r="N5" s="233"/>
+      <c r="O5" s="227"/>
     </row>
     <row r="6" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D6" s="122"/>
-      <c r="E6" s="124"/>
-      <c r="F6" s="157"/>
-      <c r="G6" s="143"/>
-      <c r="H6" s="109"/>
-      <c r="I6" s="110"/>
-      <c r="J6" s="138"/>
+      <c r="D6" s="154"/>
+      <c r="E6" s="156"/>
+      <c r="F6" s="149"/>
+      <c r="G6" s="240"/>
+      <c r="H6" s="162"/>
+      <c r="I6" s="163"/>
+      <c r="J6" s="235"/>
       <c r="K6" s="47" t="s">
         <v>61</v>
       </c>
-      <c r="L6" s="99"/>
-      <c r="M6" s="146"/>
-      <c r="N6" s="136"/>
-      <c r="O6" s="130"/>
+      <c r="L6" s="165"/>
+      <c r="M6" s="243"/>
+      <c r="N6" s="233"/>
+      <c r="O6" s="227"/>
     </row>
     <row r="7" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D7" s="122"/>
-      <c r="E7" s="124"/>
-      <c r="F7" s="158"/>
-      <c r="G7" s="144"/>
-      <c r="H7" s="109"/>
-      <c r="I7" s="110"/>
-      <c r="J7" s="139"/>
+      <c r="D7" s="154"/>
+      <c r="E7" s="156"/>
+      <c r="F7" s="150"/>
+      <c r="G7" s="241"/>
+      <c r="H7" s="162"/>
+      <c r="I7" s="163"/>
+      <c r="J7" s="236"/>
       <c r="K7" s="48" t="s">
         <v>95</v>
       </c>
-      <c r="L7" s="100"/>
-      <c r="M7" s="146"/>
-      <c r="N7" s="137"/>
-      <c r="O7" s="130"/>
+      <c r="L7" s="166"/>
+      <c r="M7" s="243"/>
+      <c r="N7" s="234"/>
+      <c r="O7" s="227"/>
     </row>
     <row r="8" spans="4:16" ht="47.15" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="D8" s="122"/>
-      <c r="E8" s="124"/>
-      <c r="F8" s="101">
+      <c r="D8" s="154"/>
+      <c r="E8" s="156"/>
+      <c r="F8" s="167">
         <v>8</v>
       </c>
       <c r="G8" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H8" s="109"/>
-      <c r="I8" s="110"/>
+      <c r="H8" s="162"/>
+      <c r="I8" s="163"/>
       <c r="J8" s="57" t="s">
         <v>73</v>
       </c>
@@ -3900,21 +4564,21 @@
       <c r="L8" s="28">
         <v>2</v>
       </c>
-      <c r="M8" s="146"/>
+      <c r="M8" s="243"/>
       <c r="N8" s="33"/>
-      <c r="O8" s="130" t="s">
+      <c r="O8" s="227" t="s">
         <v>26</v>
       </c>
     </row>
     <row r="9" spans="4:16" ht="82.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D9" s="122"/>
-      <c r="E9" s="124"/>
-      <c r="F9" s="102"/>
+      <c r="D9" s="154"/>
+      <c r="E9" s="156"/>
+      <c r="F9" s="168"/>
       <c r="G9" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H9" s="109"/>
-      <c r="I9" s="110"/>
+      <c r="H9" s="162"/>
+      <c r="I9" s="163"/>
       <c r="J9" s="41" t="s">
         <v>64</v>
       </c>
@@ -3924,22 +4588,22 @@
       <c r="L9" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="M9" s="147"/>
+      <c r="M9" s="244"/>
       <c r="N9" s="34"/>
-      <c r="O9" s="141"/>
+      <c r="O9" s="238"/>
       <c r="P9" s="1" t="s">
         <v>40</v>
       </c>
     </row>
     <row r="10" spans="4:16" ht="3" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D10" s="122"/>
-      <c r="E10" s="124"/>
-      <c r="F10" s="103"/>
+      <c r="D10" s="154"/>
+      <c r="E10" s="156"/>
+      <c r="F10" s="169"/>
       <c r="G10" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H10" s="109"/>
-      <c r="I10" s="110"/>
+      <c r="H10" s="162"/>
+      <c r="I10" s="163"/>
       <c r="J10" s="8" t="s">
         <v>15</v>
       </c>
@@ -3952,8 +4616,8 @@
       <c r="O10" s="15"/>
     </row>
     <row r="11" spans="4:16" ht="33" customHeight="1" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="D11" s="122"/>
-      <c r="E11" s="104" t="s">
+      <c r="D11" s="154"/>
+      <c r="E11" s="170" t="s">
         <v>5</v>
       </c>
       <c r="F11" s="21">
@@ -3962,10 +4626,10 @@
       <c r="G11" s="20" t="s">
         <v>63</v>
       </c>
-      <c r="H11" s="107" t="s">
+      <c r="H11" s="173" t="s">
         <v>75</v>
       </c>
-      <c r="I11" s="108"/>
+      <c r="I11" s="174"/>
       <c r="J11" s="42" t="s">
         <v>71</v>
       </c>
@@ -3973,57 +4637,57 @@
         <v>94</v>
       </c>
       <c r="L11" s="30"/>
-      <c r="M11" s="132" t="s">
+      <c r="M11" s="229" t="s">
         <v>22</v>
       </c>
       <c r="N11" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="O11" s="130" t="s">
+      <c r="O11" s="227" t="s">
         <v>25</v>
       </c>
     </row>
     <row r="12" spans="4:16" x14ac:dyDescent="0.45">
-      <c r="D12" s="122"/>
-      <c r="E12" s="105"/>
-      <c r="F12" s="113">
+      <c r="D12" s="154"/>
+      <c r="E12" s="171"/>
+      <c r="F12" s="188">
         <v>8</v>
       </c>
       <c r="G12" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H12" s="109"/>
-      <c r="I12" s="110"/>
+      <c r="H12" s="162"/>
+      <c r="I12" s="163"/>
       <c r="J12" s="58" t="s">
         <v>72</v>
       </c>
-      <c r="K12" s="115" t="s">
+      <c r="K12" s="183" t="s">
         <v>38</v>
       </c>
-      <c r="L12" s="154" t="s">
+      <c r="L12" s="190" t="s">
         <v>68</v>
       </c>
-      <c r="M12" s="133"/>
-      <c r="N12" s="92"/>
-      <c r="O12" s="130"/>
+      <c r="M12" s="230"/>
+      <c r="N12" s="187"/>
+      <c r="O12" s="227"/>
     </row>
     <row r="13" spans="4:16" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D13" s="94"/>
-      <c r="E13" s="106"/>
-      <c r="F13" s="114"/>
+      <c r="D13" s="137"/>
+      <c r="E13" s="172"/>
+      <c r="F13" s="189"/>
       <c r="G13" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H13" s="111"/>
-      <c r="I13" s="112"/>
+      <c r="H13" s="175"/>
+      <c r="I13" s="176"/>
       <c r="J13" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="K13" s="116"/>
-      <c r="L13" s="155"/>
-      <c r="M13" s="134"/>
-      <c r="N13" s="153"/>
-      <c r="O13" s="131"/>
+      <c r="K13" s="184"/>
+      <c r="L13" s="191"/>
+      <c r="M13" s="231"/>
+      <c r="N13" s="248"/>
+      <c r="O13" s="228"/>
     </row>
     <row r="14" spans="4:16" x14ac:dyDescent="0.45">
       <c r="D14"/>
@@ -4048,10 +4712,10 @@
       <c r="L15"/>
     </row>
     <row r="16" spans="4:16" ht="32.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D16" s="93" t="s">
+      <c r="D16" s="136" t="s">
         <v>9</v>
       </c>
-      <c r="E16" s="148"/>
+      <c r="E16" s="192"/>
       <c r="F16" s="59">
         <v>8</v>
       </c>
@@ -4077,8 +4741,8 @@
       <c r="N16" s="14"/>
     </row>
     <row r="17" spans="4:14" ht="51" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D17" s="122"/>
-      <c r="E17" s="149"/>
+      <c r="D17" s="154"/>
+      <c r="E17" s="245"/>
       <c r="F17" s="60">
         <v>8</v>
       </c>
@@ -4099,8 +4763,8 @@
       <c r="N17" s="14"/>
     </row>
     <row r="18" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D18" s="94"/>
-      <c r="E18" s="150"/>
+      <c r="D18" s="137"/>
+      <c r="E18" s="194"/>
       <c r="F18" s="60">
         <v>1</v>
       </c>
@@ -4147,17 +4811,17 @@
     </row>
     <row r="29" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5"/>
     <row r="30" spans="4:14" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D30" s="95"/>
-      <c r="E30" s="96"/>
-      <c r="F30" s="97"/>
+      <c r="D30" s="195"/>
+      <c r="E30" s="196"/>
+      <c r="F30" s="197"/>
       <c r="G30" s="10" t="s">
         <v>10</v>
       </c>
-      <c r="H30" s="119" t="s">
+      <c r="H30" s="198" t="s">
         <v>3</v>
       </c>
-      <c r="I30" s="120"/>
-      <c r="J30" s="121"/>
+      <c r="I30" s="199"/>
+      <c r="J30" s="200"/>
       <c r="K30" s="11" t="s">
         <v>2</v>
       </c>
@@ -4166,88 +4830,88 @@
       </c>
     </row>
     <row r="31" spans="4:14" x14ac:dyDescent="0.45">
-      <c r="D31" s="93" t="s">
+      <c r="D31" s="136" t="s">
         <v>8</v>
       </c>
-      <c r="E31" s="123" t="s">
+      <c r="E31" s="155" t="s">
         <v>4</v>
       </c>
-      <c r="F31" s="125" t="s">
+      <c r="F31" s="157" t="s">
         <v>0</v>
       </c>
       <c r="G31" s="3" t="s">
         <v>12</v>
       </c>
-      <c r="H31" s="128" t="s">
+      <c r="H31" s="160" t="s">
         <v>42</v>
       </c>
-      <c r="I31" s="129"/>
+      <c r="I31" s="161"/>
       <c r="J31" s="38" t="s">
         <v>27</v>
       </c>
-      <c r="K31" s="98" t="s">
+      <c r="K31" s="164" t="s">
         <v>52</v>
       </c>
-      <c r="L31" s="98">
+      <c r="L31" s="164">
         <v>1</v>
       </c>
     </row>
     <row r="32" spans="4:14" x14ac:dyDescent="0.45">
-      <c r="D32" s="122"/>
-      <c r="E32" s="124"/>
-      <c r="F32" s="126"/>
+      <c r="D32" s="154"/>
+      <c r="E32" s="156"/>
+      <c r="F32" s="158"/>
       <c r="G32" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="H32" s="109"/>
-      <c r="I32" s="110"/>
+      <c r="H32" s="162"/>
+      <c r="I32" s="163"/>
       <c r="J32" s="39" t="s">
         <v>28</v>
       </c>
-      <c r="K32" s="99"/>
-      <c r="L32" s="99"/>
+      <c r="K32" s="165"/>
+      <c r="L32" s="165"/>
     </row>
     <row r="33" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D33" s="122"/>
-      <c r="E33" s="124"/>
-      <c r="F33" s="126"/>
+      <c r="D33" s="154"/>
+      <c r="E33" s="156"/>
+      <c r="F33" s="158"/>
       <c r="G33" s="4" t="s">
         <v>49</v>
       </c>
-      <c r="H33" s="109"/>
-      <c r="I33" s="110"/>
+      <c r="H33" s="162"/>
+      <c r="I33" s="163"/>
       <c r="J33" s="39" t="s">
         <v>47</v>
       </c>
-      <c r="K33" s="99"/>
-      <c r="L33" s="99"/>
+      <c r="K33" s="165"/>
+      <c r="L33" s="165"/>
     </row>
     <row r="34" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D34" s="122"/>
-      <c r="E34" s="124"/>
-      <c r="F34" s="127"/>
+      <c r="D34" s="154"/>
+      <c r="E34" s="156"/>
+      <c r="F34" s="159"/>
       <c r="G34" s="4" t="s">
         <v>32</v>
       </c>
-      <c r="H34" s="109"/>
-      <c r="I34" s="110"/>
+      <c r="H34" s="162"/>
+      <c r="I34" s="163"/>
       <c r="J34" s="39" t="s">
         <v>33</v>
       </c>
-      <c r="K34" s="100"/>
-      <c r="L34" s="100"/>
+      <c r="K34" s="166"/>
+      <c r="L34" s="166"/>
     </row>
     <row r="35" spans="4:12" ht="33" x14ac:dyDescent="0.45">
-      <c r="D35" s="122"/>
-      <c r="E35" s="124"/>
-      <c r="F35" s="101" t="s">
+      <c r="D35" s="154"/>
+      <c r="E35" s="156"/>
+      <c r="F35" s="167" t="s">
         <v>1</v>
       </c>
       <c r="G35" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="H35" s="109"/>
-      <c r="I35" s="110"/>
+      <c r="H35" s="162"/>
+      <c r="I35" s="163"/>
       <c r="J35" s="40" t="s">
         <v>34</v>
       </c>
@@ -4259,14 +4923,14 @@
       </c>
     </row>
     <row r="36" spans="4:12" ht="31.4" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D36" s="122"/>
-      <c r="E36" s="124"/>
-      <c r="F36" s="102"/>
+      <c r="D36" s="154"/>
+      <c r="E36" s="156"/>
+      <c r="F36" s="168"/>
       <c r="G36" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="H36" s="109"/>
-      <c r="I36" s="110"/>
+      <c r="H36" s="162"/>
+      <c r="I36" s="163"/>
       <c r="J36" s="41" t="s">
         <v>35</v>
       </c>
@@ -4278,14 +4942,14 @@
       </c>
     </row>
     <row r="37" spans="4:12" ht="1" hidden="1" customHeight="1" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D37" s="122"/>
-      <c r="E37" s="124"/>
-      <c r="F37" s="103"/>
+      <c r="D37" s="154"/>
+      <c r="E37" s="156"/>
+      <c r="F37" s="169"/>
       <c r="G37" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H37" s="109"/>
-      <c r="I37" s="110"/>
+      <c r="H37" s="162"/>
+      <c r="I37" s="163"/>
       <c r="J37" s="8" t="s">
         <v>15</v>
       </c>
@@ -4297,8 +4961,8 @@
       </c>
     </row>
     <row r="38" spans="4:12" ht="17" thickTop="1" x14ac:dyDescent="0.45">
-      <c r="D38" s="122"/>
-      <c r="E38" s="104" t="s">
+      <c r="D38" s="154"/>
+      <c r="E38" s="170" t="s">
         <v>5</v>
       </c>
       <c r="F38" s="21" t="s">
@@ -4307,10 +4971,10 @@
       <c r="G38" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="H38" s="107" t="s">
+      <c r="H38" s="173" t="s">
         <v>53</v>
       </c>
-      <c r="I38" s="108"/>
+      <c r="I38" s="174"/>
       <c r="J38" s="42" t="s">
         <v>50</v>
       </c>
@@ -4322,65 +4986,65 @@
       </c>
     </row>
     <row r="39" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D39" s="122"/>
-      <c r="E39" s="105"/>
-      <c r="F39" s="113" t="s">
+      <c r="D39" s="154"/>
+      <c r="E39" s="171"/>
+      <c r="F39" s="188" t="s">
         <v>1</v>
       </c>
       <c r="G39" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="H39" s="109"/>
-      <c r="I39" s="110"/>
+      <c r="H39" s="162"/>
+      <c r="I39" s="163"/>
       <c r="J39" s="43" t="s">
         <v>46</v>
       </c>
-      <c r="K39" s="115" t="s">
+      <c r="K39" s="183" t="s">
         <v>38</v>
       </c>
-      <c r="L39" s="117">
+      <c r="L39" s="185">
         <v>2</v>
       </c>
     </row>
     <row r="40" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D40" s="94"/>
-      <c r="E40" s="106"/>
-      <c r="F40" s="114"/>
+      <c r="D40" s="137"/>
+      <c r="E40" s="172"/>
+      <c r="F40" s="189"/>
       <c r="G40" s="6" t="s">
         <v>51</v>
       </c>
-      <c r="H40" s="111"/>
-      <c r="I40" s="112"/>
+      <c r="H40" s="175"/>
+      <c r="I40" s="176"/>
       <c r="J40" s="44" t="s">
         <v>47</v>
       </c>
-      <c r="K40" s="116"/>
-      <c r="L40" s="118"/>
+      <c r="K40" s="184"/>
+      <c r="L40" s="186"/>
     </row>
     <row r="41" spans="4:12" x14ac:dyDescent="0.45">
-      <c r="D41" s="92"/>
-      <c r="E41" s="92"/>
-      <c r="F41" s="92"/>
-      <c r="G41" s="92"/>
-      <c r="H41" s="92"/>
-      <c r="I41" s="92"/>
-      <c r="J41" s="92"/>
-      <c r="K41" s="92"/>
-      <c r="L41" s="92"/>
+      <c r="D41" s="187"/>
+      <c r="E41" s="187"/>
+      <c r="F41" s="187"/>
+      <c r="G41" s="187"/>
+      <c r="H41" s="187"/>
+      <c r="I41" s="187"/>
+      <c r="J41" s="187"/>
+      <c r="K41" s="187"/>
+      <c r="L41" s="187"/>
     </row>
     <row r="42" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D42" s="92"/>
-      <c r="E42" s="92"/>
-      <c r="F42" s="92"/>
-      <c r="G42" s="92"/>
-      <c r="H42" s="92"/>
-      <c r="I42" s="92"/>
-      <c r="J42" s="92"/>
-      <c r="K42" s="92"/>
-      <c r="L42" s="92"/>
+      <c r="D42" s="187"/>
+      <c r="E42" s="187"/>
+      <c r="F42" s="187"/>
+      <c r="G42" s="187"/>
+      <c r="H42" s="187"/>
+      <c r="I42" s="187"/>
+      <c r="J42" s="187"/>
+      <c r="K42" s="187"/>
+      <c r="L42" s="187"/>
     </row>
     <row r="43" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D43" s="93" t="s">
+      <c r="D43" s="136" t="s">
         <v>9</v>
       </c>
       <c r="E43" s="25"/>
@@ -4405,7 +5069,7 @@
       </c>
     </row>
     <row r="44" spans="4:12" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="D44" s="94"/>
+      <c r="D44" s="137"/>
       <c r="E44" s="25"/>
       <c r="F44" s="46" t="s">
         <v>0</v>
@@ -4475,687 +5139,4 @@
   <drawing r:id="rId1"/>
   <legacyDrawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8521510C-1B37-40AB-AFA2-021412ADBA84}">
-  <dimension ref="A4:AB37"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.45"/>
-  <cols>
-    <col min="3" max="18" width="2.765625" style="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A4" s="86"/>
-    </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="C5" s="84"/>
-      <c r="D5" s="84"/>
-      <c r="E5" s="84"/>
-      <c r="G5" s="84"/>
-      <c r="H5" s="84"/>
-      <c r="I5" s="84"/>
-      <c r="K5" s="85"/>
-      <c r="M5" s="76"/>
-      <c r="Q5"/>
-      <c r="R5"/>
-    </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="C6" s="84"/>
-      <c r="D6" s="84"/>
-      <c r="E6" s="84"/>
-      <c r="F6" s="84"/>
-      <c r="G6" s="84"/>
-      <c r="H6" s="84"/>
-      <c r="I6" s="84"/>
-      <c r="J6" s="84"/>
-      <c r="K6" s="84"/>
-      <c r="L6" s="84"/>
-      <c r="M6" s="84"/>
-      <c r="N6" s="84"/>
-      <c r="O6" s="84"/>
-      <c r="P6" s="84"/>
-      <c r="Q6" s="84"/>
-      <c r="R6" s="84"/>
-    </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="C7"/>
-      <c r="D7"/>
-      <c r="E7"/>
-      <c r="F7"/>
-      <c r="H7"/>
-      <c r="I7"/>
-      <c r="J7"/>
-      <c r="K7"/>
-      <c r="M7"/>
-      <c r="N7"/>
-      <c r="O7"/>
-      <c r="P7"/>
-    </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="C8" s="84"/>
-      <c r="D8" s="84"/>
-      <c r="E8" s="84"/>
-      <c r="F8" s="84"/>
-      <c r="G8" s="84"/>
-      <c r="I8" s="84"/>
-      <c r="J8" s="84"/>
-      <c r="K8" s="84"/>
-      <c r="L8" s="84"/>
-    </row>
-    <row r="12" spans="1:18" ht="16.5" customHeight="1" x14ac:dyDescent="0.45">
-      <c r="A12" s="86" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="84"/>
-      <c r="D12" s="84"/>
-      <c r="E12" s="84"/>
-      <c r="G12" s="84"/>
-      <c r="H12" s="84"/>
-      <c r="I12" s="84"/>
-      <c r="K12" s="85"/>
-      <c r="M12" s="76"/>
-      <c r="Q12"/>
-      <c r="R12"/>
-    </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="C13" s="84"/>
-      <c r="D13" s="84"/>
-      <c r="E13" s="84"/>
-      <c r="F13" s="84"/>
-      <c r="G13" s="84"/>
-      <c r="H13" s="84"/>
-      <c r="I13" s="84"/>
-      <c r="J13" s="84"/>
-      <c r="K13" s="84"/>
-      <c r="L13" s="84"/>
-      <c r="M13" s="84"/>
-      <c r="N13" s="84"/>
-      <c r="O13" s="84"/>
-      <c r="P13" s="84"/>
-      <c r="Q13" s="84"/>
-      <c r="R13" s="84"/>
-    </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="C14"/>
-      <c r="D14"/>
-      <c r="E14"/>
-      <c r="F14"/>
-      <c r="H14"/>
-      <c r="I14"/>
-      <c r="J14"/>
-      <c r="K14"/>
-      <c r="M14"/>
-      <c r="N14"/>
-      <c r="O14"/>
-      <c r="P14"/>
-    </row>
-    <row r="15" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="C15" s="84"/>
-      <c r="D15" s="84"/>
-      <c r="E15" s="84"/>
-      <c r="F15" s="84"/>
-      <c r="G15" s="84"/>
-      <c r="I15" s="84"/>
-      <c r="J15" s="84"/>
-      <c r="K15" s="84"/>
-      <c r="L15" s="84"/>
-    </row>
-    <row r="18" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A18" s="169" t="s">
-        <v>87</v>
-      </c>
-      <c r="C18" s="1">
-        <v>1</v>
-      </c>
-      <c r="D18" s="1">
-        <v>2</v>
-      </c>
-      <c r="E18" s="1">
-        <v>3</v>
-      </c>
-      <c r="F18" s="1">
-        <v>4</v>
-      </c>
-      <c r="G18" s="1">
-        <v>5</v>
-      </c>
-      <c r="H18" s="1">
-        <v>6</v>
-      </c>
-      <c r="I18" s="1">
-        <v>7</v>
-      </c>
-      <c r="J18" s="1">
-        <v>8</v>
-      </c>
-      <c r="K18" s="1">
-        <v>9</v>
-      </c>
-      <c r="L18" s="1">
-        <v>10</v>
-      </c>
-      <c r="M18" s="1">
-        <v>11</v>
-      </c>
-      <c r="N18" s="1">
-        <v>12</v>
-      </c>
-      <c r="O18" s="1">
-        <v>13</v>
-      </c>
-      <c r="P18" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q18" s="1">
-        <v>15</v>
-      </c>
-      <c r="R18" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A19" s="92"/>
-      <c r="B19">
-        <v>1</v>
-      </c>
-      <c r="C19" s="162" t="s">
-        <v>107</v>
-      </c>
-      <c r="D19" s="163"/>
-      <c r="E19" s="163"/>
-      <c r="F19" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="G19" s="77"/>
-      <c r="H19" s="77"/>
-      <c r="I19" s="77"/>
-      <c r="J19" s="71"/>
-      <c r="K19" s="78"/>
-      <c r="L19" s="71"/>
-      <c r="M19" s="75"/>
-      <c r="N19" s="71"/>
-      <c r="O19" s="71"/>
-      <c r="P19" s="71"/>
-      <c r="Q19" s="167"/>
-      <c r="R19" s="168"/>
-    </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A20" s="92"/>
-      <c r="B20">
-        <v>2</v>
-      </c>
-      <c r="C20" s="164" t="s">
-        <v>82</v>
-      </c>
-      <c r="D20" s="165"/>
-      <c r="E20" s="165"/>
-      <c r="F20" s="165"/>
-      <c r="G20" s="165"/>
-      <c r="H20" s="165"/>
-      <c r="I20" s="165"/>
-      <c r="J20" s="165"/>
-      <c r="K20" s="165"/>
-      <c r="L20" s="165"/>
-      <c r="M20" s="165"/>
-      <c r="N20" s="165"/>
-      <c r="O20" s="165"/>
-      <c r="P20" s="165"/>
-      <c r="Q20" s="165"/>
-      <c r="R20" s="166"/>
-    </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A21" s="92"/>
-      <c r="B21">
-        <v>3</v>
-      </c>
-      <c r="C21" s="171" t="s">
-        <v>106</v>
-      </c>
-      <c r="D21" s="161"/>
-      <c r="E21" s="161"/>
-      <c r="F21" s="161"/>
-      <c r="G21" s="161" t="s">
-        <v>84</v>
-      </c>
-      <c r="H21" s="161"/>
-      <c r="I21" s="161"/>
-      <c r="J21" s="161"/>
-      <c r="K21" s="161" t="s">
-        <v>85</v>
-      </c>
-      <c r="L21" s="161"/>
-      <c r="M21" s="161"/>
-      <c r="N21" s="161"/>
-      <c r="O21" s="161" t="s">
-        <v>86</v>
-      </c>
-      <c r="P21" s="161"/>
-      <c r="Q21" s="161"/>
-      <c r="R21" s="172"/>
-    </row>
-    <row r="22" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A22" s="92"/>
-      <c r="B22">
-        <v>4</v>
-      </c>
-      <c r="C22" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="D22" s="160"/>
-      <c r="E22" s="160"/>
-      <c r="F22" s="160"/>
-      <c r="G22" s="160"/>
-      <c r="H22" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="I22" s="160" t="s">
-        <v>97</v>
-      </c>
-      <c r="J22" s="160"/>
-      <c r="K22" s="160"/>
-      <c r="L22" s="160"/>
-      <c r="M22" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="N22" s="69"/>
-      <c r="O22" s="69"/>
-      <c r="P22" s="69"/>
-      <c r="Q22" s="69"/>
-      <c r="R22" s="15"/>
-    </row>
-    <row r="26" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C26" s="1">
-        <v>1</v>
-      </c>
-      <c r="D26" s="1">
-        <v>2</v>
-      </c>
-      <c r="E26" s="1">
-        <v>3</v>
-      </c>
-      <c r="F26" s="1">
-        <v>4</v>
-      </c>
-      <c r="G26" s="1">
-        <v>5</v>
-      </c>
-      <c r="H26" s="1">
-        <v>6</v>
-      </c>
-      <c r="I26" s="1">
-        <v>7</v>
-      </c>
-      <c r="J26" s="1">
-        <v>8</v>
-      </c>
-      <c r="K26" s="1">
-        <v>9</v>
-      </c>
-      <c r="L26" s="1">
-        <v>10</v>
-      </c>
-      <c r="M26" s="1">
-        <v>11</v>
-      </c>
-      <c r="N26" s="1">
-        <v>12</v>
-      </c>
-      <c r="O26" s="1">
-        <v>13</v>
-      </c>
-      <c r="P26" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q26" s="1">
-        <v>15</v>
-      </c>
-      <c r="R26" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="27" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A27" s="92" t="s">
-        <v>96</v>
-      </c>
-      <c r="B27">
-        <v>1</v>
-      </c>
-      <c r="C27" s="162" t="s">
-        <v>109</v>
-      </c>
-      <c r="D27" s="163"/>
-      <c r="E27" s="163"/>
-      <c r="F27" s="71"/>
-      <c r="G27" s="163" t="s">
-        <v>108</v>
-      </c>
-      <c r="H27" s="163"/>
-      <c r="I27" s="163"/>
-      <c r="J27" s="163"/>
-      <c r="K27" s="163"/>
-      <c r="L27" s="71"/>
-      <c r="M27" s="71"/>
-      <c r="N27" s="71"/>
-      <c r="O27" s="71"/>
-      <c r="P27" s="71"/>
-      <c r="Q27" s="71"/>
-      <c r="R27" s="72"/>
-    </row>
-    <row r="28" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A28" s="92"/>
-      <c r="B28">
-        <v>2</v>
-      </c>
-      <c r="C28" s="170" t="s">
-        <v>89</v>
-      </c>
-      <c r="D28" s="92"/>
-      <c r="E28" s="92"/>
-      <c r="F28" s="92"/>
-      <c r="G28" s="92" t="s">
-        <v>84</v>
-      </c>
-      <c r="H28" s="92"/>
-      <c r="I28" s="92"/>
-      <c r="J28" s="92"/>
-      <c r="K28" s="92" t="s">
-        <v>85</v>
-      </c>
-      <c r="L28" s="92"/>
-      <c r="M28" s="92"/>
-      <c r="N28" s="92"/>
-      <c r="O28" s="92" t="s">
-        <v>86</v>
-      </c>
-      <c r="P28" s="92"/>
-      <c r="Q28" s="92"/>
-      <c r="R28" s="173"/>
-    </row>
-    <row r="29" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="A29" s="92"/>
-      <c r="B29">
-        <v>3</v>
-      </c>
-      <c r="C29" s="171" t="s">
-        <v>88</v>
-      </c>
-      <c r="D29" s="161"/>
-      <c r="E29" s="161"/>
-      <c r="F29" s="161"/>
-      <c r="G29" s="161" t="s">
-        <v>84</v>
-      </c>
-      <c r="H29" s="161"/>
-      <c r="I29" s="161"/>
-      <c r="J29" s="161"/>
-      <c r="K29" s="161" t="s">
-        <v>85</v>
-      </c>
-      <c r="L29" s="161"/>
-      <c r="M29" s="161"/>
-      <c r="N29" s="161"/>
-      <c r="O29" s="161" t="s">
-        <v>86</v>
-      </c>
-      <c r="P29" s="161"/>
-      <c r="Q29" s="161"/>
-      <c r="R29" s="172"/>
-    </row>
-    <row r="30" spans="1:28" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A30" s="92"/>
-      <c r="B30">
-        <v>4</v>
-      </c>
-      <c r="C30" s="159" t="s">
-        <v>83</v>
-      </c>
-      <c r="D30" s="160"/>
-      <c r="E30" s="160"/>
-      <c r="F30" s="160"/>
-      <c r="G30" s="160"/>
-      <c r="H30" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="I30" s="160" t="s">
-        <v>97</v>
-      </c>
-      <c r="J30" s="160"/>
-      <c r="K30" s="160"/>
-      <c r="L30" s="160"/>
-      <c r="M30" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="N30" s="69"/>
-      <c r="O30" s="79"/>
-      <c r="P30" s="79"/>
-      <c r="Q30" s="69"/>
-      <c r="R30" s="15"/>
-    </row>
-    <row r="31" spans="1:28" x14ac:dyDescent="0.45">
-      <c r="V31" s="73"/>
-      <c r="W31" s="1"/>
-      <c r="X31" s="1"/>
-      <c r="Y31" s="1"/>
-      <c r="Z31" s="1"/>
-      <c r="AA31" s="1"/>
-      <c r="AB31" s="1"/>
-    </row>
-    <row r="33" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="C33" s="69">
-        <v>1</v>
-      </c>
-      <c r="D33" s="69">
-        <v>2</v>
-      </c>
-      <c r="E33" s="69">
-        <v>3</v>
-      </c>
-      <c r="F33" s="69">
-        <v>4</v>
-      </c>
-      <c r="G33" s="69">
-        <v>5</v>
-      </c>
-      <c r="H33" s="69">
-        <v>6</v>
-      </c>
-      <c r="I33" s="69">
-        <v>7</v>
-      </c>
-      <c r="J33" s="69">
-        <v>8</v>
-      </c>
-      <c r="K33" s="69">
-        <v>9</v>
-      </c>
-      <c r="L33" s="1">
-        <v>10</v>
-      </c>
-      <c r="M33" s="1">
-        <v>11</v>
-      </c>
-      <c r="N33" s="1">
-        <v>12</v>
-      </c>
-      <c r="O33" s="1">
-        <v>13</v>
-      </c>
-      <c r="P33" s="1">
-        <v>14</v>
-      </c>
-      <c r="Q33" s="1">
-        <v>15</v>
-      </c>
-      <c r="R33" s="1">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A34" s="92" t="s">
-        <v>101</v>
-      </c>
-      <c r="B34">
-        <v>1</v>
-      </c>
-      <c r="C34" s="70" t="s">
-        <v>80</v>
-      </c>
-      <c r="D34" s="71" t="s">
-        <v>102</v>
-      </c>
-      <c r="E34" s="71" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="71" t="s">
-        <v>105</v>
-      </c>
-      <c r="G34" s="167" t="s">
-        <v>100</v>
-      </c>
-      <c r="H34" s="167"/>
-      <c r="I34" s="167"/>
-      <c r="J34" s="167"/>
-      <c r="K34" s="167"/>
-      <c r="L34" s="71" t="s">
-        <v>76</v>
-      </c>
-      <c r="M34" s="71"/>
-      <c r="N34" s="71" t="s">
-        <v>98</v>
-      </c>
-      <c r="O34" s="71" t="s">
-        <v>99</v>
-      </c>
-      <c r="P34" s="71" t="s">
-        <v>104</v>
-      </c>
-      <c r="Q34" s="167"/>
-      <c r="R34" s="168"/>
-    </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A35" s="92"/>
-      <c r="B35">
-        <v>2</v>
-      </c>
-      <c r="C35" s="170" t="s">
-        <v>77</v>
-      </c>
-      <c r="D35" s="92"/>
-      <c r="E35" s="92"/>
-      <c r="F35" s="92"/>
-      <c r="G35" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="H35" s="92" t="s">
-        <v>78</v>
-      </c>
-      <c r="I35" s="92"/>
-      <c r="J35" s="92"/>
-      <c r="K35" s="92"/>
-      <c r="L35" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="M35" s="92" t="s">
-        <v>79</v>
-      </c>
-      <c r="N35" s="92"/>
-      <c r="O35" s="92"/>
-      <c r="P35" s="92"/>
-      <c r="R35" s="74"/>
-    </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.45">
-      <c r="A36" s="92"/>
-      <c r="B36">
-        <v>3</v>
-      </c>
-      <c r="C36" s="80"/>
-      <c r="D36" s="83"/>
-      <c r="E36" s="83"/>
-      <c r="F36" s="83"/>
-      <c r="G36" s="83"/>
-      <c r="H36" s="83"/>
-      <c r="I36" s="83"/>
-      <c r="J36" s="83"/>
-      <c r="K36" s="83"/>
-      <c r="L36" s="83"/>
-      <c r="M36" s="83"/>
-      <c r="N36" s="83"/>
-      <c r="O36" s="83"/>
-      <c r="P36" s="83"/>
-      <c r="Q36" s="82"/>
-      <c r="R36" s="81"/>
-    </row>
-    <row r="37" spans="1:18" ht="17" thickBot="1" x14ac:dyDescent="0.5">
-      <c r="A37" s="92"/>
-      <c r="B37">
-        <v>4</v>
-      </c>
-      <c r="C37" s="159"/>
-      <c r="D37" s="160"/>
-      <c r="E37" s="160"/>
-      <c r="F37" s="160"/>
-      <c r="G37" s="160"/>
-      <c r="H37" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="I37" s="160" t="s">
-        <v>97</v>
-      </c>
-      <c r="J37" s="160"/>
-      <c r="K37" s="160"/>
-      <c r="L37" s="160"/>
-      <c r="M37" s="69" t="s">
-        <v>76</v>
-      </c>
-      <c r="N37" s="160">
-        <v>250</v>
-      </c>
-      <c r="O37" s="160"/>
-      <c r="P37" s="160"/>
-      <c r="Q37" s="69" t="s">
-        <v>80</v>
-      </c>
-      <c r="R37" s="15" t="s">
-        <v>81</v>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="32">
-    <mergeCell ref="O29:R29"/>
-    <mergeCell ref="O28:R28"/>
-    <mergeCell ref="O21:R21"/>
-    <mergeCell ref="C21:F21"/>
-    <mergeCell ref="A34:A37"/>
-    <mergeCell ref="C35:F35"/>
-    <mergeCell ref="C37:G37"/>
-    <mergeCell ref="I37:L37"/>
-    <mergeCell ref="A27:A30"/>
-    <mergeCell ref="G27:K27"/>
-    <mergeCell ref="G34:K34"/>
-    <mergeCell ref="Q34:R34"/>
-    <mergeCell ref="H35:K35"/>
-    <mergeCell ref="M35:P35"/>
-    <mergeCell ref="N37:P37"/>
-    <mergeCell ref="A18:A22"/>
-    <mergeCell ref="C30:G30"/>
-    <mergeCell ref="I30:L30"/>
-    <mergeCell ref="C28:F28"/>
-    <mergeCell ref="G28:J28"/>
-    <mergeCell ref="K28:N28"/>
-    <mergeCell ref="C27:E27"/>
-    <mergeCell ref="C29:F29"/>
-    <mergeCell ref="G29:J29"/>
-    <mergeCell ref="K29:N29"/>
-    <mergeCell ref="C22:G22"/>
-    <mergeCell ref="I22:L22"/>
-    <mergeCell ref="G21:J21"/>
-    <mergeCell ref="K21:N21"/>
-    <mergeCell ref="C19:E19"/>
-    <mergeCell ref="C20:R20"/>
-    <mergeCell ref="Q19:R19"/>
-  </mergeCells>
-  <phoneticPr fontId="6" type="noConversion"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>